--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821A6BE3-39FF-4922-A0E4-0DFCE10B668C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4871CBD-AA8F-42B8-BF9D-1136F01B388B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="233">
   <si>
     <t>N</t>
   </si>
@@ -799,6 +799,21 @@
   </si>
   <si>
     <t>Unit conversion Exiobase  (p.cap)</t>
+  </si>
+  <si>
+    <t>GtC</t>
+  </si>
+  <si>
+    <t>MtC</t>
+  </si>
+  <si>
+    <t>tC</t>
+  </si>
+  <si>
+    <t>Biodiversity loss - HANPP</t>
+  </si>
+  <si>
+    <t>Biodiversity loss - PDF</t>
   </si>
 </sst>
 </file>
@@ -1194,23 +1209,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1505,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C32444-97C3-4A7C-A91C-82059EB528AD}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27" style="28" customWidth="1"/>
@@ -1515,10 +1530,11 @@
     <col min="5" max="7" width="9.19921875" style="28"/>
     <col min="8" max="8" width="11.9296875" style="28" customWidth="1"/>
     <col min="9" max="9" width="13.9296875" style="28" customWidth="1"/>
-    <col min="10" max="16384" width="9.19921875" style="28"/>
+    <col min="10" max="10" width="16.06640625" style="28" customWidth="1"/>
+    <col min="11" max="16384" width="9.19921875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="68" t="s">
         <v>216</v>
       </c>
@@ -1544,10 +1560,13 @@
         <v>197</v>
       </c>
       <c r="I1" s="70" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+        <v>232</v>
+      </c>
+      <c r="J1" s="70" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="61" t="s">
         <v>210</v>
       </c>
@@ -1568,8 +1587,9 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J2" s="62"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="63" t="s">
         <v>212</v>
       </c>
@@ -1598,8 +1618,11 @@
       <c r="I3" s="65">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J3" s="65">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="63" t="s">
         <v>211</v>
       </c>
@@ -1626,8 +1649,12 @@
         <v>50</v>
       </c>
       <c r="I4" s="64"/>
-    </row>
-    <row r="5" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="J4" s="64">
+        <f>J3*2</f>
+        <v>11.18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="66" t="s">
         <v>218</v>
       </c>
@@ -1655,8 +1682,11 @@
       <c r="I5" s="67" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J5" s="67" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -1666,8 +1696,9 @@
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
       <c r="I6" s="20"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J6" s="20"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="52" t="s">
         <v>224</v>
       </c>
@@ -1695,8 +1726,11 @@
       <c r="I7" s="53">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J7" s="53">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="34" t="s">
         <v>213</v>
       </c>
@@ -1732,8 +1766,12 @@
         <f>(Population!C121/100)*I2</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J8" s="35">
+        <f>(Population!D121/100)*J2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="34" t="s">
         <v>215</v>
       </c>
@@ -1769,8 +1807,12 @@
         <f>(Population!C123/100)*I3*1000</f>
         <v>45.782469885452663</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J9" s="50">
+        <f>(Population!C123/100)*J3*1000</f>
+        <v>39.372924101489289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="34" t="s">
         <v>214</v>
       </c>
@@ -1806,8 +1848,12 @@
         <f>(Population!C123/100)*I4</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J10" s="35">
+        <f>(Population!D123/100)*J4*1000</f>
+        <v>467.33034413233798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="34" t="s">
         <v>217</v>
       </c>
@@ -1835,8 +1881,11 @@
       <c r="I11" s="35" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J11" s="35" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="52" t="s">
         <v>225</v>
       </c>
@@ -1865,8 +1914,11 @@
       <c r="I12" s="53">
         <v>1000000000</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" s="60" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="J12" s="53">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="60" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="58"/>
       <c r="B13" s="59"/>
       <c r="C13" s="59"/>
@@ -1875,8 +1927,9 @@
       <c r="F13" s="59"/>
       <c r="H13" s="59"/>
       <c r="I13" s="59"/>
-    </row>
-    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="J13" s="59"/>
+    </row>
+    <row r="14" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="56" t="s">
         <v>223</v>
       </c>
@@ -1904,8 +1957,11 @@
       <c r="I14" s="57" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J14" s="57" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -1915,8 +1971,9 @@
       <c r="G15" s="20"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="52" t="s">
         <v>226</v>
       </c>
@@ -1944,8 +2001,11 @@
       <c r="I16" s="53">
         <v>9.9999999999999998E-13</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J16" s="53">
+        <v>1.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="31" t="s">
         <v>219</v>
       </c>
@@ -1981,8 +2041,12 @@
         <f>I2*1000000/(Population!B120*1000)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J17" s="22">
+        <f>J2*1000000/(Population!C120*1000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="31" t="s">
         <v>220</v>
       </c>
@@ -2018,8 +2082,12 @@
         <f>I3/(Population!B122*1000)*1000000000000</f>
         <v>675.29581650469493</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J18" s="51">
+        <f>J3/(Population!C122*1000)*1000000000</f>
+        <v>82.453035489479262</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="31" t="s">
         <v>221</v>
       </c>
@@ -2055,8 +2123,12 @@
         <f>I4*1000000/(Population!B122*1000)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="J19" s="22">
+        <f>J4*1000000000/(Population!C122*1000)</f>
+        <v>164.90607097895855</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="32" t="s">
         <v>222</v>
       </c>
@@ -2084,8 +2156,11 @@
       <c r="I20" s="33" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J20" s="33" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="52" t="s">
         <v>227</v>
       </c>
@@ -2113,8 +2188,11 @@
       <c r="I21" s="55">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J21" s="55">
+        <v>1.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -2124,8 +2202,9 @@
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="19" t="s">
         <v>16</v>
       </c>
@@ -2161,8 +2240,12 @@
         <f>(Capacité!C43/100)*I3</f>
         <v>3.4277425263741722E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J23" s="28">
+        <f>(Capacité!D43/100)*J3</f>
+        <v>5.2035456186419131E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="19" t="s">
         <v>102</v>
       </c>
@@ -2198,11 +2281,15 @@
         <f>(Capacité!C43/100)*I4</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J24" s="28">
+        <f>(Capacité!D43/100)*J4</f>
+        <v>0.10407091237283826</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="19"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="19"/>
     </row>
   </sheetData>
@@ -3556,44 +3643,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="76" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="75" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="76" t="s">
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="L2" s="76"/>
+      <c r="L2" s="78"/>
       <c r="M2" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="73" t="s">
         <v>140</v>
       </c>
-      <c r="O2" s="75" t="s">
+      <c r="O2" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="76" t="s">
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="78" t="s">
         <v>142</v>
       </c>
-      <c r="S2" s="76"/>
+      <c r="S2" s="78"/>
       <c r="T2" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="U2" s="78" t="s">
+      <c r="U2" s="76" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3607,13 +3694,13 @@
       <c r="D3" s="74" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="75" t="s">
         <v>148</v>
       </c>
       <c r="H3" s="74" t="s">
@@ -3625,14 +3712,14 @@
       <c r="J3" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="K3" s="73" t="s">
+      <c r="K3" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="L3" s="73" t="s">
+      <c r="L3" s="75" t="s">
         <v>153</v>
       </c>
       <c r="M3" s="79"/>
-      <c r="N3" s="77"/>
+      <c r="N3" s="73"/>
       <c r="O3" s="74" t="s">
         <v>154</v>
       </c>
@@ -3642,38 +3729,38 @@
       <c r="Q3" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="R3" s="73" t="s">
+      <c r="R3" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="73" t="s">
+      <c r="S3" s="75" t="s">
         <v>159</v>
       </c>
       <c r="T3" s="80"/>
-      <c r="U3" s="78"/>
+      <c r="U3" s="76"/>
     </row>
     <row r="4" spans="1:21" ht="38.200000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="74"/>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
       <c r="H4" s="74"/>
       <c r="I4" s="74"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
       <c r="M4" s="79"/>
-      <c r="N4" s="77"/>
+      <c r="N4" s="73"/>
       <c r="O4" s="74"/>
       <c r="P4" s="74"/>
       <c r="Q4" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
       <c r="T4" s="80"/>
-      <c r="U4" s="78"/>
+      <c r="U4" s="76"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
@@ -3748,6 +3835,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -3762,17 +3860,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CD9438-1FE7-434C-817E-AA569D679644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152913D0-5B42-4953-B03F-D9947FCD0463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -984,23 +984,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -6803,44 +6803,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="75" t="s">
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="74" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="75" t="s">
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="73"/>
       <c r="M2" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="70" t="s">
+      <c r="N2" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="O2" s="74" t="s">
+      <c r="O2" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="75" t="s">
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="S2" s="75"/>
+      <c r="S2" s="73"/>
       <c r="T2" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="U2" s="73" t="s">
+      <c r="U2" s="75" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6854,13 +6854,13 @@
       <c r="D3" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="70" t="s">
         <v>80</v>
       </c>
       <c r="H3" s="71" t="s">
@@ -6872,14 +6872,14 @@
       <c r="J3" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="72" t="s">
+      <c r="K3" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="L3" s="72" t="s">
+      <c r="L3" s="70" t="s">
         <v>85</v>
       </c>
       <c r="M3" s="76"/>
-      <c r="N3" s="70"/>
+      <c r="N3" s="74"/>
       <c r="O3" s="71" t="s">
         <v>86</v>
       </c>
@@ -6889,38 +6889,38 @@
       <c r="Q3" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="72" t="s">
+      <c r="R3" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="72" t="s">
+      <c r="S3" s="70" t="s">
         <v>91</v>
       </c>
       <c r="T3" s="77"/>
-      <c r="U3" s="73"/>
+      <c r="U3" s="75"/>
     </row>
     <row r="4" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="71"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
       <c r="H4" s="71"/>
       <c r="I4" s="71"/>
       <c r="J4" s="71"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
       <c r="M4" s="76"/>
-      <c r="N4" s="70"/>
+      <c r="N4" s="74"/>
       <c r="O4" s="71"/>
       <c r="P4" s="71"/>
       <c r="Q4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="70"/>
       <c r="T4" s="77"/>
-      <c r="U4" s="73"/>
+      <c r="U4" s="75"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="17" t="s">
@@ -6995,17 +6995,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -7020,6 +7009,17 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152913D0-5B42-4953-B03F-D9947FCD0463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A250043-D248-4C76-A82D-BA9E85CA36FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="DLE" sheetId="7" r:id="rId6"/>
     <sheet name="Besoins" sheetId="6" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="156">
   <si>
     <t>GES</t>
   </si>
@@ -372,18 +372,12 @@
     <t>Moyenne France</t>
   </si>
   <si>
-    <t>1e3 km2</t>
-  </si>
-  <si>
     <t>Monde</t>
   </si>
   <si>
     <t>MtCO2eq</t>
   </si>
   <si>
-    <t>Gm3</t>
-  </si>
-  <si>
     <t>Europe</t>
   </si>
   <si>
@@ -429,9 +423,6 @@
     <t>PDF.m2.yr</t>
   </si>
   <si>
-    <t>1e9 PDF.m2.yr</t>
-  </si>
-  <si>
     <t>1e12 PDF.m2.yr</t>
   </si>
   <si>
@@ -541,6 +532,21 @@
   </si>
   <si>
     <t>ref = SSP2</t>
+  </si>
+  <si>
+    <t>Md m2</t>
+  </si>
+  <si>
+    <t>Md PDF.m2.yr</t>
+  </si>
+  <si>
+    <t>MtCO2e</t>
+  </si>
+  <si>
+    <t>Md m3</t>
+  </si>
+  <si>
+    <t>Part 2050</t>
   </si>
 </sst>
 </file>
@@ -984,23 +990,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1309,39 +1315,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B1" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="50" t="s">
+      <c r="F1" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="G1" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="F1" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="50" t="s">
-        <v>109</v>
-      </c>
       <c r="I1" s="51" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B2" s="43">
         <f>(1.33*10+163.83)/74</f>
@@ -1364,7 +1370,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="44" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B3" s="45">
         <f>(1.33*130+163.83)/74</f>
@@ -1397,7 +1403,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="44" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B4" s="45">
         <f>(1.33*1050+163.83)/74</f>
@@ -1429,10 +1435,10 @@
     </row>
     <row r="5" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="47" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="48" t="s">
         <v>23</v>
@@ -1453,10 +1459,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J5" s="48" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
@@ -1473,7 +1479,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="33" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B7" s="34">
         <v>1E-3</v>
@@ -1505,139 +1511,139 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="23">
-        <f>((Population!C118/100)*B2)*1000</f>
-        <v>16.859561103555574</v>
-      </c>
-      <c r="C8" s="23">
-        <f>(Population!C118/100)*C2</f>
+        <v>118</v>
+      </c>
+      <c r="B8" s="31">
+        <f>((Population!C119/100)*B2)/B7</f>
+        <v>16.859561103555571</v>
+      </c>
+      <c r="C8" s="31">
+        <f>(Population!C119/100)*C2/C7</f>
         <v>7.7478025959996817</v>
       </c>
-      <c r="D8" s="23">
-        <f>((Population!C118/100)*D2)*1000</f>
+      <c r="D8" s="31">
+        <f>((Population!C119/100)*D2)/D7</f>
         <v>74.660643197815105</v>
       </c>
-      <c r="E8" s="23">
-        <f>((Population!C118/100)*E2)*1000</f>
+      <c r="E8" s="31">
+        <f>((Population!C119/100)*E2)/E7</f>
         <v>239.4775347854447</v>
       </c>
-      <c r="F8" s="23">
-        <f>((Population!C118/100)*F2)*1000</f>
+      <c r="F8" s="31">
+        <f>((Population!C119/100)*F2)*1000</f>
         <v>0</v>
       </c>
-      <c r="G8" s="23">
-        <f>(G2*Population!C117)*0.000366668</f>
+      <c r="G8" s="31">
+        <f>(G2*Population!C118)*0.000366668</f>
         <v>0</v>
       </c>
-      <c r="H8" s="23">
-        <f>((Population!C118/100)*H2)*1000</f>
+      <c r="H8" s="31">
+        <f>((Population!C119/100)*H2)*1000</f>
         <v>0</v>
       </c>
-      <c r="I8" s="23">
-        <f>(Population!C118/100)*I2</f>
+      <c r="I8" s="31">
+        <f>(Population!C119/100)*I2</f>
         <v>0</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="31">
         <f>(Population!D116/100)*J2</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="22" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B9" s="31">
-        <f>((Population!C118/100)*B3)/B7</f>
+        <f>((Population!C119/100)*B3)/B7</f>
         <v>32.050584375319076</v>
       </c>
-      <c r="C9" s="23">
-        <f>(Population!C118/100)*C3</f>
+      <c r="C9" s="31">
+        <f>(Population!C119/100)*C3/C7</f>
         <v>19.721679335271915</v>
       </c>
-      <c r="D9" s="23">
-        <f>((Population!C118/100)*D3)*1000</f>
+      <c r="D9" s="31">
+        <f>((Population!C119/100)*D3)/D7</f>
         <v>88.747557008723618</v>
       </c>
-      <c r="E9" s="23">
-        <f>((Population!C118/100)*E3)*1000</f>
+      <c r="E9" s="31">
+        <f>((Population!C119/100)*E3)/E7</f>
         <v>401.47704361089257</v>
       </c>
-      <c r="F9" s="23">
-        <f>((Population!C118/100)*F3)*1000</f>
+      <c r="F9" s="31">
+        <f>((Population!C119/100)*F3)/F7</f>
         <v>31.695556074544147</v>
       </c>
-      <c r="G9" s="23">
-        <f>(G3*Population!C117)*0.000277778</f>
+      <c r="G9" s="31">
+        <f>(G3*Population!C118)*G7</f>
         <v>745.75846513068552</v>
       </c>
-      <c r="H9" s="23">
-        <f>((Population!C118/100)*H3)*1000</f>
-        <v>176.08642263635642</v>
+      <c r="H9" s="31">
+        <f>((Population!C119/100)*H3)/H7</f>
+        <v>176.08642263635639</v>
       </c>
       <c r="I9" s="31">
-        <f>(Population!C118/100)*I3*1000</f>
+        <f>(Population!C119/100)*I3/I7</f>
         <v>45.782469885452663</v>
       </c>
       <c r="J9" s="31">
-        <f>(Population!C118/100)*J3*1000</f>
-        <v>39.372924101489289</v>
+        <f>(Population!C119/100)*J3/J7</f>
+        <v>39.372924101489282</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="23">
-        <f>((Population!C118/100)*B4)*1000</f>
+        <v>119</v>
+      </c>
+      <c r="B10" s="31">
+        <f>((Population!C119/100)*B4)/B7</f>
         <v>148.51509612550592</v>
       </c>
-      <c r="C10" s="23">
-        <f>(Population!C118/100)*C4</f>
+      <c r="C10" s="31">
+        <f>(Population!C119/100)*C4/C7</f>
         <v>31.69555607454415</v>
       </c>
-      <c r="D10" s="23">
-        <f>((Population!C118/100)*D4)*1000</f>
+      <c r="D10" s="31">
+        <f>((Population!C119/100)*D4)/D7</f>
         <v>102.83447081963213</v>
       </c>
-      <c r="E10" s="23">
-        <f>((Population!C118/100)*E4)*1000</f>
+      <c r="E10" s="31">
+        <f>((Population!C119/100)*E4)/E7</f>
         <v>521.21581100361493</v>
       </c>
-      <c r="F10" s="23">
-        <f>((Population!C118/100)*F4)*1000</f>
+      <c r="F10" s="31">
+        <f>((Population!C119/100)*F4)/F7</f>
         <v>63.391112149088293</v>
       </c>
-      <c r="G10" s="23">
-        <f>(G4*Population!C117)*0.000366668</f>
-        <v>1218.0756146062693</v>
-      </c>
-      <c r="H10" s="23">
-        <f>((Population!C118/100)*H4)*1000</f>
-        <v>352.17284527271283</v>
-      </c>
-      <c r="I10" s="23">
-        <f>(Population!C118/100)*I4</f>
+      <c r="G10" s="31">
+        <f>(G4*Population!C118)*G7</f>
+        <v>922.78193917685826</v>
+      </c>
+      <c r="H10" s="31">
+        <f>((Population!C119/100)*H4)/H7</f>
+        <v>352.17284527271278</v>
+      </c>
+      <c r="I10" s="31">
+        <f>(Population!C119/100)*I4</f>
         <v>0</v>
       </c>
-      <c r="J10" s="23">
-        <f>(Population!D118/100)*J4*1000</f>
-        <v>467.33034413233798</v>
+      <c r="J10" s="31">
+        <f>(Population!C119/100)*J4/J7</f>
+        <v>78.745848202978564</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="E11" s="23" t="s">
         <v>29</v>
@@ -1652,15 +1658,15 @@
         <v>24</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="33" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B12" s="34">
         <v>1</v>
@@ -1704,10 +1710,10 @@
     </row>
     <row r="14" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>28</v>
@@ -1728,10 +1734,10 @@
         <v>31</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
@@ -1748,7 +1754,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="33" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B16" s="34">
         <v>1.0000000000000001E-9</v>
@@ -1780,26 +1786,26 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B17" s="11">
-        <f>B2*1000000000/(Population!B117*1000)</f>
+        <f>B2*1000000000/(Population!B118*1000)</f>
         <v>0.24868014132531518</v>
       </c>
       <c r="C17" s="11">
-        <f>C2*1000000000/(Population!B117*1000)</f>
+        <f>C2*1000000000/(Population!B118*1000)</f>
         <v>114.28083048540991</v>
       </c>
       <c r="D17" s="11">
-        <f>D2*1000000000000/(Population!B117*1000)</f>
+        <f>D2*1000000000000/(Population!B118*1000)</f>
         <v>1101.2516392230409</v>
       </c>
       <c r="E17" s="11">
-        <f>E2*1000000000/(Population!B117*1000)</f>
+        <f>E2*1000000000/(Population!B118*1000)</f>
         <v>3.5323165786399424</v>
       </c>
       <c r="F17" s="11">
-        <f>F2*1000000000/(Population!B117*1000)</f>
+        <f>F2*1000000000/(Population!B118*1000)</f>
         <v>0</v>
       </c>
       <c r="G17" s="11">
@@ -1807,11 +1813,11 @@
         <v>0</v>
       </c>
       <c r="H17" s="11">
-        <f>H2*1000000000/(Population!B117*1000)</f>
+        <f>H2*1000000000/(Population!B118*1000)</f>
         <v>0</v>
       </c>
       <c r="I17" s="11">
-        <f>I2*1000000/(Population!B117*1000)</f>
+        <f>I2*1000000/(Population!B118*1000)</f>
         <v>0</v>
       </c>
       <c r="J17" s="11">
@@ -1821,26 +1827,26 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B18" s="11">
-        <f>B3*1000000000/(Population!B117*1000)</f>
+        <f>B3*1000000000/(Population!B118*1000)</f>
         <v>0.47274918979548014</v>
       </c>
       <c r="C18" s="11">
-        <f>C3*1000000000/(Population!B117*1000)</f>
+        <f>C3*1000000000/(Population!B118*1000)</f>
         <v>290.89665941740702</v>
       </c>
       <c r="D18" s="11">
-        <f>D3*1000000000000/(Population!B117*1000)</f>
+        <f>D3*1000000000000/(Population!B118*1000)</f>
         <v>1309.0349673783317</v>
       </c>
       <c r="E18" s="11">
-        <f>E3*1000000000/(Population!B117*1000)</f>
+        <f>E3*1000000000/(Population!B118*1000)</f>
         <v>5.9218248524257859</v>
       </c>
       <c r="F18" s="11">
-        <f>F3*1000000000/(Population!B117*1000)</f>
+        <f>F3*1000000000/(Population!B118*1000)</f>
         <v>0.46751248834940412</v>
       </c>
       <c r="G18" s="11">
@@ -1848,40 +1854,40 @@
         <v>39.6</v>
       </c>
       <c r="H18" s="11">
-        <f>H3*1000000000/(Population!B117*1000)</f>
+        <f>H3*1000000000/(Population!B118*1000)</f>
         <v>2.5972916019411341</v>
       </c>
       <c r="I18" s="32">
-        <f>I3/(Population!B117*1000)*1000000000000</f>
+        <f>I3/(Population!B118*1000)*1000000000000</f>
         <v>675.29581650469493</v>
       </c>
       <c r="J18" s="32">
-        <f>J3/(Population!C117*1000)*1000000000</f>
+        <f>J3/(Population!C118*1000)*1000000000</f>
         <v>82.453035489479262</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B19" s="11">
-        <f>B4*1000000000/(Population!B117*1000)</f>
+        <f>B4*1000000000/(Population!B118*1000)</f>
         <v>2.1906118947334106</v>
       </c>
       <c r="C19" s="11">
-        <f>C4*1000000000/(Population!B117*1000)</f>
+        <f>C4*1000000000/(Population!B118*1000)</f>
         <v>467.51248834940412</v>
       </c>
       <c r="D19" s="11">
-        <f>D4*1000000000000/(Population!B117*1000)</f>
+        <f>D4*1000000000000/(Population!B118*1000)</f>
         <v>1516.8182955336224</v>
       </c>
       <c r="E19" s="11">
-        <f>E4*1000000000/(Population!B117*1000)</f>
+        <f>E4*1000000000/(Population!B118*1000)</f>
         <v>7.6879831417457574</v>
       </c>
       <c r="F19" s="11">
-        <f>F4*1000000000/(Population!B117*1000)</f>
+        <f>F4*1000000000/(Population!B118*1000)</f>
         <v>0.93502497669880824</v>
       </c>
       <c r="G19" s="11">
@@ -1889,24 +1895,24 @@
         <v>49</v>
       </c>
       <c r="H19" s="11">
-        <f>H4*1000000000/(Population!B117*1000)</f>
+        <f>H4*1000000000/(Population!B118*1000)</f>
         <v>5.1945832038822681</v>
       </c>
       <c r="I19" s="11">
-        <f>I4*1000000/(Population!B117*1000)</f>
+        <f>I4*1000000/(Population!B118*1000)</f>
         <v>0</v>
       </c>
       <c r="J19" s="11">
-        <f>J4*1000000000/(Population!C117*1000)</f>
+        <f>J4*1000000000/(Population!C118*1000)</f>
         <v>164.90607097895855</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>34</v>
@@ -1927,15 +1933,15 @@
         <v>32</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J20" s="21" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="33" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B21" s="36">
         <v>9.9999999999999995E-7</v>
@@ -1991,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -2003,19 +2009,19 @@
         <v>11</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>92</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -4273,7 +4279,7 @@
     </row>
     <row r="115" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A115" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B115" s="4">
         <f>AVERAGE(B31:B62)</f>
@@ -4300,7 +4306,7 @@
     </row>
     <row r="116" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A116" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B116" s="5">
         <f>B115/B115</f>
@@ -4323,72 +4329,97 @@
         <v>15.491065655429644</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A117" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B117" s="17">
+        <f>B62*100/B62</f>
+        <v>100</v>
+      </c>
+      <c r="C117" s="17">
+        <f>C62*100/B62</f>
+        <v>0.70588785803326692</v>
+      </c>
+      <c r="D117" s="17">
+        <f>D62*100/B62</f>
+        <v>4.3557414189697248</v>
+      </c>
+      <c r="E117" s="17">
+        <f>E62*100/B62</f>
+        <v>3.9407283828087478</v>
+      </c>
+      <c r="F117" s="17">
+        <f>F62*100/B62</f>
+        <v>13.040560048995525</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A118" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B118" s="4">
         <f>AVERAGE(B31:B112)</f>
         <v>9625411.3251341451</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C118" s="4">
         <f>AVERAGE(C31:C112)</f>
         <v>67796.169865853692</v>
       </c>
-      <c r="D117" s="4">
+      <c r="D118" s="4">
         <f>AVERAGE(D31:D112)</f>
         <v>402347.65536585363</v>
       </c>
-      <c r="E117" s="4">
-        <f t="shared" ref="E117:F117" si="1">AVERAGE(E31:E112)</f>
+      <c r="E118" s="4">
+        <f t="shared" ref="E118:F118" si="1">AVERAGE(E31:E112)</f>
         <v>386346.64082926838</v>
       </c>
-      <c r="F117" s="4">
+      <c r="F118" s="4">
         <f t="shared" si="1"/>
         <v>1101676.6355609756</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A118" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B118" s="5">
-        <f>B117/B117</f>
+    <row r="119" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A119" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B119" s="5">
+        <f>B118/B118</f>
         <v>1</v>
       </c>
-      <c r="C118" s="6">
-        <f>C117*100/B117</f>
+      <c r="C119" s="6">
+        <f>C118*100/B118</f>
         <v>0.70434569054542562</v>
       </c>
-      <c r="D118" s="6">
-        <f>D117*100/B117</f>
+      <c r="D119" s="6">
+        <f>D118*100/B118</f>
         <v>4.1800567453697495</v>
       </c>
-      <c r="E118" s="6">
-        <f>E117*100/B117</f>
+      <c r="E119" s="6">
+        <f>E118*100/B118</f>
         <v>4.0138195426561065</v>
       </c>
-      <c r="F118" s="6">
-        <f>F117*100/B117</f>
+      <c r="F119" s="6">
+        <f>F118*100/B118</f>
         <v>11.445501894389142</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A121" t="s">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
         <v>12</v>
       </c>
-      <c r="B121" s="10" t="s">
+      <c r="B122" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B122" t="s">
-        <v>104</v>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B123" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B121" r:id="rId1" xr:uid="{263EB9F2-B14E-4059-B29E-0D771DC8E530}"/>
+    <hyperlink ref="B122" r:id="rId1" xr:uid="{263EB9F2-B14E-4059-B29E-0D771DC8E530}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4423,10 +4454,10 @@
         <v>18</v>
       </c>
       <c r="E1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
@@ -5866,7 +5897,7 @@
     </row>
     <row r="65" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A65" s="17" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B65" s="17">
         <v>1</v>
@@ -5896,7 +5927,7 @@
     </row>
     <row r="66" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A66" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B66">
         <f>SUM(B2:B31)/SUM(Population!B2:B31)</f>
@@ -5927,7 +5958,7 @@
     </row>
     <row r="67" spans="1:13" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B67" s="17">
         <v>1</v>
@@ -5957,7 +5988,7 @@
     </row>
     <row r="68" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A68" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B68" s="17">
         <f>SUM(B31:B62)/SUM(Population!B31:B62)</f>
@@ -5988,7 +6019,7 @@
     </row>
     <row r="69" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A69" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B69" s="17">
         <v>1</v>
@@ -6019,7 +6050,7 @@
     </row>
     <row r="70" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A70" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B70" s="17">
         <f>SUM(B2:B62)/SUM(Population!B2:B62)</f>
@@ -6050,7 +6081,7 @@
     </row>
     <row r="71" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A71" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B71" s="17">
         <v>1</v>
@@ -6092,7 +6123,7 @@
         <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
@@ -6103,7 +6134,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>17</v>
@@ -6117,10 +6148,10 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H75" s="53"/>
       <c r="I75" s="53"/>
@@ -6131,7 +6162,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H76" s="53"/>
       <c r="I76" s="53"/>
@@ -6568,13 +6599,13 @@
         <v>22</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C1" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -6803,44 +6834,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="73" t="s">
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="72" t="s">
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="73" t="s">
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="L2" s="73"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="74" t="s">
+      <c r="N2" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="O2" s="72" t="s">
+      <c r="O2" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="73" t="s">
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="S2" s="73"/>
+      <c r="S2" s="75"/>
       <c r="T2" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="U2" s="75" t="s">
+      <c r="U2" s="73" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6854,13 +6885,13 @@
       <c r="D3" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="72" t="s">
         <v>80</v>
       </c>
       <c r="H3" s="71" t="s">
@@ -6872,14 +6903,14 @@
       <c r="J3" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="70" t="s">
+      <c r="K3" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="L3" s="70" t="s">
+      <c r="L3" s="72" t="s">
         <v>85</v>
       </c>
       <c r="M3" s="76"/>
-      <c r="N3" s="74"/>
+      <c r="N3" s="70"/>
       <c r="O3" s="71" t="s">
         <v>86</v>
       </c>
@@ -6889,38 +6920,38 @@
       <c r="Q3" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="70" t="s">
+      <c r="R3" s="72" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="70" t="s">
+      <c r="S3" s="72" t="s">
         <v>91</v>
       </c>
       <c r="T3" s="77"/>
-      <c r="U3" s="75"/>
+      <c r="U3" s="73"/>
     </row>
     <row r="4" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="71"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
       <c r="H4" s="71"/>
       <c r="I4" s="71"/>
       <c r="J4" s="71"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
       <c r="M4" s="76"/>
-      <c r="N4" s="74"/>
+      <c r="N4" s="70"/>
       <c r="O4" s="71"/>
       <c r="P4" s="71"/>
       <c r="Q4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="R4" s="70"/>
-      <c r="S4" s="70"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
       <c r="T4" s="77"/>
-      <c r="U4" s="75"/>
+      <c r="U4" s="73"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="17" t="s">
@@ -6995,6 +7026,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -7009,17 +7051,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A250043-D248-4C76-A82D-BA9E85CA36FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84E4C2A-3CB2-496B-8DFC-075920026A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
@@ -990,23 +990,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -6834,44 +6834,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="75" t="s">
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="74" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="75" t="s">
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="73"/>
       <c r="M2" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="70" t="s">
+      <c r="N2" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="O2" s="74" t="s">
+      <c r="O2" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="75" t="s">
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="S2" s="75"/>
+      <c r="S2" s="73"/>
       <c r="T2" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="U2" s="73" t="s">
+      <c r="U2" s="75" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6885,13 +6885,13 @@
       <c r="D3" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="70" t="s">
         <v>80</v>
       </c>
       <c r="H3" s="71" t="s">
@@ -6903,14 +6903,14 @@
       <c r="J3" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="72" t="s">
+      <c r="K3" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="L3" s="72" t="s">
+      <c r="L3" s="70" t="s">
         <v>85</v>
       </c>
       <c r="M3" s="76"/>
-      <c r="N3" s="70"/>
+      <c r="N3" s="74"/>
       <c r="O3" s="71" t="s">
         <v>86</v>
       </c>
@@ -6920,38 +6920,38 @@
       <c r="Q3" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="72" t="s">
+      <c r="R3" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="72" t="s">
+      <c r="S3" s="70" t="s">
         <v>91</v>
       </c>
       <c r="T3" s="77"/>
-      <c r="U3" s="73"/>
+      <c r="U3" s="75"/>
     </row>
     <row r="4" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="71"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
       <c r="H4" s="71"/>
       <c r="I4" s="71"/>
       <c r="J4" s="71"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
       <c r="M4" s="76"/>
-      <c r="N4" s="70"/>
+      <c r="N4" s="74"/>
       <c r="O4" s="71"/>
       <c r="P4" s="71"/>
       <c r="Q4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="70"/>
       <c r="T4" s="77"/>
-      <c r="U4" s="73"/>
+      <c r="U4" s="75"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="17" t="s">
@@ -7026,17 +7026,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -7051,6 +7040,17 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84E4C2A-3CB2-496B-8DFC-075920026A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8180FC1D-0F23-420D-BB82-17E2625E23C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
-    <sheet name="Population" sheetId="2" r:id="rId2"/>
-    <sheet name="Capacité" sheetId="3" r:id="rId3"/>
-    <sheet name="DLS v2" sheetId="10" r:id="rId4"/>
-    <sheet name="DLS" sheetId="5" r:id="rId5"/>
-    <sheet name="DLE" sheetId="7" r:id="rId6"/>
-    <sheet name="Besoins" sheetId="6" r:id="rId7"/>
+    <sheet name="Synthèse agri" sheetId="12" r:id="rId2"/>
+    <sheet name="Population" sheetId="2" r:id="rId3"/>
+    <sheet name="Capacité" sheetId="3" r:id="rId4"/>
+    <sheet name="DLS" sheetId="11" r:id="rId5"/>
+    <sheet name="DLS bis" sheetId="10" r:id="rId6"/>
+    <sheet name="DLE" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,16 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="156">
-  <si>
-    <t>GES</t>
-  </si>
-  <si>
-    <t>Eau</t>
-  </si>
-  <si>
-    <t>Biodiv</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="149">
   <si>
     <t>Unité</t>
   </si>
@@ -66,15 +57,6 @@
     <t>Tg</t>
   </si>
   <si>
-    <t>M MSA-loss.ha</t>
-  </si>
-  <si>
-    <t>Matière</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>GJ/hab.</t>
   </si>
   <si>
@@ -108,9 +90,6 @@
     <t>Moyenne 2019-2100</t>
   </si>
   <si>
-    <t>Sols</t>
-  </si>
-  <si>
     <t>Nom LP</t>
   </si>
   <si>
@@ -168,15 +147,6 @@
     <t>https://www.sciencedirect.com/science/article/pii/S0921800925003027</t>
   </si>
   <si>
-    <t>1000km2</t>
-  </si>
-  <si>
-    <t>GJ/hab/an</t>
-  </si>
-  <si>
-    <t>https://linkinghub.elsevier.com/retrieve/pii/S0959378020307512</t>
-  </si>
-  <si>
     <t>Current system technology (p.hab)</t>
   </si>
   <si>
@@ -186,55 +156,7 @@
     <t>Moyennes mondiales</t>
   </si>
   <si>
-    <t>Moyenne Monde</t>
-  </si>
-  <si>
-    <t>Poids (moyenne scénarios)</t>
-  </si>
-  <si>
-    <t>Poids (Efficient scenario)</t>
-  </si>
-  <si>
-    <t>Poids (Current system technology)</t>
-  </si>
-  <si>
     <t>Nutrition</t>
-  </si>
-  <si>
-    <t>shelter</t>
-  </si>
-  <si>
-    <t>collective services</t>
-  </si>
-  <si>
-    <t>healthcare</t>
-  </si>
-  <si>
-    <t>education</t>
-  </si>
-  <si>
-    <t>clothing</t>
-  </si>
-  <si>
-    <t>agriculture</t>
-  </si>
-  <si>
-    <t>buildings</t>
-  </si>
-  <si>
-    <t>current technology</t>
-  </si>
-  <si>
-    <t>coeff hanafiah</t>
-  </si>
-  <si>
-    <t>1000 MSA.m2</t>
-  </si>
-  <si>
-    <t>0,1 MSA.ha</t>
-  </si>
-  <si>
-    <t>1e-7 M MSA.ha</t>
   </si>
   <si>
     <t>m2/hab.</t>
@@ -270,9 +192,6 @@
     </r>
   </si>
   <si>
-    <t>MSA-loss.ha/hab.</t>
-  </si>
-  <si>
     <t>Shelter &amp; living conditions</t>
   </si>
   <si>
@@ -354,8 +273,233 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>Monde</t>
+  </si>
+  <si>
+    <t>MtCO2eq</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>GtCO2eq</t>
+  </si>
+  <si>
+    <t>tCO2eq</t>
+  </si>
+  <si>
+    <t>medium variant, 1st july</t>
+  </si>
+  <si>
+    <t>GHG emissions</t>
+  </si>
+  <si>
+    <t>N surplus</t>
+  </si>
+  <si>
+    <t>P surplus</t>
+  </si>
+  <si>
+    <t>Raw material consumption</t>
+  </si>
+  <si>
+    <t>Blue water consumption</t>
+  </si>
+  <si>
+    <t>Final energy use</t>
+  </si>
+  <si>
+    <t>Moyenne 2019-2050</t>
+  </si>
+  <si>
+    <t>GDP PPP</t>
+  </si>
+  <si>
+    <t>Projections SSP</t>
+  </si>
+  <si>
+    <t>PDF.m2.yr</t>
+  </si>
+  <si>
+    <t>1e12 PDF.m2.yr</t>
+  </si>
+  <si>
+    <t>Lower safe bound</t>
+  </si>
+  <si>
+    <t>Upper safe bound</t>
+  </si>
+  <si>
+    <t>Safe limit</t>
+  </si>
+  <si>
+    <t>Equality (Lower bound)</t>
+  </si>
+  <si>
+    <t>Equality (Upper bound)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equality </t>
+  </si>
+  <si>
+    <t>PB name</t>
+  </si>
+  <si>
+    <t>Figures unit</t>
+  </si>
+  <si>
+    <t>Unit budget</t>
+  </si>
+  <si>
+    <t>Equality (Lower bound) (p. cap)</t>
+  </si>
+  <si>
+    <t>Equality (p.cap)</t>
+  </si>
+  <si>
+    <t>Equality (Upper bound) (p.cap)</t>
+  </si>
+  <si>
+    <t>Figures unit (p.cap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit Exiobase </t>
+  </si>
+  <si>
+    <t>Unit conversion budget</t>
+  </si>
+  <si>
+    <t>Unit conversion Exiobase</t>
+  </si>
+  <si>
+    <t>Unit conversion budget  (p. cap)</t>
+  </si>
+  <si>
+    <t>Unit conversion Exiobase  (p.cap)</t>
+  </si>
+  <si>
+    <t>GtC</t>
+  </si>
+  <si>
+    <t>MtC</t>
+  </si>
+  <si>
+    <t>tC</t>
+  </si>
+  <si>
+    <t>Biodiversity loss - HANPP</t>
+  </si>
+  <si>
+    <t>Biodiversity loss - PDF</t>
+  </si>
+  <si>
+    <t>Part 2019-2050</t>
+  </si>
+  <si>
+    <t>Part 2019-2100</t>
+  </si>
+  <si>
+    <t>Ratio 2019</t>
+  </si>
+  <si>
+    <t>https://ssp.apps.ece.iiasa.ac.at/basic-elements?type=line-chart&amp;variables=299</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Chine</t>
+  </si>
+  <si>
+    <t>Moyenne 1990-2019</t>
+  </si>
+  <si>
+    <t>Ratio 2019-2050</t>
+  </si>
+  <si>
+    <t>Ratio 1990-2019</t>
+  </si>
+  <si>
+    <t>GDP PPP, per capita, constant 2021 USD</t>
+  </si>
+  <si>
+    <t>Moyenne 1990-2050</t>
+  </si>
+  <si>
+    <t>Ratio 1990-2050</t>
+  </si>
+  <si>
+    <t>ref = SSP2</t>
+  </si>
+  <si>
+    <t>Md m2</t>
+  </si>
+  <si>
+    <t>Md PDF.m2.yr</t>
+  </si>
+  <si>
+    <t>MtCO2e</t>
+  </si>
+  <si>
+    <t>Md m3</t>
+  </si>
+  <si>
+    <t>Part 2050</t>
+  </si>
+  <si>
+    <t>Agricultural land</t>
+  </si>
+  <si>
+    <t>I-SDP-EI</t>
+  </si>
+  <si>
+    <t>I-SSP2</t>
+  </si>
+  <si>
+    <t>I-SDP-MC</t>
+  </si>
+  <si>
+    <t>IDP-RC</t>
+  </si>
+  <si>
+    <t>I-SDP-EI-2020</t>
+  </si>
+  <si>
+    <t>tCO2e/hab/an</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1748-9326/adc3ad#erladc3ads5</t>
+  </si>
+  <si>
+    <t>Source GHG</t>
+  </si>
+  <si>
+    <t>Source autres pressions</t>
+  </si>
+  <si>
+    <t>DLS 2050</t>
+  </si>
+  <si>
+    <t>DLS 2050 lower bound</t>
+  </si>
+  <si>
+    <t>DLS 2050 upper bound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLS </t>
+  </si>
+  <si>
+    <t>DLS lower bound</t>
+  </si>
+  <si>
+    <t>DLS upper bound</t>
+  </si>
+  <si>
+    <t>DLS total</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Moyenne France </t>
+      <t xml:space="preserve">DLS lower bound </t>
     </r>
     <r>
       <rPr>
@@ -365,188 +509,83 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(p.hab)</t>
+      <t>(p.cap)</t>
     </r>
   </si>
   <si>
-    <t>Moyenne France</t>
-  </si>
-  <si>
-    <t>Monde</t>
-  </si>
-  <si>
-    <t>MtCO2eq</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>GtCO2eq</t>
-  </si>
-  <si>
-    <t>tCO2eq</t>
-  </si>
-  <si>
-    <t>medium variant, 1st july</t>
-  </si>
-  <si>
-    <t>GHG emissions</t>
-  </si>
-  <si>
-    <t>Cropland use</t>
-  </si>
-  <si>
-    <t>N surplus</t>
-  </si>
-  <si>
-    <t>P surplus</t>
-  </si>
-  <si>
-    <t>Raw material consumption</t>
-  </si>
-  <si>
-    <t>Blue water consumption</t>
-  </si>
-  <si>
-    <t>Final energy use</t>
-  </si>
-  <si>
-    <t>Moyenne 2019-2050</t>
-  </si>
-  <si>
-    <t>GDP PPP</t>
-  </si>
-  <si>
-    <t>Projections SSP</t>
-  </si>
-  <si>
-    <t>PDF.m2.yr</t>
-  </si>
-  <si>
-    <t>1e12 PDF.m2.yr</t>
-  </si>
-  <si>
-    <t>Lower safe bound</t>
-  </si>
-  <si>
-    <t>Upper safe bound</t>
-  </si>
-  <si>
-    <t>Safe limit</t>
-  </si>
-  <si>
-    <t>Equality (Lower bound)</t>
-  </si>
-  <si>
-    <t>Equality (Upper bound)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equality </t>
-  </si>
-  <si>
-    <t>PB name</t>
-  </si>
-  <si>
-    <t>Figures unit</t>
-  </si>
-  <si>
-    <t>Unit budget</t>
-  </si>
-  <si>
-    <t>Equality (Lower bound) (p. cap)</t>
-  </si>
-  <si>
-    <t>Equality (p.cap)</t>
-  </si>
-  <si>
-    <t>Equality (Upper bound) (p.cap)</t>
-  </si>
-  <si>
-    <t>Figures unit (p.cap)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit Exiobase </t>
-  </si>
-  <si>
-    <t>Unit conversion budget</t>
-  </si>
-  <si>
-    <t>Unit conversion Exiobase</t>
-  </si>
-  <si>
-    <t>Unit conversion budget  (p. cap)</t>
-  </si>
-  <si>
-    <t>Unit conversion Exiobase  (p.cap)</t>
-  </si>
-  <si>
-    <t>GtC</t>
-  </si>
-  <si>
-    <t>MtC</t>
-  </si>
-  <si>
-    <t>tC</t>
-  </si>
-  <si>
-    <t>Biodiversity loss - HANPP</t>
-  </si>
-  <si>
-    <t>Biodiversity loss - PDF</t>
-  </si>
-  <si>
-    <t>Part 2019-2050</t>
-  </si>
-  <si>
-    <t>Part 2019-2100</t>
-  </si>
-  <si>
-    <t>Ratio 2019</t>
-  </si>
-  <si>
-    <t>https://ssp.apps.ece.iiasa.ac.at/basic-elements?type=line-chart&amp;variables=299</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>Chine</t>
-  </si>
-  <si>
-    <t>Moyenne 1990-2019</t>
-  </si>
-  <si>
-    <t>Ratio 2019-2050</t>
-  </si>
-  <si>
-    <t>Ratio 1990-2019</t>
-  </si>
-  <si>
-    <t>GDP PPP, per capita, constant 2021 USD</t>
-  </si>
-  <si>
-    <t>Moyenne 1990-2050</t>
-  </si>
-  <si>
-    <t>Ratio 1990-2050</t>
-  </si>
-  <si>
-    <t>ref = SSP2</t>
-  </si>
-  <si>
-    <t>Md m2</t>
-  </si>
-  <si>
-    <t>Md PDF.m2.yr</t>
-  </si>
-  <si>
-    <t>MtCO2e</t>
-  </si>
-  <si>
-    <t>Md m3</t>
-  </si>
-  <si>
-    <t>Part 2050</t>
+    <r>
+      <t xml:space="preserve">DLS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(p.cap)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DLS upper bound </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(p.cap)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DLS 2050 lower bound </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(p.cap)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DLS 2050 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(p.cap)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DLS 2050 upper bound </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(p.cap)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -663,7 +702,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -751,6 +790,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -851,7 +896,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -871,10 +916,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -975,6 +1016,7 @@
     <xf numFmtId="164" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1014,6 +1056,8 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Lien hypertexte" xfId="3" builtinId="8"/>
@@ -1299,173 +1343,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C32444-97C3-4A7C-A91C-82059EB528AD}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="27" style="17" customWidth="1"/>
-    <col min="2" max="2" width="14.1328125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="14.06640625" style="17" customWidth="1"/>
-    <col min="5" max="6" width="9.19921875" style="17"/>
-    <col min="7" max="7" width="11.3984375" style="17" customWidth="1"/>
-    <col min="8" max="8" width="11.9296875" style="17" customWidth="1"/>
-    <col min="9" max="9" width="13.9296875" style="17" customWidth="1"/>
-    <col min="10" max="10" width="16.06640625" style="17" customWidth="1"/>
-    <col min="11" max="16384" width="9.19921875" style="17"/>
+    <col min="1" max="1" width="27" style="13" customWidth="1"/>
+    <col min="2" max="2" width="14.15234375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="11.69140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="14.07421875" style="13" customWidth="1"/>
+    <col min="5" max="6" width="9.23046875" style="13"/>
+    <col min="7" max="7" width="11.3828125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="11.921875" style="13" customWidth="1"/>
+    <col min="9" max="9" width="13.921875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="16.07421875" style="13" customWidth="1"/>
+    <col min="11" max="16384" width="9.23046875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B1" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>104</v>
-      </c>
-      <c r="E1" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1" s="50" t="s">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="I1" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="J1" s="51" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" s="43">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="39">
         <f>(1.33*10+163.83)/74</f>
         <v>2.3936486486486488</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="39">
         <v>1100</v>
       </c>
-      <c r="D2" s="43">
-        <v>10.6</v>
-      </c>
-      <c r="E2" s="43">
+      <c r="D2" s="39"/>
+      <c r="E2" s="39">
         <v>34</v>
       </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="45">
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="41">
         <f>(1.33*130+163.83)/74</f>
         <v>4.5504054054054057</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="41">
         <v>2800</v>
       </c>
-      <c r="D3" s="45">
-        <v>12.6</v>
-      </c>
-      <c r="E3" s="45">
+      <c r="D3" s="41">
+        <v>43.2</v>
+      </c>
+      <c r="E3" s="41">
         <v>57</v>
       </c>
-      <c r="F3" s="45">
+      <c r="F3" s="41">
         <v>4.5</v>
       </c>
-      <c r="G3" s="45">
+      <c r="G3" s="41">
         <v>39.6</v>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="41">
         <v>25</v>
       </c>
-      <c r="I3" s="46">
+      <c r="I3" s="42">
         <v>6.5</v>
       </c>
-      <c r="J3" s="46">
+      <c r="J3" s="42">
         <v>5.59</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="41">
         <f>(1.33*1050+163.83)/74</f>
         <v>21.085540540540539</v>
       </c>
-      <c r="C4" s="45">
+      <c r="C4" s="41">
         <v>4500</v>
       </c>
-      <c r="D4" s="45">
-        <v>14.6</v>
-      </c>
-      <c r="E4" s="45">
+      <c r="D4" s="41">
+        <v>48</v>
+      </c>
+      <c r="E4" s="41">
         <v>74</v>
       </c>
-      <c r="F4" s="45">
+      <c r="F4" s="41">
         <v>9</v>
       </c>
-      <c r="G4" s="45">
+      <c r="G4" s="41">
         <v>49</v>
       </c>
-      <c r="H4" s="45">
+      <c r="H4" s="41">
         <v>50</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45">
+      <c r="I4" s="41"/>
+      <c r="J4" s="41">
         <f>J3*2</f>
         <v>11.18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="48" t="s">
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="J5" s="48" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="H5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1477,270 +1519,270 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="34">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="30">
         <v>1E-3</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="31">
         <v>1</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="30">
         <v>1E-3</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="30">
         <v>1E-3</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="30">
         <v>1E-3</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="31">
         <v>2.7777800000000001E-4</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="30">
         <v>1E-3</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="30">
         <v>1E-3</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="30">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="31">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="27">
         <f>((Population!C119/100)*B2)/B7</f>
-        <v>16.859561103555571</v>
-      </c>
-      <c r="C8" s="31">
+        <v>17.558864381613638</v>
+      </c>
+      <c r="C8" s="27">
         <f>(Population!C119/100)*C2/C7</f>
-        <v>7.7478025959996817</v>
-      </c>
-      <c r="D8" s="31">
+        <v>8.069167056192347</v>
+      </c>
+      <c r="D8" s="27">
         <f>((Population!C119/100)*D2)/D7</f>
-        <v>74.660643197815105</v>
-      </c>
-      <c r="E8" s="31">
+        <v>0</v>
+      </c>
+      <c r="E8" s="27">
         <f>((Population!C119/100)*E2)/E7</f>
-        <v>239.4775347854447</v>
-      </c>
-      <c r="F8" s="31">
+        <v>249.41061810049069</v>
+      </c>
+      <c r="F8" s="27">
         <f>((Population!C119/100)*F2)*1000</f>
         <v>0</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="27">
         <f>(G2*Population!C118)*0.000366668</f>
         <v>0</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="27">
         <f>((Population!C119/100)*H2)*1000</f>
         <v>0</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="27">
         <f>(Population!C119/100)*I2</f>
         <v>0</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="27">
         <f>(Population!D116/100)*J2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="31">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="27">
         <f>((Population!C119/100)*B3)/B7</f>
-        <v>32.050584375319076</v>
-      </c>
-      <c r="C9" s="31">
+        <v>33.379983081469888</v>
+      </c>
+      <c r="C9" s="27">
         <f>(Population!C119/100)*C3/C7</f>
-        <v>19.721679335271915</v>
-      </c>
-      <c r="D9" s="31">
+        <v>20.539697961216881</v>
+      </c>
+      <c r="D9" s="27">
         <f>((Population!C119/100)*D3)/D7</f>
-        <v>88.747557008723618</v>
-      </c>
-      <c r="E9" s="31">
+        <v>316.89819711591764</v>
+      </c>
+      <c r="E9" s="27">
         <f>((Population!C119/100)*E3)/E7</f>
-        <v>401.47704361089257</v>
-      </c>
-      <c r="F9" s="31">
+        <v>418.12956563905794</v>
+      </c>
+      <c r="F9" s="27">
         <f>((Population!C119/100)*F3)/F7</f>
-        <v>31.695556074544147</v>
-      </c>
-      <c r="G9" s="31">
+        <v>33.010228866241413</v>
+      </c>
+      <c r="G9" s="27">
         <f>(G3*Population!C118)*G7</f>
-        <v>745.75846513068552</v>
-      </c>
-      <c r="H9" s="31">
+        <v>776.69114102314745</v>
+      </c>
+      <c r="H9" s="27">
         <f>((Population!C119/100)*H3)/H7</f>
-        <v>176.08642263635639</v>
-      </c>
-      <c r="I9" s="31">
+        <v>183.39016036800786</v>
+      </c>
+      <c r="I9" s="27">
         <f>(Population!C119/100)*I3/I7</f>
-        <v>45.782469885452663</v>
-      </c>
-      <c r="J9" s="31">
+        <v>47.681441695682047</v>
+      </c>
+      <c r="J9" s="27">
         <f>(Population!C119/100)*J3/J7</f>
-        <v>39.372924101489282</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="31">
+        <v>41.006039858286563</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="27">
         <f>((Population!C119/100)*B4)/B7</f>
-        <v>148.51509612550592</v>
-      </c>
-      <c r="C10" s="31">
+        <v>154.67522644703445</v>
+      </c>
+      <c r="C10" s="27">
         <f>(Population!C119/100)*C4/C7</f>
-        <v>31.69555607454415</v>
-      </c>
-      <c r="D10" s="31">
+        <v>33.01022886624142</v>
+      </c>
+      <c r="D10" s="27">
         <f>((Population!C119/100)*D4)/D7</f>
-        <v>102.83447081963213</v>
-      </c>
-      <c r="E10" s="31">
+        <v>352.1091079065751</v>
+      </c>
+      <c r="E10" s="27">
         <f>((Population!C119/100)*E4)/E7</f>
-        <v>521.21581100361493</v>
-      </c>
-      <c r="F10" s="31">
+        <v>542.83487468930332</v>
+      </c>
+      <c r="F10" s="27">
         <f>((Population!C119/100)*F4)/F7</f>
-        <v>63.391112149088293</v>
-      </c>
-      <c r="G10" s="31">
+        <v>66.020457732482825</v>
+      </c>
+      <c r="G10" s="27">
         <f>(G4*Population!C118)*G7</f>
-        <v>922.78193917685826</v>
-      </c>
-      <c r="H10" s="31">
+        <v>961.05721995288445</v>
+      </c>
+      <c r="H10" s="27">
         <f>((Population!C119/100)*H4)/H7</f>
-        <v>352.17284527271278</v>
-      </c>
-      <c r="I10" s="31">
+        <v>366.78032073601571</v>
+      </c>
+      <c r="I10" s="27">
         <f>(Population!C119/100)*I4</f>
         <v>0</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="27">
         <f>(Population!C119/100)*J4/J7</f>
-        <v>78.745848202978564</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="22" t="s">
+        <v>82.012079716573126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="34">
+      <c r="J11" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="30">
         <v>1</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="30">
         <v>1000</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="30">
         <v>1000</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="30">
         <v>1E-3</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="30">
         <v>1E-3</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="31">
         <f>1/0.000277778</f>
         <v>3599.9971200023037</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="30">
         <v>1000</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="30">
         <v>1000000000</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="30">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="41" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="38" t="s">
+    <row r="13" spans="1:10" s="37" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="38" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B14" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1752,41 +1794,41 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="34">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="30">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="30">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="30">
         <v>9.9999999999999998E-13</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="30">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="30">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="30">
         <v>1</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="30">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="30">
         <v>9.9999999999999998E-13</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="30">
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" s="19" t="s">
-        <v>124</v>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="15" t="s">
+        <v>94</v>
       </c>
       <c r="B17" s="11">
         <f>B2*1000000000/(Population!B118*1000)</f>
@@ -1798,7 +1840,7 @@
       </c>
       <c r="D17" s="11">
         <f>D2*1000000000000/(Population!B118*1000)</f>
-        <v>1101.2516392230409</v>
+        <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>E2*1000000000/(Population!B118*1000)</f>
@@ -1825,9 +1867,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" s="19" t="s">
-        <v>125</v>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="B18" s="11">
         <f>B3*1000000000/(Population!B118*1000)</f>
@@ -1839,7 +1881,7 @@
       </c>
       <c r="D18" s="11">
         <f>D3*1000000000000/(Population!B118*1000)</f>
-        <v>1309.0349673783317</v>
+        <v>4488.1198881542796</v>
       </c>
       <c r="E18" s="11">
         <f>E3*1000000000/(Population!B118*1000)</f>
@@ -1857,18 +1899,18 @@
         <f>H3*1000000000/(Population!B118*1000)</f>
         <v>2.5972916019411341</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="28">
         <f>I3/(Population!B118*1000)*1000000000000</f>
         <v>675.29581650469493</v>
       </c>
-      <c r="J18" s="32">
+      <c r="J18" s="28">
         <f>J3/(Population!C118*1000)*1000000000</f>
-        <v>82.453035489479262</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" s="19" t="s">
-        <v>126</v>
+        <v>79.16924237219726</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="15" t="s">
+        <v>96</v>
       </c>
       <c r="B19" s="11">
         <f>B4*1000000000/(Population!B118*1000)</f>
@@ -1880,7 +1922,7 @@
       </c>
       <c r="D19" s="11">
         <f>D4*1000000000000/(Population!B118*1000)</f>
-        <v>1516.8182955336224</v>
+        <v>4986.7998757269779</v>
       </c>
       <c r="E19" s="11">
         <f>E4*1000000000/(Population!B118*1000)</f>
@@ -1904,74 +1946,74 @@
       </c>
       <c r="J19" s="11">
         <f>J4*1000000000/(Population!C118*1000)</f>
-        <v>164.90607097895855</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="21" t="s">
+        <v>158.33848474439455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="36">
+      <c r="H20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="32">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="32">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="32">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="32">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="32">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="32">
         <v>1E-3</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="32">
         <v>1E-3</v>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="32">
         <v>1</v>
       </c>
-      <c r="J21" s="36">
+      <c r="J21" s="32">
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1983,10 +2025,10 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="8"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="8"/>
     </row>
   </sheetData>
@@ -1996,35 +2038,523 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
-  <dimension ref="A1:H123"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763A0529-0113-40C2-8132-A760C1078623}">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" customWidth="1"/>
-    <col min="2" max="2" width="12.86328125" customWidth="1"/>
+    <col min="1" max="1" width="27" style="13" customWidth="1"/>
+    <col min="2" max="2" width="14.15234375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="11.69140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="14.07421875" style="13" customWidth="1"/>
+    <col min="5" max="6" width="9.23046875" style="13"/>
+    <col min="7" max="7" width="16.07421875" style="13" customWidth="1"/>
+    <col min="8" max="16384" width="9.23046875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="41">
+        <v>5</v>
+      </c>
+      <c r="C3" s="41">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="41">
+        <v>48</v>
+      </c>
+      <c r="E3" s="41">
+        <v>57</v>
+      </c>
+      <c r="F3" s="41">
+        <v>4.5</v>
+      </c>
+      <c r="G3" s="42">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="44" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="C7" s="31">
+        <v>1</v>
+      </c>
+      <c r="D7" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="E7" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="F7" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="G7" s="30">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="27">
+        <f>((Population!C119/100)*B2)/B7</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="27">
+        <f>(Population!C119/100)*C2/C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="27">
+        <f>((Population!C119/100)*D2)/D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="27">
+        <f>((Population!C119/100)*E2)/E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="27">
+        <f>((Population!C119/100)*F2)*1000</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="27">
+        <f>(Population!D116/100)*G2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="27">
+        <f>((Population!C119/100)*B3)/B7</f>
+        <v>36.678032073601578</v>
+      </c>
+      <c r="C9" s="27">
+        <f>(Population!C119/100)*C3/C7</f>
+        <v>14.671212829440631</v>
+      </c>
+      <c r="D9" s="27">
+        <f>((Population!C119/100)*D3)/D7</f>
+        <v>352.1091079065751</v>
+      </c>
+      <c r="E9" s="27">
+        <f>((Population!C119/100)*E3)/E7</f>
+        <v>418.12956563905794</v>
+      </c>
+      <c r="F9" s="27">
+        <f>((Population!C119/100)*F3)/F7</f>
+        <v>33.010228866241413</v>
+      </c>
+      <c r="G9" s="27">
+        <f>(Population!C119/100)*G3/G7</f>
+        <v>40.345835280961737</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="27">
+        <f>((Population!C119/100)*B4)/B7</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="27">
+        <f>(Population!C119/100)*C4/C7</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="27">
+        <f>((Population!C119/100)*D4)/D7</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="27">
+        <f>((Population!C119/100)*E4)/E7</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="27">
+        <f>((Population!C119/100)*F4)/F7</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="27">
+        <f>(Population!C119/100)*G4/G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="30">
+        <v>1</v>
+      </c>
+      <c r="C12" s="30">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="30">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="F12" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="G12" s="30">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="37" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="C16" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="D16" s="30">
+        <v>9.9999999999999998E-13</v>
+      </c>
+      <c r="E16" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F16" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="G16" s="30">
+        <v>1.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="11">
+        <f>B2*1000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="11">
+        <f>C2*1000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="11">
+        <f>D2*1000000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="11">
+        <f>E2*1000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="11">
+        <f>F2*1000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="11">
+        <f>G2*1000000/(Population!C115*1000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="11">
+        <f>B3*1000000000/(Population!B118*1000)</f>
+        <v>0.51945832038822681</v>
+      </c>
+      <c r="C18" s="11">
+        <f>C3*1000000000/(Population!B118*1000)</f>
+        <v>207.78332815529072</v>
+      </c>
+      <c r="D18" s="11">
+        <f>D3*1000000000000/(Population!B118*1000)</f>
+        <v>4986.7998757269779</v>
+      </c>
+      <c r="E18" s="11">
+        <f>E3*1000000000/(Population!B118*1000)</f>
+        <v>5.9218248524257859</v>
+      </c>
+      <c r="F18" s="11">
+        <f>F3*1000000000/(Population!B118*1000)</f>
+        <v>0.46751248834940412</v>
+      </c>
+      <c r="G18" s="28">
+        <f>G3/(Population!C118*1000)*1000000000</f>
+        <v>77.894603407349734</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="11">
+        <f>B4*1000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="11">
+        <f>C4*1000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="11">
+        <f>D4*1000000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <f>E4*1000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="11">
+        <f>F4*1000000000/(Population!B118*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="11">
+        <f>G4*1000000000/(Population!C118*1000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B20" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="32">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C21" s="32">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="D21" s="32">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E21" s="32">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F21" s="32">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="G21" s="32">
+        <v>1.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="8"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
+  <dimension ref="A1:F123"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.3828125" customWidth="1"/>
+    <col min="2" max="2" width="12.84375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -2032,7 +2562,7 @@
         <v>5327803.1100000003</v>
       </c>
       <c r="C2" s="2">
-        <v>56990.237999999998</v>
+        <v>58604.902000000002</v>
       </c>
       <c r="D2" s="2">
         <v>419997.47</v>
@@ -2044,7 +2574,7 @@
         <v>1153582.7239999999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -2052,7 +2582,7 @@
         <v>5418735.8909999998</v>
       </c>
       <c r="C3" s="2">
-        <v>57271.565000000002</v>
+        <v>58919.182000000001</v>
       </c>
       <c r="D3" s="2">
         <v>421419.174</v>
@@ -2064,7 +2594,7 @@
         <v>1170788.5279999999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -2072,7 +2602,7 @@
         <v>5505989.8159999996</v>
       </c>
       <c r="C4" s="2">
-        <v>57554.87</v>
+        <v>59235.822</v>
       </c>
       <c r="D4" s="2">
         <v>422863.59999999992</v>
@@ -2084,7 +2614,7 @@
         <v>1184574.237</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -2092,7 +2622,7 @@
         <v>5591544.7970000003</v>
       </c>
       <c r="C5" s="2">
-        <v>57801.266000000003</v>
+        <v>59515.843000000001</v>
       </c>
       <c r="D5" s="2">
         <v>424104.70499999996</v>
@@ -2104,7 +2634,7 @@
         <v>1197308.575</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -2112,7 +2642,7 @@
         <v>5675551.2549999999</v>
       </c>
       <c r="C6" s="2">
-        <v>57999.866000000002</v>
+        <v>59747.877</v>
       </c>
       <c r="D6" s="2">
         <v>425188.98800000019</v>
@@ -2124,7 +2654,7 @@
         <v>1209003.0959999999</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -2132,7 +2662,7 @@
         <v>5758878.9819999998</v>
       </c>
       <c r="C7" s="2">
-        <v>58192.203000000001</v>
+        <v>59973.548000000003</v>
       </c>
       <c r="D7" s="2">
         <v>425847.82800000004</v>
@@ -2144,7 +2674,7 @@
         <v>1220133.9269999999</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -2152,7 +2682,7 @@
         <v>5842055.7340000002</v>
       </c>
       <c r="C8" s="2">
-        <v>58380.641000000003</v>
+        <v>60195.175999999999</v>
       </c>
       <c r="D8" s="2">
         <v>426181.87299999996</v>
@@ -2164,7 +2694,7 @@
         <v>1230944.8119999999</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -2172,7 +2702,7 @@
         <v>5924787.8159999996</v>
       </c>
       <c r="C9" s="2">
-        <v>58568.66</v>
+        <v>60416.197999999997</v>
       </c>
       <c r="D9" s="2">
         <v>426651.66799999989</v>
@@ -2184,7 +2714,7 @@
         <v>1241139.622</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -2192,7 +2722,7 @@
         <v>6007066.6900000004</v>
       </c>
       <c r="C10" s="2">
-        <v>58778.815999999999</v>
+        <v>60657.506999999998</v>
       </c>
       <c r="D10" s="2">
         <v>426655.42999999993</v>
@@ -2204,7 +2734,7 @@
         <v>1250847.1270000001</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -2212,7 +2742,7 @@
         <v>6089006.3389999997</v>
       </c>
       <c r="C11" s="2">
-        <v>59084.21</v>
+        <v>60987.091</v>
       </c>
       <c r="D11" s="2">
         <v>426830.63099999999</v>
@@ -2224,7 +2754,7 @@
         <v>1260176.655</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -2232,7 +2762,7 @@
         <v>6171702.9929999998</v>
       </c>
       <c r="C12" s="2">
-        <v>59483.716999999997</v>
+        <v>61404.917999999998</v>
       </c>
       <c r="D12" s="2">
         <v>427627.31800000009</v>
@@ -2244,7 +2774,7 @@
         <v>1269581.175</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -2252,7 +2782,7 @@
         <v>6254936.4589999998</v>
       </c>
       <c r="C13" s="2">
-        <v>59905.127999999997</v>
+        <v>61843.576000000001</v>
       </c>
       <c r="D13" s="2">
         <v>428578.28599999996</v>
@@ -2264,7 +2794,7 @@
         <v>1278725.0630000001</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -2272,7 +2802,7 @@
         <v>6337730.3420000002</v>
       </c>
       <c r="C14" s="2">
-        <v>60327.248</v>
+        <v>62281.563000000002</v>
       </c>
       <c r="D14" s="2">
         <v>429890.46400000004</v>
@@ -2284,7 +2814,7 @@
         <v>1286866.8389999999</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -2292,7 +2822,7 @@
         <v>6420361.6339999996</v>
       </c>
       <c r="C15" s="2">
-        <v>60741.125999999997</v>
+        <v>62710.292000000001</v>
       </c>
       <c r="D15" s="2">
         <v>431461.80999999994</v>
@@ -2304,7 +2834,7 @@
         <v>1294517.3259999999</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -2312,7 +2842,7 @@
         <v>6503377.7719999999</v>
       </c>
       <c r="C16" s="2">
-        <v>61175.247000000003</v>
+        <v>63156.877999999997</v>
       </c>
       <c r="D16" s="2">
         <v>433058.58899999998</v>
@@ -2324,7 +2854,7 @@
         <v>1302100.3160000001</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -2332,7 +2862,7 @@
         <v>6586970.1320000002</v>
       </c>
       <c r="C17" s="2">
-        <v>61625.031999999999</v>
+        <v>63617.228000000003</v>
       </c>
       <c r="D17" s="2">
         <v>434557.12100000004</v>
@@ -2344,7 +2874,7 @@
         <v>1310027.1359999999</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -2352,7 +2882,7 @@
         <v>6671452.0149999997</v>
       </c>
       <c r="C18" s="2">
-        <v>62049.838000000003</v>
+        <v>64060.148999999998</v>
       </c>
       <c r="D18" s="2">
         <v>435683.11500000011</v>
@@ -2364,7 +2894,7 @@
         <v>1318054.0360000001</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -2372,7 +2902,7 @@
         <v>6757308.7810000004</v>
       </c>
       <c r="C19" s="2">
-        <v>62432.438999999998</v>
+        <v>64470.141000000003</v>
       </c>
       <c r="D19" s="2">
         <v>436994.47300000006</v>
@@ -2384,7 +2914,7 @@
         <v>1325813.5819999999</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -2392,7 +2922,7 @@
         <v>6844457.6619999995</v>
       </c>
       <c r="C20" s="2">
-        <v>62780.19</v>
+        <v>64842.856</v>
       </c>
       <c r="D20" s="2">
         <v>438548.18900000007</v>
@@ -2404,7 +2934,7 @@
         <v>1333821.0160000001</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -2412,7 +2942,7 @@
         <v>6932766.4160000002</v>
       </c>
       <c r="C21" s="2">
-        <v>63106.463000000003</v>
+        <v>65186.042000000001</v>
       </c>
       <c r="D21" s="2">
         <v>439690.78899999993</v>
@@ -2424,7 +2954,7 @@
         <v>1342522.716</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -2432,7 +2962,7 @@
         <v>7021732.148</v>
       </c>
       <c r="C22" s="2">
-        <v>63417.362999999998</v>
+        <v>65510.017</v>
       </c>
       <c r="D22" s="2">
         <v>440608.95100000006</v>
@@ -2444,7 +2974,7 @@
         <v>1351561.514</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -2452,7 +2982,7 @@
         <v>7110923.7649999997</v>
       </c>
       <c r="C23" s="2">
-        <v>63733.777000000002</v>
+        <v>65836.675000000003</v>
       </c>
       <c r="D23" s="2">
         <v>441440.62800000008</v>
@@ -2464,7 +2994,7 @@
         <v>1360250.6640000001</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -2472,7 +3002,7 @@
         <v>7201202.4850000003</v>
       </c>
       <c r="C24" s="2">
-        <v>64058.464999999997</v>
+        <v>66169.17</v>
       </c>
       <c r="D24" s="2">
         <v>441999.21399999998</v>
@@ -2484,7 +3014,7 @@
         <v>1369520.8640000001</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -2492,7 +3022,7 @@
         <v>7291793.585</v>
       </c>
       <c r="C25" s="2">
-        <v>64387.733999999997</v>
+        <v>66513.020999999993</v>
       </c>
       <c r="D25" s="2">
         <v>442399.391</v>
@@ -2504,7 +3034,7 @@
         <v>1379008.04</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -2512,7 +3042,7 @@
         <v>7381616.2439999999</v>
       </c>
       <c r="C26" s="2">
-        <v>64692.493000000002</v>
+        <v>66841.142000000007</v>
       </c>
       <c r="D26" s="2">
         <v>442964.72000000003</v>
@@ -2524,7 +3054,7 @@
         <v>1387951.9720000001</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -2532,7 +3062,7 @@
         <v>7470491.8720000004</v>
       </c>
       <c r="C27" s="2">
-        <v>64916.336000000003</v>
+        <v>67080.971000000005</v>
       </c>
       <c r="D27" s="2">
         <v>443910.90800000017</v>
@@ -2544,7 +3074,7 @@
         <v>1396134.1740000001</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -2552,7 +3082,7 @@
         <v>7558554.5259999996</v>
       </c>
       <c r="C28" s="2">
-        <v>65086.855000000003</v>
+        <v>67260.373000000007</v>
       </c>
       <c r="D28" s="2">
         <v>444911.48800000001</v>
@@ -2564,7 +3094,7 @@
         <v>1404052.632</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2572,7 +3102,7 @@
         <v>7645617.9539999999</v>
       </c>
       <c r="C29" s="2">
-        <v>65284.775999999998</v>
+        <v>67469.032000000007</v>
       </c>
       <c r="D29" s="2">
         <v>445696.74599999998</v>
@@ -2584,7 +3114,7 @@
         <v>1412354.727</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2592,7 +3122,7 @@
         <v>7729902.7810000004</v>
       </c>
       <c r="C30" s="2">
-        <v>65519.542999999998</v>
+        <v>67706.406000000003</v>
       </c>
       <c r="D30" s="2">
         <v>446503.6480000001</v>
@@ -2604,7 +3134,7 @@
         <v>1419008.956</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2612,7 +3142,7 @@
         <v>7811293.6979999999</v>
       </c>
       <c r="C31" s="2">
-        <v>65729.459000000003</v>
+        <v>67917.133000000002</v>
       </c>
       <c r="D31" s="2">
         <v>447369.19099999999</v>
@@ -2624,7 +3154,7 @@
         <v>1423520.3570000001</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2632,7 +3162,7 @@
         <v>7887001.2920000004</v>
       </c>
       <c r="C32" s="2">
-        <v>65905.277000000002</v>
+        <v>68104.157000000007</v>
       </c>
       <c r="D32" s="2">
         <v>447777.53599999996</v>
@@ -2644,7 +3174,7 @@
         <v>1426106.0930000001</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2652,7 +3182,7 @@
         <v>7954448.3909999998</v>
       </c>
       <c r="C33" s="2">
-        <v>66083.547999999995</v>
+        <v>68291.491999999998</v>
       </c>
       <c r="D33" s="2">
         <v>447705.902</v>
@@ -2664,7 +3194,7 @@
         <v>1426437.267</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2672,7 +3202,7 @@
         <v>8021407.1919999998</v>
       </c>
       <c r="C34" s="2">
-        <v>66277.409</v>
+        <v>68486.679999999993</v>
       </c>
       <c r="D34" s="2">
         <v>449113.45499999996</v>
@@ -2684,7 +3214,7 @@
         <v>1425179.5689999999</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2692,7 +3222,7 @@
         <v>8091734.9299999997</v>
       </c>
       <c r="C35" s="2">
-        <v>66438.822</v>
+        <v>68655.641000000003</v>
       </c>
       <c r="D35" s="2">
         <v>450657.52199999994</v>
@@ -2704,7 +3234,7 @@
         <v>1422584.933</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2712,7 +3242,7 @@
         <v>8161972.5719999997</v>
       </c>
       <c r="C36" s="2">
-        <v>66548.53</v>
+        <v>68780.448999999993</v>
       </c>
       <c r="D36" s="2">
         <v>450259.53600000002</v>
@@ -2724,7 +3254,7 @@
         <v>1419321.2779999999</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -2732,7 +3262,7 @@
         <v>8231613.0700000003</v>
       </c>
       <c r="C37" s="2">
-        <v>66650.804000000004</v>
+        <v>68898.115999999995</v>
       </c>
       <c r="D37" s="2">
         <v>448992.58499999996</v>
@@ -2744,1515 +3274,1515 @@
         <v>1416096.094</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A38" s="63">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A38" s="59">
         <v>2026</v>
       </c>
-      <c r="B38" s="64">
+      <c r="B38" s="60">
         <v>8300678.3949999996</v>
       </c>
-      <c r="C38" s="64">
-        <v>66746.400999999998</v>
-      </c>
-      <c r="D38" s="64">
+      <c r="C38" s="60">
+        <v>69009.270999999993</v>
+      </c>
+      <c r="D38" s="60">
         <v>447890.473</v>
       </c>
-      <c r="E38" s="64">
+      <c r="E38" s="60">
         <v>349035.49400000001</v>
       </c>
-      <c r="F38" s="64">
+      <c r="F38" s="60">
         <v>1412914.0889999999</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A39" s="63">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A39" s="59">
         <v>2027</v>
       </c>
-      <c r="B39" s="64">
+      <c r="B39" s="60">
         <v>8369094.3439999996</v>
       </c>
-      <c r="C39" s="64">
-        <v>66838.260999999999</v>
-      </c>
-      <c r="D39" s="64">
+      <c r="C39" s="60">
+        <v>69116.986999999994</v>
+      </c>
+      <c r="D39" s="60">
         <v>447205.74899999995</v>
       </c>
-      <c r="E39" s="64">
+      <c r="E39" s="60">
         <v>350728.35499999998</v>
       </c>
-      <c r="F39" s="64">
+      <c r="F39" s="60">
         <v>1409679.406</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A40" s="63">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A40" s="59">
         <v>2028</v>
       </c>
-      <c r="B40" s="64">
+      <c r="B40" s="60">
         <v>8436618.8859999999</v>
       </c>
-      <c r="C40" s="64">
-        <v>66928.635999999999</v>
-      </c>
-      <c r="D40" s="64">
+      <c r="C40" s="60">
+        <v>69223.342000000004</v>
+      </c>
+      <c r="D40" s="60">
         <v>446459.31699999998</v>
       </c>
-      <c r="E40" s="64">
+      <c r="E40" s="60">
         <v>352404.08500000002</v>
       </c>
-      <c r="F40" s="64">
+      <c r="F40" s="60">
         <v>1406136.7439999999</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A41" s="63">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A41" s="59">
         <v>2029</v>
       </c>
-      <c r="B41" s="64">
+      <c r="B41" s="60">
         <v>8503285.3230000008</v>
       </c>
-      <c r="C41" s="64">
-        <v>67018.328999999998</v>
-      </c>
-      <c r="D41" s="64">
+      <c r="C41" s="60">
+        <v>69329.116999999998</v>
+      </c>
+      <c r="D41" s="60">
         <v>445651.23500000004</v>
       </c>
-      <c r="E41" s="64">
+      <c r="E41" s="60">
         <v>354050.26799999998</v>
       </c>
-      <c r="F41" s="64">
+      <c r="F41" s="60">
         <v>1402282.7520000001</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A42" s="63">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A42" s="59">
         <v>2030</v>
       </c>
-      <c r="B42" s="64">
+      <c r="B42" s="60">
         <v>8569124.9110000003</v>
       </c>
-      <c r="C42" s="64">
-        <v>67107.691000000006</v>
-      </c>
-      <c r="D42" s="64">
+      <c r="C42" s="60">
+        <v>69434.807000000001</v>
+      </c>
+      <c r="D42" s="60">
         <v>444782.38100000005</v>
       </c>
-      <c r="E42" s="64">
+      <c r="E42" s="60">
         <v>355649.88099999999</v>
       </c>
-      <c r="F42" s="64">
+      <c r="F42" s="60">
         <v>1398153.8319999999</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A43" s="63">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A43" s="59">
         <v>2031</v>
       </c>
-      <c r="B43" s="64">
+      <c r="B43" s="60">
         <v>8634119.3330000006</v>
       </c>
-      <c r="C43" s="64">
-        <v>67194.854999999996</v>
-      </c>
-      <c r="D43" s="64">
+      <c r="C43" s="60">
+        <v>69538.657000000007</v>
+      </c>
+      <c r="D43" s="60">
         <v>443853.3349999999</v>
       </c>
-      <c r="E43" s="64">
+      <c r="E43" s="60">
         <v>357222.71500000003</v>
       </c>
-      <c r="F43" s="64">
+      <c r="F43" s="60">
         <v>1393748.67</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A44" s="63">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A44" s="59">
         <v>2032</v>
       </c>
-      <c r="B44" s="64">
+      <c r="B44" s="60">
         <v>8698229.8120000008</v>
       </c>
-      <c r="C44" s="64">
-        <v>67281.98</v>
-      </c>
-      <c r="D44" s="64">
+      <c r="C44" s="60">
+        <v>69642.721000000005</v>
+      </c>
+      <c r="D44" s="60">
         <v>442896.55800000002</v>
       </c>
-      <c r="E44" s="64">
+      <c r="E44" s="60">
         <v>358769.97399999999</v>
       </c>
-      <c r="F44" s="64">
+      <c r="F44" s="60">
         <v>1389060.0319999999</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A45" s="63">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A45" s="59">
         <v>2033</v>
       </c>
-      <c r="B45" s="64">
+      <c r="B45" s="60">
         <v>8761449.0810000002</v>
       </c>
-      <c r="C45" s="64">
-        <v>67369.322</v>
-      </c>
-      <c r="D45" s="64">
+      <c r="C45" s="60">
+        <v>69747.017000000007</v>
+      </c>
+      <c r="D45" s="60">
         <v>441929.64600000007</v>
       </c>
-      <c r="E45" s="64">
+      <c r="E45" s="60">
         <v>360294.00799999997</v>
       </c>
-      <c r="F45" s="64">
+      <c r="F45" s="60">
         <v>1384096.5209999999</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A46" s="63">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A46" s="59">
         <v>2034</v>
       </c>
-      <c r="B46" s="64">
+      <c r="B46" s="60">
         <v>8823784.909</v>
       </c>
-      <c r="C46" s="64">
-        <v>67458.149000000005</v>
-      </c>
-      <c r="D46" s="64">
+      <c r="C46" s="60">
+        <v>69852.736999999994</v>
+      </c>
+      <c r="D46" s="60">
         <v>440942.37400000007</v>
       </c>
-      <c r="E46" s="64">
+      <c r="E46" s="60">
         <v>361801.81099999999</v>
       </c>
-      <c r="F46" s="64">
+      <c r="F46" s="60">
         <v>1378876.9339999999</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A47" s="63">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A47" s="59">
         <v>2035</v>
       </c>
-      <c r="B47" s="64">
+      <c r="B47" s="60">
         <v>8885210.1809999999</v>
       </c>
-      <c r="C47" s="64">
-        <v>67547.945999999996</v>
-      </c>
-      <c r="D47" s="64">
+      <c r="C47" s="60">
+        <v>69959.539000000004</v>
+      </c>
+      <c r="D47" s="60">
         <v>439928.23599999998</v>
       </c>
-      <c r="E47" s="64">
+      <c r="E47" s="60">
         <v>363284.71600000001</v>
       </c>
-      <c r="F47" s="64">
+      <c r="F47" s="60">
         <v>1373427.531</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A48" s="63">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A48" s="59">
         <v>2036</v>
       </c>
-      <c r="B48" s="64">
+      <c r="B48" s="60">
         <v>8945686.6140000001</v>
       </c>
-      <c r="C48" s="64">
-        <v>67635.315000000002</v>
-      </c>
-      <c r="D48" s="64">
+      <c r="C48" s="60">
+        <v>70064.307000000001</v>
+      </c>
+      <c r="D48" s="60">
         <v>438876.35599999991</v>
       </c>
-      <c r="E48" s="64">
+      <c r="E48" s="60">
         <v>364731.66</v>
       </c>
-      <c r="F48" s="64">
+      <c r="F48" s="60">
         <v>1367742.7849999999</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A49" s="63">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A49" s="59">
         <v>2037</v>
       </c>
-      <c r="B49" s="64">
+      <c r="B49" s="60">
         <v>9005152.6239999998</v>
       </c>
-      <c r="C49" s="64">
-        <v>67721.11</v>
-      </c>
-      <c r="D49" s="64">
+      <c r="C49" s="60">
+        <v>70167.604999999996</v>
+      </c>
+      <c r="D49" s="60">
         <v>437800.28700000013</v>
       </c>
-      <c r="E49" s="64">
+      <c r="E49" s="60">
         <v>366152.37</v>
       </c>
-      <c r="F49" s="64">
+      <c r="F49" s="60">
         <v>1361830.0630000001</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A50" s="63">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A50" s="59">
         <v>2038</v>
       </c>
-      <c r="B50" s="64">
+      <c r="B50" s="60">
         <v>9063572.9260000009</v>
       </c>
-      <c r="C50" s="64">
-        <v>67801.926999999996</v>
-      </c>
-      <c r="D50" s="64">
+      <c r="C50" s="60">
+        <v>70265.826000000001</v>
+      </c>
+      <c r="D50" s="60">
         <v>436704.79599999997</v>
       </c>
-      <c r="E50" s="64">
+      <c r="E50" s="60">
         <v>367551.45500000002</v>
       </c>
-      <c r="F50" s="64">
+      <c r="F50" s="60">
         <v>1355722.7069999999</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A51" s="63">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A51" s="59">
         <v>2039</v>
       </c>
-      <c r="B51" s="64">
+      <c r="B51" s="60">
         <v>9120928.3800000008</v>
       </c>
-      <c r="C51" s="64">
-        <v>67873.403000000006</v>
-      </c>
-      <c r="D51" s="64">
+      <c r="C51" s="60">
+        <v>70354.623999999996</v>
+      </c>
+      <c r="D51" s="60">
         <v>435575.79399999999</v>
       </c>
-      <c r="E51" s="64">
+      <c r="E51" s="60">
         <v>368906.81800000003</v>
       </c>
-      <c r="F51" s="64">
+      <c r="F51" s="60">
         <v>1349394.7180000001</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A52" s="63">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A52" s="59">
         <v>2040</v>
       </c>
-      <c r="B52" s="64">
+      <c r="B52" s="60">
         <v>9177190.2029999997</v>
       </c>
-      <c r="C52" s="64">
-        <v>67938.903999999995</v>
-      </c>
-      <c r="D52" s="64">
+      <c r="C52" s="60">
+        <v>70437.452999999994</v>
+      </c>
+      <c r="D52" s="60">
         <v>434422.40100000007</v>
       </c>
-      <c r="E52" s="64">
+      <c r="E52" s="60">
         <v>370209.31599999999</v>
       </c>
-      <c r="F52" s="64">
+      <c r="F52" s="60">
         <v>1342816.6569999999</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A53" s="63">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A53" s="59">
         <v>2041</v>
       </c>
-      <c r="B53" s="64">
+      <c r="B53" s="60">
         <v>9232281.5749999993</v>
       </c>
-      <c r="C53" s="64">
-        <v>68002.574999999997</v>
-      </c>
-      <c r="D53" s="64">
+      <c r="C53" s="60">
+        <v>70518.601999999999</v>
+      </c>
+      <c r="D53" s="60">
         <v>433267.647</v>
       </c>
-      <c r="E53" s="64">
+      <c r="E53" s="60">
         <v>371469.478</v>
       </c>
-      <c r="F53" s="64">
+      <c r="F53" s="60">
         <v>1335990.2309999999</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A54" s="63">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A54" s="59">
         <v>2042</v>
       </c>
-      <c r="B54" s="64">
+      <c r="B54" s="60">
         <v>9286110.3709999993</v>
       </c>
-      <c r="C54" s="64">
-        <v>68063.86</v>
-      </c>
-      <c r="D54" s="64">
+      <c r="C54" s="60">
+        <v>70597.447</v>
+      </c>
+      <c r="D54" s="60">
         <v>432096.70899999997</v>
       </c>
-      <c r="E54" s="64">
+      <c r="E54" s="60">
         <v>372704.772</v>
       </c>
-      <c r="F54" s="64">
+      <c r="F54" s="60">
         <v>1328909.2379999999</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A55" s="63">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A55" s="59">
         <v>2043</v>
       </c>
-      <c r="B55" s="64">
+      <c r="B55" s="60">
         <v>9338661.3139999993</v>
       </c>
-      <c r="C55" s="64">
-        <v>68115.785999999993</v>
-      </c>
-      <c r="D55" s="64">
+      <c r="C55" s="60">
+        <v>70666.918999999994</v>
+      </c>
+      <c r="D55" s="60">
         <v>430874.26299999998</v>
       </c>
-      <c r="E55" s="64">
+      <c r="E55" s="60">
         <v>373900.67700000003</v>
       </c>
-      <c r="F55" s="64">
+      <c r="F55" s="60">
         <v>1321590.798</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A56" s="63">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A56" s="59">
         <v>2044</v>
       </c>
-      <c r="B56" s="64">
+      <c r="B56" s="60">
         <v>9389873.693</v>
       </c>
-      <c r="C56" s="64">
-        <v>68157.082999999999</v>
-      </c>
-      <c r="D56" s="64">
+      <c r="C56" s="60">
+        <v>70725.672999999995</v>
+      </c>
+      <c r="D56" s="60">
         <v>429598.62099999987</v>
       </c>
-      <c r="E56" s="64">
+      <c r="E56" s="60">
         <v>375029.24599999998</v>
       </c>
-      <c r="F56" s="64">
+      <c r="F56" s="60">
         <v>1314015.987</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A57" s="63">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A57" s="59">
         <v>2045</v>
       </c>
-      <c r="B57" s="64">
+      <c r="B57" s="60">
         <v>9439639.6679999996</v>
       </c>
-      <c r="C57" s="64">
-        <v>68190.955000000002</v>
-      </c>
-      <c r="D57" s="64">
+      <c r="C57" s="60">
+        <v>70776.744999999995</v>
+      </c>
+      <c r="D57" s="60">
         <v>428280.46499999997</v>
       </c>
-      <c r="E57" s="64">
+      <c r="E57" s="60">
         <v>376106.47200000001</v>
       </c>
-      <c r="F57" s="64">
+      <c r="F57" s="60">
         <v>1306113.7879999999</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A58" s="63">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A58" s="59">
         <v>2046</v>
       </c>
-      <c r="B58" s="64">
+      <c r="B58" s="60">
         <v>9487889.6040000003</v>
       </c>
-      <c r="C58" s="64">
-        <v>68214.672999999995</v>
-      </c>
-      <c r="D58" s="64">
+      <c r="C58" s="60">
+        <v>70817.377999999997</v>
+      </c>
+      <c r="D58" s="60">
         <v>426921.04200000002</v>
       </c>
-      <c r="E58" s="64">
+      <c r="E58" s="60">
         <v>377131.72700000001</v>
       </c>
-      <c r="F58" s="64">
+      <c r="F58" s="60">
         <v>1297817.5819999999</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A59" s="63">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A59" s="59">
         <v>2047</v>
       </c>
-      <c r="B59" s="64">
+      <c r="B59" s="60">
         <v>9534545.977</v>
       </c>
-      <c r="C59" s="64">
-        <v>68229.077000000005</v>
-      </c>
-      <c r="D59" s="64">
+      <c r="C59" s="60">
+        <v>70848.555999999997</v>
+      </c>
+      <c r="D59" s="60">
         <v>425511.16099999996</v>
       </c>
-      <c r="E59" s="64">
+      <c r="E59" s="60">
         <v>378117.76699999999</v>
       </c>
-      <c r="F59" s="64">
+      <c r="F59" s="60">
         <v>1289120.4269999999</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A60" s="63">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A60" s="59">
         <v>2048</v>
       </c>
-      <c r="B60" s="64">
+      <c r="B60" s="60">
         <v>9579536.0429999996</v>
       </c>
-      <c r="C60" s="64">
-        <v>68235.289000000004</v>
-      </c>
-      <c r="D60" s="64">
+      <c r="C60" s="60">
+        <v>70871.183000000005</v>
+      </c>
+      <c r="D60" s="60">
         <v>424046.07800000015</v>
       </c>
-      <c r="E60" s="64">
+      <c r="E60" s="60">
         <v>379063.74400000001</v>
       </c>
-      <c r="F60" s="64">
+      <c r="F60" s="60">
         <v>1279992.585</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A61" s="63">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A61" s="59">
         <v>2049</v>
       </c>
-      <c r="B61" s="64">
+      <c r="B61" s="60">
         <v>9622824.0289999992</v>
       </c>
-      <c r="C61" s="64">
-        <v>68231.375</v>
-      </c>
-      <c r="D61" s="64">
+      <c r="C61" s="60">
+        <v>70883.187999999995</v>
+      </c>
+      <c r="D61" s="60">
         <v>422524.55599999998</v>
       </c>
-      <c r="E61" s="64">
+      <c r="E61" s="60">
         <v>379966.90600000002</v>
       </c>
-      <c r="F61" s="64">
+      <c r="F61" s="60">
         <v>1270381.145</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A62" s="63">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A62" s="59">
         <v>2050</v>
       </c>
-      <c r="B62" s="64">
+      <c r="B62" s="60">
         <v>9664378.5869999994</v>
       </c>
-      <c r="C62" s="64">
-        <v>68219.675000000003</v>
-      </c>
-      <c r="D62" s="64">
+      <c r="C62" s="60">
+        <v>70886.817999999999</v>
+      </c>
+      <c r="D62" s="60">
         <v>420955.34100000001</v>
       </c>
-      <c r="E62" s="64">
+      <c r="E62" s="60">
         <v>380846.91</v>
       </c>
-      <c r="F62" s="64">
+      <c r="F62" s="60">
         <v>1260289.0930000001</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A63" s="63">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A63" s="59">
         <v>2051</v>
       </c>
-      <c r="B63" s="64">
+      <c r="B63" s="60">
         <v>9704192.3039999995</v>
       </c>
-      <c r="C63" s="64">
-        <v>68200.254000000001</v>
-      </c>
-      <c r="D63" s="64">
+      <c r="C63" s="60">
+        <v>70882.233999999997</v>
+      </c>
+      <c r="D63" s="60">
         <v>419346.89500000008</v>
       </c>
-      <c r="E63" s="64">
+      <c r="E63" s="60">
         <v>381708.39600000001</v>
       </c>
-      <c r="F63" s="64">
+      <c r="F63" s="60">
         <v>1249692.5379999999</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A64" s="63">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A64" s="59">
         <v>2052</v>
       </c>
-      <c r="B64" s="64">
+      <c r="B64" s="60">
         <v>9742264.5150000006</v>
       </c>
-      <c r="C64" s="64">
-        <v>68175.77</v>
-      </c>
-      <c r="D64" s="64">
+      <c r="C64" s="60">
+        <v>70872.498999999996</v>
+      </c>
+      <c r="D64" s="60">
         <v>417691.14999999997</v>
       </c>
-      <c r="E64" s="64">
+      <c r="E64" s="60">
         <v>382543.75300000003</v>
       </c>
-      <c r="F64" s="64">
+      <c r="F64" s="60">
         <v>1238557.132</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A65" s="63">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A65" s="59">
         <v>2053</v>
       </c>
-      <c r="B65" s="64">
+      <c r="B65" s="60">
         <v>9778614.6140000001</v>
       </c>
-      <c r="C65" s="64">
-        <v>68146.932000000001</v>
-      </c>
-      <c r="D65" s="64">
+      <c r="C65" s="60">
+        <v>70858.290999999997</v>
+      </c>
+      <c r="D65" s="60">
         <v>415966.71600000001</v>
       </c>
-      <c r="E65" s="64">
+      <c r="E65" s="60">
         <v>383359.33199999999</v>
       </c>
-      <c r="F65" s="64">
+      <c r="F65" s="60">
         <v>1226929.8540000001</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A66" s="63">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A66" s="59">
         <v>2054</v>
       </c>
-      <c r="B66" s="64">
+      <c r="B66" s="60">
         <v>9813251.659</v>
       </c>
-      <c r="C66" s="64">
-        <v>68111.014999999999</v>
-      </c>
-      <c r="D66" s="64">
+      <c r="C66" s="60">
+        <v>70836.75</v>
+      </c>
+      <c r="D66" s="60">
         <v>414174.85799999995</v>
       </c>
-      <c r="E66" s="64">
+      <c r="E66" s="60">
         <v>384145.91999999998</v>
       </c>
-      <c r="F66" s="64">
+      <c r="F66" s="60">
         <v>1214853.3459999999</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A67" s="63">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A67" s="59">
         <v>2055</v>
       </c>
-      <c r="B67" s="64">
+      <c r="B67" s="60">
         <v>9846237.5700000003</v>
       </c>
-      <c r="C67" s="64">
-        <v>68067.630999999994</v>
-      </c>
-      <c r="D67" s="64">
+      <c r="C67" s="60">
+        <v>70807.737999999998</v>
+      </c>
+      <c r="D67" s="60">
         <v>412334.533</v>
       </c>
-      <c r="E67" s="64">
+      <c r="E67" s="60">
         <v>384894.29700000002</v>
       </c>
-      <c r="F67" s="64">
+      <c r="F67" s="60">
         <v>1202342.4709999999</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A68" s="63">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A68" s="59">
         <v>2056</v>
       </c>
-      <c r="B68" s="64">
+      <c r="B68" s="60">
         <v>9877680.3920000009</v>
       </c>
-      <c r="C68" s="64">
-        <v>68022.156000000003</v>
-      </c>
-      <c r="D68" s="64">
+      <c r="C68" s="60">
+        <v>70776.800000000003</v>
+      </c>
+      <c r="D68" s="60">
         <v>410448.42000000004</v>
       </c>
-      <c r="E68" s="64">
+      <c r="E68" s="60">
         <v>385642.34100000001</v>
       </c>
-      <c r="F68" s="64">
+      <c r="F68" s="60">
         <v>1189440.669</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A69" s="63">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A69" s="59">
         <v>2057</v>
       </c>
-      <c r="B69" s="64">
+      <c r="B69" s="60">
         <v>9907637.193</v>
       </c>
-      <c r="C69" s="64">
-        <v>67978.668999999994</v>
-      </c>
-      <c r="D69" s="64">
+      <c r="C69" s="60">
+        <v>70747.672999999995</v>
+      </c>
+      <c r="D69" s="60">
         <v>408533.27399999992</v>
       </c>
-      <c r="E69" s="64">
+      <c r="E69" s="60">
         <v>386425.22600000002</v>
       </c>
-      <c r="F69" s="64">
+      <c r="F69" s="60">
         <v>1176217.9450000001</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A70" s="63">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A70" s="59">
         <v>2058</v>
       </c>
-      <c r="B70" s="64">
+      <c r="B70" s="60">
         <v>9936164.3790000007</v>
       </c>
-      <c r="C70" s="64">
-        <v>67935.849000000002</v>
-      </c>
-      <c r="D70" s="64">
+      <c r="C70" s="60">
+        <v>70719.057000000001</v>
+      </c>
+      <c r="D70" s="60">
         <v>406603.29399999999</v>
       </c>
-      <c r="E70" s="64">
+      <c r="E70" s="60">
         <v>387253.70500000002</v>
       </c>
-      <c r="F70" s="64">
+      <c r="F70" s="60">
         <v>1162722.7080000001</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A71" s="63">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A71" s="59">
         <v>2059</v>
       </c>
-      <c r="B71" s="64">
+      <c r="B71" s="60">
         <v>9963337.0820000004</v>
       </c>
-      <c r="C71" s="64">
-        <v>67892.952000000005</v>
-      </c>
-      <c r="D71" s="64">
+      <c r="C71" s="60">
+        <v>70690.423999999999</v>
+      </c>
+      <c r="D71" s="60">
         <v>404661.71100000007</v>
       </c>
-      <c r="E71" s="64">
+      <c r="E71" s="60">
         <v>388093.05699999997</v>
       </c>
-      <c r="F71" s="64">
+      <c r="F71" s="60">
         <v>1149002.1669999999</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A72" s="63">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A72" s="59">
         <v>2060</v>
       </c>
-      <c r="B72" s="64">
+      <c r="B72" s="60">
         <v>9989232.2919999994</v>
       </c>
-      <c r="C72" s="64">
-        <v>67850.294999999998</v>
-      </c>
-      <c r="D72" s="64">
+      <c r="C72" s="60">
+        <v>70661.854000000007</v>
+      </c>
+      <c r="D72" s="60">
         <v>402712.63299999991</v>
       </c>
-      <c r="E72" s="64">
+      <c r="E72" s="60">
         <v>388918.39399999997</v>
       </c>
-      <c r="F72" s="64">
+      <c r="F72" s="60">
         <v>1135127.1910000001</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A73" s="63">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A73" s="59">
         <v>2061</v>
       </c>
-      <c r="B73" s="64">
+      <c r="B73" s="60">
         <v>10013916.213</v>
       </c>
-      <c r="C73" s="64">
-        <v>67810.557000000001</v>
-      </c>
-      <c r="D73" s="64">
+      <c r="C73" s="60">
+        <v>70636.285999999993</v>
+      </c>
+      <c r="D73" s="60">
         <v>400766.93200000015</v>
       </c>
-      <c r="E73" s="64">
+      <c r="E73" s="60">
         <v>389765.29399999999</v>
       </c>
-      <c r="F73" s="64">
+      <c r="F73" s="60">
         <v>1121174.7169999999</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A74" s="63">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A74" s="59">
         <v>2062</v>
       </c>
-      <c r="B74" s="64">
+      <c r="B74" s="60">
         <v>10037466.6</v>
       </c>
-      <c r="C74" s="64">
-        <v>67772.615999999995</v>
-      </c>
-      <c r="D74" s="64">
+      <c r="C74" s="60">
+        <v>70612.785000000003</v>
+      </c>
+      <c r="D74" s="60">
         <v>398823.46799999999</v>
       </c>
-      <c r="E74" s="64">
+      <c r="E74" s="60">
         <v>390647.52100000001</v>
       </c>
-      <c r="F74" s="64">
+      <c r="F74" s="60">
         <v>1107207.1329999999</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A75" s="63">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A75" s="59">
         <v>2063</v>
       </c>
-      <c r="B75" s="64">
+      <c r="B75" s="60">
         <v>10059950.035</v>
       </c>
-      <c r="C75" s="64">
-        <v>67739.664000000004</v>
-      </c>
-      <c r="D75" s="64">
+      <c r="C75" s="60">
+        <v>70594.607999999993</v>
+      </c>
+      <c r="D75" s="60">
         <v>396899.60199999996</v>
       </c>
-      <c r="E75" s="64">
+      <c r="E75" s="60">
         <v>391545.61800000002</v>
       </c>
-      <c r="F75" s="64">
+      <c r="F75" s="60">
         <v>1093276.7039999999</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A76" s="63">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A76" s="59">
         <v>2064</v>
       </c>
-      <c r="B76" s="64">
+      <c r="B76" s="60">
         <v>10081402.737</v>
       </c>
-      <c r="C76" s="64">
-        <v>67713.646999999997</v>
-      </c>
-      <c r="D76" s="64">
+      <c r="C76" s="60">
+        <v>70583.659</v>
+      </c>
+      <c r="D76" s="60">
         <v>395004.61700000003</v>
       </c>
-      <c r="E76" s="64">
+      <c r="E76" s="60">
         <v>392444.228</v>
       </c>
-      <c r="F76" s="64">
+      <c r="F76" s="60">
         <v>1079407.882</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A77" s="63">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A77" s="59">
         <v>2065</v>
       </c>
-      <c r="B77" s="64">
+      <c r="B77" s="60">
         <v>10101849.561000001</v>
       </c>
-      <c r="C77" s="64">
-        <v>67691.804000000004</v>
-      </c>
-      <c r="D77" s="64">
+      <c r="C77" s="60">
+        <v>70577.035000000003</v>
+      </c>
+      <c r="D77" s="60">
         <v>393131.79000000004</v>
       </c>
-      <c r="E77" s="64">
+      <c r="E77" s="60">
         <v>393352.609</v>
       </c>
-      <c r="F77" s="64">
+      <c r="F77" s="60">
         <v>1065632.5290000001</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A78" s="63">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A78" s="59">
         <v>2066</v>
       </c>
-      <c r="B78" s="64">
+      <c r="B78" s="60">
         <v>10121317.107000001</v>
       </c>
-      <c r="C78" s="64">
-        <v>67677.298999999999</v>
-      </c>
-      <c r="D78" s="64">
+      <c r="C78" s="60">
+        <v>70578.236000000004</v>
+      </c>
+      <c r="D78" s="60">
         <v>391291.73300000001</v>
       </c>
-      <c r="E78" s="64">
+      <c r="E78" s="60">
         <v>394294.35</v>
       </c>
-      <c r="F78" s="64">
+      <c r="F78" s="60">
         <v>1051989.135</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A79" s="63">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A79" s="59">
         <v>2067</v>
       </c>
-      <c r="B79" s="64">
+      <c r="B79" s="60">
         <v>10139808.361</v>
       </c>
-      <c r="C79" s="64">
-        <v>67669.051999999996</v>
-      </c>
-      <c r="D79" s="64">
+      <c r="C79" s="60">
+        <v>70586.297000000006</v>
+      </c>
+      <c r="D79" s="60">
         <v>389489.04200000002</v>
       </c>
-      <c r="E79" s="64">
+      <c r="E79" s="60">
         <v>395267.22600000002</v>
       </c>
-      <c r="F79" s="64">
+      <c r="F79" s="60">
         <v>1038472.818</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A80" s="63">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A80" s="59">
         <v>2068</v>
       </c>
-      <c r="B80" s="64">
+      <c r="B80" s="60">
         <v>10157301.941</v>
       </c>
-      <c r="C80" s="64">
-        <v>67664.28</v>
-      </c>
-      <c r="D80" s="64">
+      <c r="C80" s="60">
+        <v>70598.070999999996</v>
+      </c>
+      <c r="D80" s="60">
         <v>387721.924</v>
       </c>
-      <c r="E80" s="64">
+      <c r="E80" s="60">
         <v>396248.28499999997</v>
       </c>
-      <c r="F80" s="64">
+      <c r="F80" s="60">
         <v>1025103.452</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A81" s="63">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A81" s="59">
         <v>2069</v>
       </c>
-      <c r="B81" s="64">
+      <c r="B81" s="60">
         <v>10173782.135</v>
       </c>
-      <c r="C81" s="64">
-        <v>67668.108999999997</v>
-      </c>
-      <c r="D81" s="64">
+      <c r="C81" s="60">
+        <v>70618.812000000005</v>
+      </c>
+      <c r="D81" s="60">
         <v>385994.04200000007</v>
       </c>
-      <c r="E81" s="64">
+      <c r="E81" s="60">
         <v>397237.40500000003</v>
       </c>
-      <c r="F81" s="64">
+      <c r="F81" s="60">
         <v>1011878.19</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A82" s="63">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A82" s="59">
         <v>2070</v>
       </c>
-      <c r="B82" s="64">
+      <c r="B82" s="60">
         <v>10189241.959000001</v>
       </c>
-      <c r="C82" s="64">
-        <v>67678.904999999999</v>
-      </c>
-      <c r="D82" s="64">
+      <c r="C82" s="60">
+        <v>70646.951000000001</v>
+      </c>
+      <c r="D82" s="60">
         <v>384310.26799999998</v>
       </c>
-      <c r="E82" s="64">
+      <c r="E82" s="60">
         <v>398218.08799999999</v>
       </c>
-      <c r="F82" s="64">
+      <c r="F82" s="60">
         <v>998784.31900000002</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A83" s="63">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A83" s="59">
         <v>2071</v>
       </c>
-      <c r="B83" s="64">
+      <c r="B83" s="60">
         <v>10203681.568</v>
       </c>
-      <c r="C83" s="64">
-        <v>67698.398000000001</v>
-      </c>
-      <c r="D83" s="64">
+      <c r="C83" s="60">
+        <v>70683.694000000003</v>
+      </c>
+      <c r="D83" s="60">
         <v>382670.826</v>
       </c>
-      <c r="E83" s="64">
+      <c r="E83" s="60">
         <v>399192.92</v>
       </c>
-      <c r="F83" s="64">
+      <c r="F83" s="60">
         <v>985806.56</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A84" s="63">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A84" s="59">
         <v>2072</v>
       </c>
-      <c r="B84" s="64">
+      <c r="B84" s="60">
         <v>10217055.169</v>
       </c>
-      <c r="C84" s="64">
-        <v>67724.513999999996</v>
-      </c>
-      <c r="D84" s="64">
+      <c r="C84" s="60">
+        <v>70727.335000000006</v>
+      </c>
+      <c r="D84" s="60">
         <v>381068.141</v>
       </c>
-      <c r="E84" s="64">
+      <c r="E84" s="60">
         <v>400151.80300000001</v>
       </c>
-      <c r="F84" s="64">
+      <c r="F84" s="60">
         <v>972905.67099999997</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A85" s="63">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A85" s="59">
         <v>2073</v>
       </c>
-      <c r="B85" s="64">
+      <c r="B85" s="60">
         <v>10229327.823999999</v>
       </c>
-      <c r="C85" s="64">
-        <v>67752.34</v>
-      </c>
-      <c r="D85" s="64">
+      <c r="C85" s="60">
+        <v>70773.160999999993</v>
+      </c>
+      <c r="D85" s="60">
         <v>379495.90099999995</v>
       </c>
-      <c r="E85" s="64">
+      <c r="E85" s="60">
         <v>401080.53200000001</v>
       </c>
-      <c r="F85" s="64">
+      <c r="F85" s="60">
         <v>960055.38300000003</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A86" s="63">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A86" s="59">
         <v>2074</v>
       </c>
-      <c r="B86" s="64">
+      <c r="B86" s="60">
         <v>10240485.056</v>
       </c>
-      <c r="C86" s="64">
-        <v>67784.584000000003</v>
-      </c>
-      <c r="D86" s="64">
+      <c r="C86" s="60">
+        <v>70823.368000000002</v>
+      </c>
+      <c r="D86" s="60">
         <v>377958.35600000003</v>
       </c>
-      <c r="E86" s="64">
+      <c r="E86" s="60">
         <v>401993.348</v>
       </c>
-      <c r="F86" s="64">
+      <c r="F86" s="60">
         <v>947249.41700000002</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A87" s="63">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A87" s="59">
         <v>2075</v>
       </c>
-      <c r="B87" s="64">
+      <c r="B87" s="60">
         <v>10250496.432</v>
       </c>
-      <c r="C87" s="64">
-        <v>67822.260999999999</v>
-      </c>
-      <c r="D87" s="64">
+      <c r="C87" s="60">
+        <v>70879.096999999994</v>
+      </c>
+      <c r="D87" s="60">
         <v>376480.08500000008</v>
       </c>
-      <c r="E87" s="64">
+      <c r="E87" s="60">
         <v>402910.163</v>
       </c>
-      <c r="F87" s="64">
+      <c r="F87" s="60">
         <v>934466.66</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A88" s="63">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A88" s="59">
         <v>2076</v>
       </c>
-      <c r="B88" s="64">
+      <c r="B88" s="60">
         <v>10259351.432</v>
       </c>
-      <c r="C88" s="64">
-        <v>67863.936000000002</v>
-      </c>
-      <c r="D88" s="64">
+      <c r="C88" s="60">
+        <v>70938.891000000003</v>
+      </c>
+      <c r="D88" s="60">
         <v>375047.78200000006</v>
       </c>
-      <c r="E88" s="64">
+      <c r="E88" s="60">
         <v>403820.92599999998</v>
       </c>
-      <c r="F88" s="64">
+      <c r="F88" s="60">
         <v>921677.63</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A89" s="63">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A89" s="59">
         <v>2077</v>
       </c>
-      <c r="B89" s="64">
+      <c r="B89" s="60">
         <v>10267045.023</v>
       </c>
-      <c r="C89" s="64">
-        <v>67905.317999999999</v>
-      </c>
-      <c r="D89" s="64">
+      <c r="C89" s="60">
+        <v>70998.558000000005</v>
+      </c>
+      <c r="D89" s="60">
         <v>373634.73</v>
       </c>
-      <c r="E89" s="64">
+      <c r="E89" s="60">
         <v>404683.462</v>
       </c>
-      <c r="F89" s="64">
+      <c r="F89" s="60">
         <v>908874.53200000001</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A90" s="63">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A90" s="59">
         <v>2078</v>
       </c>
-      <c r="B90" s="64">
+      <c r="B90" s="60">
         <v>10273556.322000001</v>
       </c>
-      <c r="C90" s="64">
-        <v>67945.203999999998</v>
-      </c>
-      <c r="D90" s="64">
+      <c r="C90" s="60">
+        <v>71056.766000000003</v>
+      </c>
+      <c r="D90" s="60">
         <v>372260.67599999998</v>
       </c>
-      <c r="E90" s="64">
+      <c r="E90" s="60">
         <v>405518.70199999999</v>
       </c>
-      <c r="F90" s="64">
+      <c r="F90" s="60">
         <v>896043.78899999999</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A91" s="63">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A91" s="59">
         <v>2079</v>
       </c>
-      <c r="B91" s="64">
+      <c r="B91" s="60">
         <v>10278887.472999999</v>
       </c>
-      <c r="C91" s="64">
-        <v>67984.811000000002</v>
-      </c>
-      <c r="D91" s="64">
+      <c r="C91" s="60">
+        <v>71114.271999999997</v>
+      </c>
+      <c r="D91" s="60">
         <v>370924.19000000006</v>
       </c>
-      <c r="E91" s="64">
+      <c r="E91" s="60">
         <v>406319.93</v>
       </c>
-      <c r="F91" s="64">
+      <c r="F91" s="60">
         <v>883166.97499999998</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A92" s="63">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A92" s="59">
         <v>2080</v>
       </c>
-      <c r="B92" s="64">
+      <c r="B92" s="60">
         <v>10283078.028999999</v>
       </c>
-      <c r="C92" s="64">
-        <v>68024.937000000005</v>
-      </c>
-      <c r="D92" s="64">
+      <c r="C92" s="60">
+        <v>71172.107999999993</v>
+      </c>
+      <c r="D92" s="60">
         <v>369621.90600000002</v>
       </c>
-      <c r="E92" s="64">
+      <c r="E92" s="60">
         <v>407079.81599999999</v>
       </c>
-      <c r="F92" s="64">
+      <c r="F92" s="60">
         <v>870252.34400000004</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A93" s="63">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A93" s="59">
         <v>2081</v>
       </c>
-      <c r="B93" s="64">
+      <c r="B93" s="60">
         <v>10286161.734999999</v>
       </c>
-      <c r="C93" s="64">
-        <v>68066.815000000002</v>
-      </c>
-      <c r="D93" s="64">
+      <c r="C93" s="60">
+        <v>71231.608999999997</v>
+      </c>
+      <c r="D93" s="60">
         <v>368361.90900000004</v>
       </c>
-      <c r="E93" s="64">
+      <c r="E93" s="60">
         <v>407866.28499999997</v>
       </c>
-      <c r="F93" s="64">
+      <c r="F93" s="60">
         <v>857328.71499999997</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A94" s="63">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A94" s="59">
         <v>2082</v>
       </c>
-      <c r="B94" s="64">
+      <c r="B94" s="60">
         <v>10288205.050000001</v>
       </c>
-      <c r="C94" s="64">
-        <v>68108.438999999998</v>
-      </c>
-      <c r="D94" s="64">
+      <c r="C94" s="60">
+        <v>71290.903000000006</v>
+      </c>
+      <c r="D94" s="60">
         <v>367136.15699999989</v>
       </c>
-      <c r="E94" s="64">
+      <c r="E94" s="60">
         <v>408655.86099999998</v>
       </c>
-      <c r="F94" s="64">
+      <c r="F94" s="60">
         <v>844439.196</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A95" s="63">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A95" s="59">
         <v>2083</v>
       </c>
-      <c r="B95" s="64">
+      <c r="B95" s="60">
         <v>10289247.323000001</v>
       </c>
-      <c r="C95" s="64">
-        <v>68153.316999999995</v>
-      </c>
-      <c r="D95" s="64">
+      <c r="C95" s="60">
+        <v>71353.495999999999</v>
+      </c>
+      <c r="D95" s="60">
         <v>365939.98800000007</v>
       </c>
-      <c r="E95" s="64">
+      <c r="E95" s="60">
         <v>409401.65899999999</v>
       </c>
-      <c r="F95" s="64">
+      <c r="F95" s="60">
         <v>831604.66700000002</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A96" s="63">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A96" s="59">
         <v>2084</v>
       </c>
-      <c r="B96" s="64">
+      <c r="B96" s="60">
         <v>10289315.244000001</v>
       </c>
-      <c r="C96" s="64">
-        <v>68198.942999999999</v>
-      </c>
-      <c r="D96" s="64">
+      <c r="C96" s="60">
+        <v>71416.544999999998</v>
+      </c>
+      <c r="D96" s="60">
         <v>364768.47600000014</v>
       </c>
-      <c r="E96" s="64">
+      <c r="E96" s="60">
         <v>410134.66600000003</v>
       </c>
-      <c r="F96" s="64">
+      <c r="F96" s="60">
         <v>818815.35600000003</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A97" s="63">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A97" s="59">
         <v>2085</v>
       </c>
-      <c r="B97" s="64">
+      <c r="B97" s="60">
         <v>10288456.598999999</v>
       </c>
-      <c r="C97" s="64">
-        <v>68237.653999999995</v>
-      </c>
-      <c r="D97" s="64">
+      <c r="C97" s="60">
+        <v>71472.520999999993</v>
+      </c>
+      <c r="D97" s="60">
         <v>363612.08199999999</v>
       </c>
-      <c r="E97" s="64">
+      <c r="E97" s="60">
         <v>410829.98499999999</v>
       </c>
-      <c r="F97" s="64">
+      <c r="F97" s="60">
         <v>806115.054</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A98" s="63">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A98" s="59">
         <v>2086</v>
       </c>
-      <c r="B98" s="64">
+      <c r="B98" s="60">
         <v>10286708.359999999</v>
       </c>
-      <c r="C98" s="64">
-        <v>68276.452000000005</v>
-      </c>
-      <c r="D98" s="64">
+      <c r="C98" s="60">
+        <v>71528.369000000006</v>
+      </c>
+      <c r="D98" s="60">
         <v>362474.72799999989</v>
       </c>
-      <c r="E98" s="64">
+      <c r="E98" s="60">
         <v>411520.08600000001</v>
       </c>
-      <c r="F98" s="64">
+      <c r="F98" s="60">
         <v>793559.25399999996</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A99" s="63">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A99" s="59">
         <v>2087</v>
       </c>
-      <c r="B99" s="64">
+      <c r="B99" s="60">
         <v>10284111.374</v>
       </c>
-      <c r="C99" s="64">
-        <v>68316.292000000001</v>
-      </c>
-      <c r="D99" s="64">
+      <c r="C99" s="60">
+        <v>71584.963000000003</v>
+      </c>
+      <c r="D99" s="60">
         <v>361363.54499999998</v>
       </c>
-      <c r="E99" s="64">
+      <c r="E99" s="60">
         <v>412236.77600000001</v>
       </c>
-      <c r="F99" s="64">
+      <c r="F99" s="60">
         <v>781153.71799999999</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A100" s="63">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A100" s="59">
         <v>2088</v>
       </c>
-      <c r="B100" s="64">
+      <c r="B100" s="60">
         <v>10280704.572000001</v>
       </c>
-      <c r="C100" s="64">
-        <v>68354.444000000003</v>
-      </c>
-      <c r="D100" s="64">
+      <c r="C100" s="60">
+        <v>71639.769</v>
+      </c>
+      <c r="D100" s="60">
         <v>360281.40500000003</v>
       </c>
-      <c r="E100" s="64">
+      <c r="E100" s="60">
         <v>412978.78</v>
       </c>
-      <c r="F100" s="64">
+      <c r="F100" s="60">
         <v>768899.13199999998</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A101" s="63">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A101" s="59">
         <v>2089</v>
       </c>
-      <c r="B101" s="64">
+      <c r="B101" s="60">
         <v>10276518.279999999</v>
       </c>
-      <c r="C101" s="64">
-        <v>68389.692999999999</v>
-      </c>
-      <c r="D101" s="64">
+      <c r="C101" s="60">
+        <v>71691.237999999998</v>
+      </c>
+      <c r="D101" s="60">
         <v>359214.11100000003</v>
       </c>
-      <c r="E101" s="64">
+      <c r="E101" s="60">
         <v>413730.74099999998</v>
       </c>
-      <c r="F101" s="64">
+      <c r="F101" s="60">
         <v>756809.11</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A102" s="63">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A102" s="59">
         <v>2090</v>
       </c>
-      <c r="B102" s="64">
+      <c r="B102" s="60">
         <v>10271565.07</v>
       </c>
-      <c r="C102" s="64">
-        <v>68421.883000000002</v>
-      </c>
-      <c r="D102" s="64">
+      <c r="C102" s="60">
+        <v>71739.254000000001</v>
+      </c>
+      <c r="D102" s="60">
         <v>358149.47100000002</v>
       </c>
-      <c r="E102" s="64">
+      <c r="E102" s="60">
         <v>414457.64</v>
       </c>
-      <c r="F102" s="64">
+      <c r="F102" s="60">
         <v>744902.83600000001</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A103" s="63">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A103" s="59">
         <v>2091</v>
       </c>
-      <c r="B103" s="64">
+      <c r="B103" s="60">
         <v>10265861.714</v>
       </c>
-      <c r="C103" s="64">
-        <v>68451.044999999998</v>
-      </c>
-      <c r="D103" s="64">
+      <c r="C103" s="60">
+        <v>71783.903999999995</v>
+      </c>
+      <c r="D103" s="60">
         <v>357104.93199999997</v>
       </c>
-      <c r="E103" s="64">
+      <c r="E103" s="60">
         <v>415186.38900000002</v>
       </c>
-      <c r="F103" s="64">
+      <c r="F103" s="60">
         <v>733179.45600000001</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A104" s="63">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A104" s="59">
         <v>2092</v>
       </c>
-      <c r="B104" s="64">
+      <c r="B104" s="60">
         <v>10259408.375</v>
       </c>
-      <c r="C104" s="64">
-        <v>68475.278000000006</v>
-      </c>
-      <c r="D104" s="64">
+      <c r="C104" s="60">
+        <v>71823.241999999998</v>
+      </c>
+      <c r="D104" s="60">
         <v>356085.554</v>
       </c>
-      <c r="E104" s="64">
+      <c r="E104" s="60">
         <v>415929</v>
       </c>
-      <c r="F104" s="64">
+      <c r="F104" s="60">
         <v>721612.75</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A105" s="63">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A105" s="59">
         <v>2093</v>
       </c>
-      <c r="B105" s="64">
+      <c r="B105" s="60">
         <v>10252184.759</v>
       </c>
-      <c r="C105" s="64">
-        <v>68498.701000000001</v>
-      </c>
-      <c r="D105" s="64">
+      <c r="C105" s="60">
+        <v>71861.244999999995</v>
+      </c>
+      <c r="D105" s="60">
         <v>355083.0670000001</v>
       </c>
-      <c r="E105" s="64">
+      <c r="E105" s="60">
         <v>416662.12699999998</v>
       </c>
-      <c r="F105" s="64">
+      <c r="F105" s="60">
         <v>710185.96799999999</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A106" s="63">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A106" s="59">
         <v>2094</v>
       </c>
-      <c r="B106" s="64">
+      <c r="B106" s="60">
         <v>10244185.836999999</v>
       </c>
-      <c r="C106" s="64">
-        <v>68518.865000000005</v>
-      </c>
-      <c r="D106" s="64">
+      <c r="C106" s="60">
+        <v>71895.763000000006</v>
+      </c>
+      <c r="D106" s="60">
         <v>354087.00400000002</v>
       </c>
-      <c r="E106" s="64">
+      <c r="E106" s="60">
         <v>417391.61599999998</v>
       </c>
-      <c r="F106" s="64">
+      <c r="F106" s="60">
         <v>698893.77</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A107" s="63">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A107" s="59">
         <v>2095</v>
       </c>
-      <c r="B107" s="64">
+      <c r="B107" s="60">
         <v>10235403.601</v>
       </c>
-      <c r="C107" s="64">
-        <v>68529.646999999997</v>
-      </c>
-      <c r="D107" s="64">
+      <c r="C107" s="60">
+        <v>71920.963000000003</v>
+      </c>
+      <c r="D107" s="60">
         <v>353078.46800000005</v>
       </c>
-      <c r="E107" s="64">
+      <c r="E107" s="60">
         <v>418115.52799999999</v>
       </c>
-      <c r="F107" s="64">
+      <c r="F107" s="60">
         <v>687724.08499999996</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A108" s="63">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A108" s="59">
         <v>2096</v>
       </c>
-      <c r="B108" s="64">
+      <c r="B108" s="60">
         <v>10225850.874</v>
       </c>
-      <c r="C108" s="64">
-        <v>68529.527000000002</v>
-      </c>
-      <c r="D108" s="64">
+      <c r="C108" s="60">
+        <v>71935.070999999996</v>
+      </c>
+      <c r="D108" s="60">
         <v>352052.02500000008</v>
       </c>
-      <c r="E108" s="64">
+      <c r="E108" s="60">
         <v>418800.09700000001</v>
       </c>
-      <c r="F108" s="64">
+      <c r="F108" s="60">
         <v>676660.87699999998</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A109" s="63">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A109" s="59">
         <v>2097</v>
       </c>
-      <c r="B109" s="64">
+      <c r="B109" s="60">
         <v>10215549.310000001</v>
       </c>
-      <c r="C109" s="64">
-        <v>68523.856</v>
-      </c>
-      <c r="D109" s="64">
+      <c r="C109" s="60">
+        <v>71943.085000000006</v>
+      </c>
+      <c r="D109" s="60">
         <v>351009.62299999996</v>
       </c>
-      <c r="E109" s="64">
+      <c r="E109" s="60">
         <v>419461.01699999999</v>
       </c>
-      <c r="F109" s="64">
+      <c r="F109" s="60">
         <v>665695.50300000003</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A110" s="63">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A110" s="59">
         <v>2098</v>
       </c>
-      <c r="B110" s="64">
+      <c r="B110" s="60">
         <v>10204489.862</v>
       </c>
-      <c r="C110" s="64">
-        <v>68516.588000000003</v>
-      </c>
-      <c r="D110" s="64">
+      <c r="C110" s="60">
+        <v>71948.88</v>
+      </c>
+      <c r="D110" s="60">
         <v>349970.60700000002</v>
       </c>
-      <c r="E110" s="64">
+      <c r="E110" s="60">
         <v>420095.82</v>
       </c>
-      <c r="F110" s="64">
+      <c r="F110" s="60">
         <v>654825.38899999997</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A111" s="63">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A111" s="59">
         <v>2099</v>
       </c>
-      <c r="B111" s="64">
+      <c r="B111" s="60">
         <v>10192689.066</v>
       </c>
-      <c r="C111" s="64">
-        <v>68503.747000000003</v>
-      </c>
-      <c r="D111" s="64">
+      <c r="C111" s="60">
+        <v>71948.638999999996</v>
+      </c>
+      <c r="D111" s="60">
         <v>348929.72599999985</v>
       </c>
-      <c r="E111" s="64">
+      <c r="E111" s="60">
         <v>420702.88799999998</v>
       </c>
-      <c r="F111" s="64">
+      <c r="F111" s="60">
         <v>644049.4</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A112" s="63">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A112" s="59">
         <v>2100</v>
       </c>
-      <c r="B112" s="64">
+      <c r="B112" s="60">
         <v>10180160.751</v>
       </c>
-      <c r="C112" s="64">
-        <v>68484.558000000005</v>
-      </c>
-      <c r="D112" s="64">
+      <c r="C112" s="60">
+        <v>71941.827000000005</v>
+      </c>
+      <c r="D112" s="60">
         <v>347864.81900000002</v>
       </c>
-      <c r="E112" s="64">
+      <c r="E112" s="60">
         <v>421278.88900000002</v>
       </c>
-      <c r="F112" s="64">
+      <c r="F112" s="60">
         <v>633368.11300000001</v>
       </c>
     </row>
-    <row r="113" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B114">
         <f>B31*100/B31</f>
@@ -4260,26 +4790,24 @@
       </c>
       <c r="C114">
         <f>C31*100/B31</f>
-        <v>0.8414670033061149</v>
+        <v>0.86947355490409317</v>
       </c>
       <c r="D114">
         <f>D31*100/B31</f>
         <v>5.7272099641387726</v>
       </c>
-      <c r="E114" s="17">
+      <c r="E114" s="13">
         <f>E31*100/B31</f>
         <v>4.324380570743199</v>
       </c>
-      <c r="F114" s="17">
+      <c r="F114" s="13">
         <f>F31*100/B31</f>
         <v>18.223874457114288</v>
       </c>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
-    </row>
-    <row r="115" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="115" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B115" s="4">
         <f>AVERAGE(B31:B62)</f>
@@ -4287,7 +4815,7 @@
       </c>
       <c r="C115" s="4">
         <f>AVERAGE(C31:C62)</f>
-        <v>67367.388312500014</v>
+        <v>69777.193343750012</v>
       </c>
       <c r="D115" s="4">
         <f>AVERAGE(D31:D62)</f>
@@ -4301,12 +4829,10 @@
         <f t="shared" si="0"/>
         <v>1365292.1845625006</v>
       </c>
-      <c r="G115" s="4"/>
-      <c r="H115" s="4"/>
-    </row>
-    <row r="116" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="116" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="B116" s="5">
         <f>B115/B115</f>
@@ -4314,7 +4840,7 @@
       </c>
       <c r="C116" s="6">
         <f>C115*100/B115</f>
-        <v>0.76437311161945465</v>
+        <v>0.79171557236007672</v>
       </c>
       <c r="D116" s="6">
         <f>D115*100/B115</f>
@@ -4329,34 +4855,34 @@
         <v>15.491065655429644</v>
       </c>
     </row>
-    <row r="117" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B117" s="17">
+        <v>125</v>
+      </c>
+      <c r="B117" s="13">
         <f>B62*100/B62</f>
         <v>100</v>
       </c>
-      <c r="C117" s="17">
+      <c r="C117" s="13">
         <f>C62*100/B62</f>
-        <v>0.70588785803326692</v>
-      </c>
-      <c r="D117" s="17">
+        <v>0.73348552482570495</v>
+      </c>
+      <c r="D117" s="13">
         <f>D62*100/B62</f>
         <v>4.3557414189697248</v>
       </c>
-      <c r="E117" s="17">
+      <c r="E117" s="13">
         <f>E62*100/B62</f>
         <v>3.9407283828087478</v>
       </c>
-      <c r="F117" s="17">
+      <c r="F117" s="13">
         <f>F62*100/B62</f>
         <v>13.040560048995525</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B118" s="4">
         <f>AVERAGE(B31:B112)</f>
@@ -4364,7 +4890,7 @@
       </c>
       <c r="C118" s="4">
         <f>AVERAGE(C31:C112)</f>
-        <v>67796.169865853692</v>
+        <v>70608.229060975602</v>
       </c>
       <c r="D118" s="4">
         <f>AVERAGE(D31:D112)</f>
@@ -4379,9 +4905,9 @@
         <v>1101676.6355609756</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="B119" s="5">
         <f>B118/B118</f>
@@ -4389,7 +4915,7 @@
       </c>
       <c r="C119" s="6">
         <f>C118*100/B118</f>
-        <v>0.70434569054542562</v>
+        <v>0.73356064147203148</v>
       </c>
       <c r="D119" s="6">
         <f>D118*100/B118</f>
@@ -4404,17 +4930,17 @@
         <v>11.445501894389142</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B123" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -4425,39 +4951,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
   <dimension ref="A1:AI76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.19921875" customWidth="1"/>
-    <col min="3" max="3" width="16.46484375" customWidth="1"/>
-    <col min="4" max="4" width="22.06640625" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.23046875" customWidth="1"/>
+    <col min="3" max="3" width="16.4609375" customWidth="1"/>
+    <col min="4" max="4" width="22.07421875" customWidth="1"/>
+    <col min="5" max="5" width="20.69140625" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="17"/>
-    <col min="9" max="10" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.69140625" style="13"/>
+    <col min="9" max="10" width="10.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="F1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
@@ -4488,23 +5014,23 @@
       <c r="AH1" s="7"/>
       <c r="AI1" s="7"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A2" s="57">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A2" s="53">
         <v>1990</v>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="54">
         <v>59746506695071</v>
       </c>
-      <c r="C2" s="58">
+      <c r="C2" s="54">
         <v>2252131019723</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D2" s="54">
         <v>14055046900287</v>
       </c>
-      <c r="E2" s="58">
+      <c r="E2" s="54">
         <v>11079319700573</v>
       </c>
-      <c r="F2" s="58">
+      <c r="F2" s="54">
         <v>1892142389584</v>
       </c>
       <c r="H2" s="7"/>
@@ -4536,23 +5062,23 @@
       <c r="AH2" s="7"/>
       <c r="AI2" s="7"/>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A3" s="57">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A3" s="53">
         <v>1991</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="54">
         <v>60258490453633</v>
       </c>
-      <c r="C3" s="58">
+      <c r="C3" s="54">
         <v>2279982279111</v>
       </c>
-      <c r="D3" s="58">
+      <c r="D3" s="54">
         <v>14163697291311</v>
       </c>
-      <c r="E3" s="58">
+      <c r="E3" s="54">
         <v>11067319371015</v>
       </c>
-      <c r="F3" s="58">
+      <c r="F3" s="54">
         <v>2069542704119</v>
       </c>
       <c r="H3" s="7"/>
@@ -4584,23 +5110,23 @@
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A4" s="57">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A4" s="53">
         <v>1992</v>
       </c>
-      <c r="B4" s="58">
+      <c r="B4" s="54">
         <v>61053199066222</v>
       </c>
-      <c r="C4" s="58">
+      <c r="C4" s="54">
         <v>2314548203919</v>
       </c>
-      <c r="D4" s="58">
+      <c r="D4" s="54">
         <v>14246781423744</v>
       </c>
-      <c r="E4" s="58">
+      <c r="E4" s="54">
         <v>11457165382936</v>
       </c>
-      <c r="F4" s="58">
+      <c r="F4" s="54">
         <v>2365438109816</v>
       </c>
       <c r="H4" s="7"/>
@@ -4632,23 +5158,23 @@
       <c r="AH4" s="7"/>
       <c r="AI4" s="7"/>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A5" s="57">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A5" s="53">
         <v>1993</v>
       </c>
-      <c r="B5" s="58">
+      <c r="B5" s="54">
         <v>61978794358267</v>
       </c>
-      <c r="C5" s="58">
+      <c r="C5" s="54">
         <v>2306239026543</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="54">
         <v>14165170093636</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="54">
         <v>11772443185977</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="54">
         <v>2694851453398</v>
       </c>
       <c r="I5" s="7"/>
@@ -4679,1255 +5205,1255 @@
       <c r="AH5" s="7"/>
       <c r="AI5" s="7"/>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A6" s="57">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A6" s="53">
         <v>1994</v>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="54">
         <v>63652014872828</v>
       </c>
-      <c r="C6" s="58">
+      <c r="C6" s="54">
         <v>2361211943582</v>
       </c>
-      <c r="D6" s="58">
+      <c r="D6" s="54">
         <v>14548276355074</v>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="54">
         <v>12246757597390</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="54">
         <v>3047411115925</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A7" s="57">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A7" s="53">
         <v>1995</v>
       </c>
-      <c r="B7" s="58">
+      <c r="B7" s="54">
         <v>65638271921048</v>
       </c>
-      <c r="C7" s="58">
+      <c r="C7" s="54">
         <v>2415632986071</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="54">
         <v>14965907122544</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="54">
         <v>12575513322951</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="54">
         <v>3383096056447</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A8" s="57">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A8" s="53">
         <v>1996</v>
       </c>
-      <c r="B8" s="58">
+      <c r="B8" s="54">
         <v>68072956904076</v>
       </c>
-      <c r="C8" s="58">
+      <c r="C8" s="54">
         <v>2449381308301</v>
       </c>
-      <c r="D8" s="58">
+      <c r="D8" s="54">
         <v>15272122048686</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="54">
         <v>13049958855286</v>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="54">
         <v>3720501963123</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A9" s="57">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A9" s="53">
         <v>1997</v>
       </c>
-      <c r="B9" s="58">
+      <c r="B9" s="54">
         <v>70778368389422</v>
       </c>
-      <c r="C9" s="58">
+      <c r="C9" s="54">
         <v>2511278683612</v>
       </c>
-      <c r="D9" s="58">
+      <c r="D9" s="54">
         <v>15664417730527</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="54">
         <v>13630307220971</v>
       </c>
-      <c r="F9" s="58">
+      <c r="F9" s="54">
         <v>4066419152961</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A10" s="57">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A10" s="53">
         <v>1998</v>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="54">
         <v>72514571649884</v>
       </c>
-      <c r="C10" s="58">
+      <c r="C10" s="54">
         <v>2597982949374</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="54">
         <v>16123564133041</v>
       </c>
-      <c r="E10" s="58">
+      <c r="E10" s="54">
         <v>14241372070382</v>
       </c>
-      <c r="F10" s="58">
+      <c r="F10" s="54">
         <v>4388623718711</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A11" s="57">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A11" s="53">
         <v>1999</v>
       </c>
-      <c r="B11" s="58">
+      <c r="B11" s="54">
         <v>75129460995882</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="54">
         <v>2686296393899</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="54">
         <v>16590357951915</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="54">
         <v>14923309497831</v>
       </c>
-      <c r="F11" s="58">
+      <c r="F11" s="54">
         <v>4728357537870</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A12" s="57">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A12" s="53">
         <v>2000</v>
       </c>
-      <c r="B12" s="58">
+      <c r="B12" s="54">
         <v>78748266091431</v>
       </c>
-      <c r="C12" s="58">
+      <c r="C12" s="54">
         <v>2797535926604</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="54">
         <v>17242731410767</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="54">
         <v>15531820240832</v>
       </c>
-      <c r="F12" s="58">
+      <c r="F12" s="54">
         <v>5133746736757</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A13" s="57">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A13" s="53">
         <v>2001</v>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="54">
         <v>80651158295443</v>
       </c>
-      <c r="C13" s="58">
+      <c r="C13" s="54">
         <v>2850674198675</v>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="54">
         <v>17630418686268</v>
       </c>
-      <c r="E13" s="58">
+      <c r="E13" s="54">
         <v>15680232737760</v>
       </c>
-      <c r="F13" s="58">
+      <c r="F13" s="54">
         <v>5561082225597</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A14" s="57">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A14" s="53">
         <v>2002</v>
       </c>
-      <c r="B14" s="58">
+      <c r="B14" s="54">
         <v>82913446416271</v>
       </c>
-      <c r="C14" s="58">
+      <c r="C14" s="54">
         <v>2881112280148</v>
       </c>
-      <c r="D14" s="58">
+      <c r="D14" s="54">
         <v>17850581067931</v>
       </c>
-      <c r="E14" s="58">
+      <c r="E14" s="54">
         <v>15946866836810</v>
       </c>
-      <c r="F14" s="58">
+      <c r="F14" s="54">
         <v>6074706488414</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A15" s="57">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A15" s="53">
         <v>2003</v>
       </c>
-      <c r="B15" s="58">
+      <c r="B15" s="54">
         <v>85953247177967</v>
       </c>
-      <c r="C15" s="58">
+      <c r="C15" s="54">
         <v>2908996467956</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D15" s="54">
         <v>18048815545511</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E15" s="54">
         <v>16392678397137</v>
       </c>
-      <c r="F15" s="58">
+      <c r="F15" s="54">
         <v>6689090876282</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A16" s="57">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A16" s="53">
         <v>2004</v>
       </c>
-      <c r="B16" s="58">
+      <c r="B16" s="54">
         <v>90382276783126</v>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="54">
         <v>2992433774420</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D16" s="54">
         <v>18551610186281</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E16" s="54">
         <v>17023431236173</v>
       </c>
-      <c r="F16" s="58">
+      <c r="F16" s="54">
         <v>7367393399861</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" s="57">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" s="53">
         <v>2005</v>
       </c>
-      <c r="B17" s="58">
+      <c r="B17" s="54">
         <v>94536020338349</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="54">
         <v>3048947856501</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D17" s="54">
         <v>18946844284538</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="54">
         <v>17616450964293</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F17" s="54">
         <v>8211218760901</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" s="57">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" s="53">
         <v>2006</v>
       </c>
-      <c r="B18" s="58">
+      <c r="B18" s="54">
         <v>99458127988160</v>
       </c>
-      <c r="C18" s="58">
+      <c r="C18" s="54">
         <v>3131698267519</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="54">
         <v>19653724210861</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="54">
         <v>18106988023981</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F18" s="54">
         <v>9252014077441</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" s="57">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" s="53">
         <v>2007</v>
       </c>
-      <c r="B19" s="58">
+      <c r="B19" s="54">
         <v>104664529164622</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="54">
         <v>3210945324824</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="54">
         <v>20305277396116</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="54">
         <v>18469826407095</v>
       </c>
-      <c r="F19" s="58">
+      <c r="F19" s="54">
         <v>10561245407110</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="57">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" s="53">
         <v>2008</v>
       </c>
-      <c r="B20" s="58">
+      <c r="B20" s="54">
         <v>107616102342598</v>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="54">
         <v>3223152421770</v>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="54">
         <v>20481942205927</v>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="54">
         <v>18490805774529</v>
       </c>
-      <c r="F20" s="58">
+      <c r="F20" s="54">
         <v>11582388576956</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="57">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" s="53">
         <v>2009</v>
       </c>
-      <c r="B21" s="58">
+      <c r="B21" s="54">
         <v>106900393523163</v>
       </c>
-      <c r="C21" s="58">
+      <c r="C21" s="54">
         <v>3132112820496</v>
       </c>
-      <c r="D21" s="58">
+      <c r="D21" s="54">
         <v>19611106610198</v>
       </c>
-      <c r="E21" s="58">
+      <c r="E21" s="54">
         <v>18014390119987</v>
       </c>
-      <c r="F21" s="58">
+      <c r="F21" s="54">
         <v>12671839645498</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" s="57">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" s="53">
         <v>2010</v>
       </c>
-      <c r="B22" s="58">
+      <c r="B22" s="54">
         <v>112369774826691</v>
       </c>
-      <c r="C22" s="58">
+      <c r="C22" s="54">
         <v>3194765248768</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="54">
         <v>20004956152632</v>
       </c>
-      <c r="E22" s="58">
+      <c r="E22" s="54">
         <v>18499912627047</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F22" s="54">
         <v>14014001667285</v>
       </c>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" s="57">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="53">
         <v>2011</v>
       </c>
-      <c r="B23" s="58">
+      <c r="B23" s="54">
         <v>116779323374085</v>
       </c>
-      <c r="C23" s="58">
+      <c r="C23" s="54">
         <v>3272640096894</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="54">
         <v>20396009895487</v>
       </c>
-      <c r="E23" s="58">
+      <c r="E23" s="54">
         <v>18789326527808</v>
       </c>
-      <c r="F23" s="58">
+      <c r="F23" s="54">
         <v>15340013860010</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24" s="57">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="53">
         <v>2012</v>
       </c>
-      <c r="B24" s="58">
+      <c r="B24" s="54">
         <v>120457639815694</v>
       </c>
-      <c r="C24" s="58">
+      <c r="C24" s="54">
         <v>3278656363487</v>
       </c>
-      <c r="D24" s="58">
+      <c r="D24" s="54">
         <v>20241900939245</v>
       </c>
-      <c r="E24" s="58">
+      <c r="E24" s="54">
         <v>19219435517265</v>
       </c>
-      <c r="F24" s="58">
+      <c r="F24" s="54">
         <v>16545404559826</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A25" s="57">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="53">
         <v>2013</v>
       </c>
-      <c r="B25" s="58">
+      <c r="B25" s="54">
         <v>124396248689855</v>
       </c>
-      <c r="C25" s="58">
+      <c r="C25" s="54">
         <v>3304287470959</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="54">
         <v>20229842702374</v>
       </c>
-      <c r="E25" s="58">
+      <c r="E25" s="54">
         <v>19626470506630</v>
       </c>
-      <c r="F25" s="58">
+      <c r="F25" s="54">
         <v>17832377196873</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" s="57">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="53">
         <v>2014</v>
       </c>
-      <c r="B26" s="58">
+      <c r="B26" s="54">
         <v>128707260097480</v>
       </c>
-      <c r="C26" s="58">
+      <c r="C26" s="54">
         <v>3337258740017</v>
       </c>
-      <c r="D26" s="58">
+      <c r="D26" s="54">
         <v>20576138491055</v>
       </c>
-      <c r="E26" s="58">
+      <c r="E26" s="54">
         <v>20121807258768</v>
       </c>
-      <c r="F26" s="58">
+      <c r="F26" s="54">
         <v>19162852171599</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" s="57">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="53">
         <v>2015</v>
       </c>
-      <c r="B27" s="58">
+      <c r="B27" s="54">
         <v>132979475190067</v>
       </c>
-      <c r="C27" s="58">
+      <c r="C27" s="54">
         <v>3372859106074</v>
       </c>
-      <c r="D27" s="58">
+      <c r="D27" s="54">
         <v>21076145421659</v>
       </c>
-      <c r="E27" s="58">
+      <c r="E27" s="54">
         <v>20714505243484</v>
       </c>
-      <c r="F27" s="58">
+      <c r="F27" s="54">
         <v>20500730181113</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" s="57">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="53">
         <v>2016</v>
       </c>
-      <c r="B28" s="58">
+      <c r="B28" s="54">
         <v>137269733552341</v>
       </c>
-      <c r="C28" s="58">
+      <c r="C28" s="54">
         <v>3401866742516</v>
       </c>
-      <c r="D28" s="58">
+      <c r="D28" s="54">
         <v>21494116675138</v>
       </c>
-      <c r="E28" s="58">
+      <c r="E28" s="54">
         <v>21091395615523</v>
       </c>
-      <c r="F28" s="58">
+      <c r="F28" s="54">
         <v>21889385822096</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" s="57">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="53">
         <v>2017</v>
       </c>
-      <c r="B29" s="58">
+      <c r="B29" s="54">
         <v>142488808751000</v>
       </c>
-      <c r="C29" s="58">
+      <c r="C29" s="54">
         <v>3472748543480</v>
       </c>
-      <c r="D29" s="58">
+      <c r="D29" s="54">
         <v>22134351131538</v>
       </c>
-      <c r="E29" s="58">
+      <c r="E29" s="54">
         <v>21609742457818</v>
       </c>
-      <c r="F29" s="58">
+      <c r="F29" s="54">
         <v>23397835751145</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A30" s="57">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30" s="53">
         <v>2018</v>
       </c>
-      <c r="B30" s="58">
+      <c r="B30" s="54">
         <v>147685397273163</v>
       </c>
-      <c r="C30" s="58">
+      <c r="C30" s="54">
         <v>3529906814718</v>
       </c>
-      <c r="D30" s="58">
+      <c r="D30" s="54">
         <v>22631771734001</v>
       </c>
-      <c r="E30" s="58">
+      <c r="E30" s="54">
         <v>22250796562799</v>
       </c>
-      <c r="F30" s="58">
+      <c r="F30" s="54">
         <v>24979016132707</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A31" s="57">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" s="53">
         <v>2019</v>
       </c>
-      <c r="B31" s="58">
+      <c r="B31" s="54">
         <v>152051967520231</v>
       </c>
-      <c r="C31" s="58">
+      <c r="C31" s="54">
         <v>3601473785623</v>
       </c>
-      <c r="D31" s="58">
+      <c r="D31" s="54">
         <v>23088322198062</v>
       </c>
-      <c r="E31" s="58">
+      <c r="E31" s="54">
         <v>22825718280632</v>
       </c>
-      <c r="F31" s="58">
+      <c r="F31" s="54">
         <v>26494587477980</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A32" s="57">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32" s="53">
         <v>2020</v>
       </c>
-      <c r="B32" s="58">
+      <c r="B32" s="54">
         <v>147750738921631</v>
       </c>
-      <c r="C32" s="58">
+      <c r="C32" s="54">
         <v>3333500874072</v>
       </c>
-      <c r="D32" s="58">
+      <c r="D32" s="54">
         <v>21793679288788</v>
       </c>
-      <c r="E32" s="58">
+      <c r="E32" s="54">
         <v>22350629263579</v>
       </c>
-      <c r="F32" s="58">
+      <c r="F32" s="54">
         <v>27114429372607</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A33" s="57">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A33" s="53">
         <v>2021</v>
       </c>
-      <c r="B33" s="58">
+      <c r="B33" s="54">
         <v>157405903630917</v>
       </c>
-      <c r="C33" s="58">
+      <c r="C33" s="54">
         <v>3562923665911</v>
       </c>
-      <c r="D33" s="58">
+      <c r="D33" s="54">
         <v>23189787125040</v>
       </c>
-      <c r="E33" s="58">
+      <c r="E33" s="54">
         <v>23725645000000</v>
       </c>
-      <c r="F33" s="58">
+      <c r="F33" s="54">
         <v>29438240129870</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="57">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A34" s="53">
         <v>2022</v>
       </c>
-      <c r="B34" s="58">
+      <c r="B34" s="54">
         <v>163140044693829</v>
       </c>
-      <c r="C34" s="58">
+      <c r="C34" s="54">
         <v>3659719845025</v>
       </c>
-      <c r="D34" s="58">
+      <c r="D34" s="54">
         <v>24049416863216</v>
       </c>
-      <c r="E34" s="58">
+      <c r="E34" s="54">
         <v>24324531017266</v>
       </c>
-      <c r="F34" s="58">
+      <c r="F34" s="54">
         <v>30360791708735</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A35" s="57">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A35" s="53">
         <v>2023</v>
       </c>
-      <c r="B35" s="58">
+      <c r="B35" s="54">
         <v>168473707388178</v>
       </c>
-      <c r="C35" s="58">
+      <c r="C35" s="54">
         <v>3712391079957</v>
       </c>
-      <c r="D35" s="58">
+      <c r="D35" s="54">
         <v>24178427617055</v>
       </c>
-      <c r="E35" s="58">
+      <c r="E35" s="54">
         <v>25038301109944</v>
       </c>
-      <c r="F35" s="58">
+      <c r="F35" s="54">
         <v>32005133203227</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A36" s="57">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A36" s="53">
         <v>2024</v>
       </c>
-      <c r="B36" s="58">
+      <c r="B36" s="54">
         <v>174159721560706</v>
       </c>
-      <c r="C36" s="58">
+      <c r="C36" s="54">
         <v>3756585907158</v>
       </c>
-      <c r="D36" s="58">
+      <c r="D36" s="54">
         <v>24466131679265</v>
       </c>
-      <c r="E36" s="58">
+      <c r="E36" s="54">
         <v>25737667720037</v>
       </c>
-      <c r="F36" s="58">
+      <c r="F36" s="54">
         <v>33592044935159</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="57">
+    <row r="37" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="53">
         <v>2025</v>
       </c>
-      <c r="B37" s="58">
+      <c r="B37" s="54">
         <v>180028791385506</v>
       </c>
-      <c r="C37" s="58">
+      <c r="C37" s="54">
         <v>3788176914672</v>
       </c>
-      <c r="D37" s="58">
+      <c r="D37" s="54">
         <v>24851249652329</v>
       </c>
-      <c r="E37" s="58">
+      <c r="E37" s="54">
         <v>26293957026094</v>
       </c>
-      <c r="F37" s="58">
+      <c r="F37" s="54">
         <v>35258193185781</v>
       </c>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-    </row>
-    <row r="38" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="61">
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
+    </row>
+    <row r="38" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="57">
         <v>2026</v>
       </c>
-      <c r="B38" s="62">
+      <c r="B38" s="58">
         <v>185613362588448</v>
       </c>
-      <c r="C38" s="62">
+      <c r="C38" s="58">
         <v>3847211671289</v>
       </c>
-      <c r="D38" s="62">
+      <c r="D38" s="58">
         <v>25266462332861</v>
       </c>
-      <c r="E38" s="62">
+      <c r="E38" s="58">
         <v>26785348656778</v>
       </c>
-      <c r="F38" s="62">
+      <c r="F38" s="58">
         <v>36578487945445</v>
       </c>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="53"/>
-      <c r="K38" s="53"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A39" s="61">
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="49"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A39" s="57">
         <v>2027</v>
       </c>
-      <c r="B39" s="62">
+      <c r="B39" s="58">
         <v>191371169612619</v>
       </c>
-      <c r="C39" s="62">
+      <c r="C39" s="58">
         <v>3907166422555</v>
       </c>
-      <c r="D39" s="62">
+      <c r="D39" s="58">
         <v>25688612353466</v>
       </c>
-      <c r="E39" s="62">
+      <c r="E39" s="58">
         <v>27285923604162</v>
       </c>
-      <c r="F39" s="62">
+      <c r="F39" s="58">
         <v>37948223078959</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A40" s="61">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A40" s="57">
         <v>2028</v>
       </c>
-      <c r="B40" s="62">
+      <c r="B40" s="58">
         <v>197307586308343</v>
       </c>
-      <c r="C40" s="62">
+      <c r="C40" s="58">
         <v>3968055505619</v>
       </c>
-      <c r="D40" s="62">
+      <c r="D40" s="58">
         <v>26117815622664</v>
       </c>
-      <c r="E40" s="62">
+      <c r="E40" s="58">
         <v>27795853489620</v>
       </c>
-      <c r="F40" s="62">
+      <c r="F40" s="58">
         <v>39369249953641</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A41" s="61">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A41" s="57">
         <v>2029</v>
       </c>
-      <c r="B41" s="62">
+      <c r="B41" s="58">
         <v>203428153225109</v>
       </c>
-      <c r="C41" s="62">
+      <c r="C41" s="58">
         <v>4029893481061</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="58">
         <v>26554189985565</v>
       </c>
-      <c r="E41" s="62">
+      <c r="E41" s="58">
         <v>28315313141849</v>
       </c>
-      <c r="F41" s="62">
+      <c r="F41" s="58">
         <v>40843489263971</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A42" s="61">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A42" s="57">
         <v>2030</v>
       </c>
-      <c r="B42" s="62">
+      <c r="B42" s="58">
         <v>209738582782655</v>
       </c>
-      <c r="C42" s="62">
+      <c r="C42" s="58">
         <v>4092695136370</v>
       </c>
-      <c r="D42" s="62">
+      <c r="D42" s="58">
         <v>26997855256225</v>
       </c>
-      <c r="E42" s="62">
+      <c r="E42" s="58">
         <v>28844480656814</v>
       </c>
-      <c r="F42" s="62">
+      <c r="F42" s="58">
         <v>42372933627653</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A43" s="61">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A43" s="57">
         <v>2031</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="58">
         <v>215595098179775</v>
       </c>
-      <c r="C43" s="62">
+      <c r="C43" s="58">
         <v>4146550170992</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="58">
         <v>27393032292760</v>
       </c>
-      <c r="E43" s="62">
+      <c r="E43" s="58">
         <v>29289437645355</v>
       </c>
-      <c r="F43" s="62">
+      <c r="F43" s="58">
         <v>43593096339827</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A44" s="61">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="57">
         <v>2032</v>
       </c>
-      <c r="B44" s="62">
+      <c r="B44" s="58">
         <v>221615144636090</v>
       </c>
-      <c r="C44" s="62">
+      <c r="C44" s="58">
         <v>4201113874267</v>
       </c>
-      <c r="D44" s="62">
+      <c r="D44" s="58">
         <v>27793993673597</v>
       </c>
-      <c r="E44" s="62">
+      <c r="E44" s="58">
         <v>29741258571716</v>
       </c>
-      <c r="F44" s="62">
+      <c r="F44" s="58">
         <v>44848394618899</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A45" s="61">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="57">
         <v>2033</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="58">
         <v>227803288417633</v>
       </c>
-      <c r="C45" s="62">
+      <c r="C45" s="58">
         <v>4256395571439</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="58">
         <v>28200824066202</v>
       </c>
-      <c r="E45" s="62">
+      <c r="E45" s="58">
         <v>30200049319483</v>
       </c>
-      <c r="F45" s="62">
+      <c r="F45" s="58">
         <v>46139840221786</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A46" s="61">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A46" s="57">
         <v>2034</v>
       </c>
-      <c r="B46" s="62">
+      <c r="B46" s="58">
         <v>234164223293954</v>
       </c>
-      <c r="C46" s="62">
+      <c r="C46" s="58">
         <v>4312404710460</v>
       </c>
-      <c r="D46" s="62">
+      <c r="D46" s="58">
         <v>28613609377352</v>
       </c>
-      <c r="E46" s="62">
+      <c r="E46" s="58">
         <v>30665917405613</v>
       </c>
-      <c r="F46" s="62">
+      <c r="F46" s="58">
         <v>47468474039756</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A47" s="61">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A47" s="57">
         <v>2035</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="58">
         <v>240702774098393</v>
       </c>
-      <c r="C47" s="62">
+      <c r="C47" s="58">
         <v>4369150863605</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="58">
         <v>29032436771269</v>
       </c>
-      <c r="E47" s="62">
+      <c r="E47" s="58">
         <v>31138972005625</v>
       </c>
-      <c r="F47" s="62">
+      <c r="F47" s="58">
         <v>48835366937379</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A48" s="61">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A48" s="57">
         <v>2036</v>
       </c>
-      <c r="B48" s="62">
+      <c r="B48" s="58">
         <v>246643680941786</v>
       </c>
-      <c r="C48" s="62">
+      <c r="C48" s="58">
         <v>4424116315805</v>
       </c>
-      <c r="D48" s="62">
+      <c r="D48" s="58">
         <v>29430112863175</v>
       </c>
-      <c r="E48" s="62">
+      <c r="E48" s="58">
         <v>31558582849020</v>
       </c>
-      <c r="F48" s="62">
+      <c r="F48" s="58">
         <v>49829940141406</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A49" s="61">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A49" s="57">
         <v>2037</v>
       </c>
-      <c r="B49" s="62">
+      <c r="B49" s="58">
         <v>252731218310124</v>
       </c>
-      <c r="C49" s="62">
+      <c r="C49" s="58">
         <v>4479773252696</v>
       </c>
-      <c r="D49" s="62">
+      <c r="D49" s="58">
         <v>29833236182101</v>
       </c>
-      <c r="E49" s="62">
+      <c r="E49" s="58">
         <v>31983848126346</v>
       </c>
-      <c r="F49" s="62">
+      <c r="F49" s="58">
         <v>50844768662843</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A50" s="61">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A50" s="57">
         <v>2038</v>
       </c>
-      <c r="B50" s="62">
+      <c r="B50" s="58">
         <v>258969005265516</v>
       </c>
-      <c r="C50" s="62">
+      <c r="C50" s="58">
         <v>4536130373399</v>
       </c>
-      <c r="D50" s="62">
+      <c r="D50" s="58">
         <v>30241881342246</v>
       </c>
-      <c r="E50" s="62">
+      <c r="E50" s="58">
         <v>32414844033496</v>
       </c>
-      <c r="F50" s="62">
+      <c r="F50" s="58">
         <v>51880265018217</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A51" s="61">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A51" s="57">
         <v>2039</v>
       </c>
-      <c r="B51" s="62">
+      <c r="B51" s="58">
         <v>265360750193972</v>
       </c>
-      <c r="C51" s="62">
+      <c r="C51" s="58">
         <v>4593196486471</v>
       </c>
-      <c r="D51" s="62">
+      <c r="D51" s="58">
         <v>30656123979845</v>
       </c>
-      <c r="E51" s="62">
+      <c r="E51" s="58">
         <v>32851647793136</v>
       </c>
-      <c r="F51" s="62">
+      <c r="F51" s="58">
         <v>52936850125299</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A52" s="61">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A52" s="57">
         <v>2040</v>
       </c>
-      <c r="B52" s="62">
+      <c r="B52" s="58">
         <v>271910253010050</v>
       </c>
-      <c r="C52" s="62">
+      <c r="C52" s="58">
         <v>4650980511286</v>
       </c>
-      <c r="D52" s="62">
+      <c r="D52" s="58">
         <v>31076040767172</v>
       </c>
-      <c r="E52" s="62">
+      <c r="E52" s="58">
         <v>33294337668540</v>
       </c>
-      <c r="F52" s="62">
+      <c r="F52" s="58">
         <v>54014953474205</v>
       </c>
-      <c r="H52" s="53"/>
-      <c r="I52" s="53"/>
-      <c r="J52" s="53"/>
-      <c r="K52" s="53"/>
-      <c r="L52" s="53"/>
-      <c r="M52" s="53"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A53" s="61">
+      <c r="H52" s="49"/>
+      <c r="I52" s="49"/>
+      <c r="J52" s="49"/>
+      <c r="K52" s="49"/>
+      <c r="L52" s="49"/>
+      <c r="M52" s="49"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A53" s="57">
         <v>2041</v>
       </c>
-      <c r="B53" s="62">
+      <c r="B53" s="58">
         <v>278169312765321</v>
       </c>
-      <c r="C53" s="62">
+      <c r="C53" s="58">
         <v>4707133864249</v>
       </c>
-      <c r="D53" s="62">
+      <c r="D53" s="58">
         <v>31464874770701</v>
       </c>
-      <c r="E53" s="62">
+      <c r="E53" s="58">
         <v>33703559031431</v>
       </c>
-      <c r="F53" s="62">
+      <c r="F53" s="58">
         <v>54972135673960</v>
       </c>
-      <c r="H53" s="53"/>
-      <c r="I53" s="53"/>
-      <c r="J53" s="53"/>
-      <c r="K53" s="53"/>
-      <c r="L53" s="53"/>
-      <c r="M53" s="53"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A54" s="61">
+      <c r="H53" s="49"/>
+      <c r="I53" s="49"/>
+      <c r="J53" s="49"/>
+      <c r="K53" s="49"/>
+      <c r="L53" s="49"/>
+      <c r="M53" s="49"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A54" s="57">
         <v>2042</v>
       </c>
-      <c r="B54" s="62">
+      <c r="B54" s="58">
         <v>284572448842050</v>
       </c>
-      <c r="C54" s="62">
+      <c r="C54" s="58">
         <v>4763965181578</v>
       </c>
-      <c r="D54" s="62">
+      <c r="D54" s="58">
         <v>31858573997680</v>
       </c>
-      <c r="E54" s="62">
+      <c r="E54" s="58">
         <v>34117810142188</v>
       </c>
-      <c r="F54" s="62">
+      <c r="F54" s="58">
         <v>55946279801933</v>
       </c>
-      <c r="H54" s="53"/>
-      <c r="I54" s="53"/>
-      <c r="J54" s="53"/>
-      <c r="K54" s="53"/>
-      <c r="L54" s="53"/>
-      <c r="M54" s="53"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A55" s="61">
+      <c r="H54" s="49"/>
+      <c r="I54" s="49"/>
+      <c r="J54" s="49"/>
+      <c r="K54" s="49"/>
+      <c r="L54" s="49"/>
+      <c r="M54" s="49"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A55" s="57">
         <v>2043</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="58">
         <v>291122977710634</v>
       </c>
-      <c r="C55" s="62">
+      <c r="C55" s="58">
         <v>4821482648637</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="58">
         <v>32257199323442</v>
       </c>
-      <c r="E55" s="62">
+      <c r="E55" s="58">
         <v>34537152821542</v>
       </c>
-      <c r="F55" s="62">
+      <c r="F55" s="58">
         <v>56937686435181</v>
       </c>
-      <c r="H55" s="53"/>
-      <c r="I55" s="53"/>
-      <c r="J55" s="53"/>
-      <c r="K55" s="53"/>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A56" s="61">
+      <c r="H55" s="49"/>
+      <c r="I55" s="49"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
+      <c r="L55" s="49"/>
+      <c r="M55" s="49"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A56" s="57">
         <v>2044</v>
       </c>
-      <c r="B56" s="62">
+      <c r="B56" s="58">
         <v>297824292182789</v>
       </c>
-      <c r="C56" s="62">
+      <c r="C56" s="58">
         <v>4879694549615</v>
       </c>
-      <c r="D56" s="62">
+      <c r="D56" s="58">
         <v>32660812385013</v>
       </c>
-      <c r="E56" s="62">
+      <c r="E56" s="58">
         <v>34961649650063</v>
       </c>
-      <c r="F56" s="62">
+      <c r="F56" s="58">
         <v>57946661477194</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A57" s="61">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A57" s="57">
         <v>2045</v>
       </c>
-      <c r="B57" s="62">
+      <c r="B57" s="58">
         <v>304679863168833</v>
       </c>
-      <c r="C57" s="62">
+      <c r="C57" s="58">
         <v>4938609268723</v>
       </c>
-      <c r="D57" s="62">
+      <c r="D57" s="58">
         <v>33069475590641</v>
       </c>
-      <c r="E57" s="62">
+      <c r="E57" s="58">
         <v>35391363977500</v>
       </c>
-      <c r="F57" s="62">
+      <c r="F57" s="58">
         <v>58973516252283</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A58" s="61">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A58" s="57">
         <v>2046</v>
       </c>
-      <c r="B58" s="62">
+      <c r="B58" s="58">
         <v>311271173147336</v>
       </c>
-      <c r="C58" s="62">
+      <c r="C58" s="58">
         <v>4996915126985</v>
       </c>
-      <c r="D58" s="62">
+      <c r="D58" s="58">
         <v>33449062869246</v>
       </c>
-      <c r="E58" s="62">
+      <c r="E58" s="58">
         <v>35797424235974</v>
       </c>
-      <c r="F58" s="62">
+      <c r="F58" s="58">
         <v>59871715719212</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A59" s="61">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A59" s="57">
         <v>2047</v>
       </c>
-      <c r="B59" s="62">
+      <c r="B59" s="58">
         <v>318005076623094</v>
       </c>
-      <c r="C59" s="62">
+      <c r="C59" s="58">
         <v>5055909351732</v>
       </c>
-      <c r="D59" s="62">
+      <c r="D59" s="58">
         <v>33833007232429</v>
       </c>
-      <c r="E59" s="62">
+      <c r="E59" s="58">
         <v>36208143397495</v>
       </c>
-      <c r="F59" s="62">
+      <c r="F59" s="58">
         <v>60783595263805</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A60" s="61">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A60" s="57">
         <v>2048</v>
       </c>
-      <c r="B60" s="62">
+      <c r="B60" s="58">
         <v>324884658401031</v>
       </c>
-      <c r="C60" s="62">
+      <c r="C60" s="58">
         <v>5115600069908</v>
       </c>
-      <c r="D60" s="62">
+      <c r="D60" s="58">
         <v>34221358692892</v>
       </c>
-      <c r="E60" s="62">
+      <c r="E60" s="58">
         <v>36623574915653</v>
       </c>
-      <c r="F60" s="62">
+      <c r="F60" s="58">
         <v>61709363241255</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="61">
+    <row r="61" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="57">
         <v>2049</v>
       </c>
-      <c r="B61" s="62">
+      <c r="B61" s="58">
         <v>331913070021377</v>
       </c>
-      <c r="C61" s="62">
+      <c r="C61" s="58">
         <v>5175995504406</v>
       </c>
-      <c r="D61" s="62">
+      <c r="D61" s="58">
         <v>34614167837410</v>
       </c>
-      <c r="E61" s="62">
+      <c r="E61" s="58">
         <v>37043772857329</v>
       </c>
-      <c r="F61" s="62">
+      <c r="F61" s="58">
         <v>62649231180123</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="61">
+    <row r="62" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="57">
         <v>2050</v>
       </c>
-      <c r="B62" s="62">
+      <c r="B62" s="58">
         <v>339093531203398</v>
       </c>
-      <c r="C62" s="62">
+      <c r="C62" s="58">
         <v>5237103975196</v>
       </c>
-      <c r="D62" s="62">
+      <c r="D62" s="58">
         <v>35011485833414</v>
       </c>
-      <c r="E62" s="62">
+      <c r="E62" s="58">
         <v>37468791909741</v>
       </c>
-      <c r="F62" s="62">
+      <c r="F62" s="58">
         <v>63603413830667</v>
       </c>
     </row>
-    <row r="63" spans="1:13" s="53" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="59"/>
-      <c r="B63" s="60"/>
-      <c r="C63" s="60"/>
-      <c r="D63" s="60"/>
-      <c r="E63" s="60"/>
-      <c r="F63" s="60"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A64" s="52">
+    <row r="63" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="55"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="56"/>
+      <c r="D63" s="56"/>
+      <c r="E63" s="56"/>
+      <c r="F63" s="56"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A64" s="48">
         <v>2019</v>
       </c>
       <c r="B64">
         <f>B31/Population!B31</f>
         <v>19465657.469666302</v>
       </c>
-      <c r="C64" s="17">
+      <c r="C64" s="13">
         <f>C31/Population!C31</f>
-        <v>54792384.425726064</v>
-      </c>
-      <c r="D64" s="17">
+        <v>53027470.780060753</v>
+      </c>
+      <c r="D64" s="13">
         <f>D31/Population!D31</f>
         <v>51609101.973367676</v>
       </c>
-      <c r="E64" s="17">
+      <c r="E64" s="13">
         <f>E31/Population!E31</f>
         <v>67573681.142708093</v>
       </c>
-      <c r="F64" s="17">
+      <c r="F64" s="13">
         <f>F31/Population!F31</f>
         <v>18612018.681500316</v>
       </c>
-      <c r="H64" s="53"/>
-      <c r="I64" s="53"/>
-      <c r="J64" s="53"/>
-      <c r="K64" s="53"/>
-      <c r="L64" s="53"/>
-      <c r="M64" s="53"/>
-    </row>
-    <row r="65" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" s="17">
+      <c r="H64" s="49"/>
+      <c r="I64" s="49"/>
+      <c r="J64" s="49"/>
+      <c r="K64" s="49"/>
+      <c r="L64" s="49"/>
+      <c r="M64" s="49"/>
+    </row>
+    <row r="65" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" s="13">
         <v>1</v>
       </c>
-      <c r="C65" s="17">
+      <c r="C65" s="13">
         <f>C64/B64</f>
-        <v>2.8148232090855427</v>
-      </c>
-      <c r="D65" s="17">
+        <v>2.724155136434228</v>
+      </c>
+      <c r="D65" s="13">
         <f>D64/B64</f>
         <v>2.6512899476316742</v>
       </c>
-      <c r="E65" s="17">
+      <c r="E65" s="13">
         <f>E64/B64</f>
         <v>3.4714307106250804</v>
       </c>
-      <c r="F65" s="17">
+      <c r="F65" s="13">
         <f>F64/B64</f>
         <v>0.95614641891771557</v>
       </c>
-      <c r="H65" s="53"/>
-      <c r="I65" s="65"/>
-      <c r="J65" s="66"/>
-      <c r="K65" s="67"/>
-      <c r="L65" s="53"/>
-      <c r="M65" s="53"/>
-    </row>
-    <row r="66" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="H65" s="49"/>
+      <c r="I65" s="62"/>
+      <c r="J65" s="63"/>
+      <c r="K65" s="64"/>
+      <c r="L65" s="49"/>
+      <c r="M65" s="49"/>
+    </row>
+    <row r="66" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A66" s="3" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="B66">
         <f>SUM(B2:B31)/SUM(Population!B2:B31)</f>
@@ -5935,241 +6461,241 @@
       </c>
       <c r="C66">
         <f>SUM(C2:C31)/SUM(Population!C2:C31)</f>
-        <v>47862650.924622238</v>
-      </c>
-      <c r="D66" s="17">
+        <v>46375102.355172761</v>
+      </c>
+      <c r="D66" s="13">
         <f>SUM(D2:D31)/SUM(Population!D2:D31)</f>
         <v>42243264.776802398</v>
       </c>
-      <c r="E66" s="17">
+      <c r="E66" s="13">
         <f>SUM(E2:E31)/SUM(Population!E2:E31)</f>
         <v>56694165.181799427</v>
       </c>
-      <c r="F66" s="17">
+      <c r="F66" s="13">
         <f>SUM(F2:F31)/SUM(Population!F2:F31)</f>
         <v>8075380.8224280654</v>
       </c>
-      <c r="H66" s="53"/>
-      <c r="I66" s="54"/>
-      <c r="J66" s="54"/>
-      <c r="K66" s="54"/>
-      <c r="L66" s="53"/>
-      <c r="M66" s="53"/>
-    </row>
-    <row r="67" spans="1:13" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="H66" s="49"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="49"/>
+      <c r="M66" s="49"/>
+    </row>
+    <row r="67" spans="1:13" s="13" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A67" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B67" s="17">
+        <v>116</v>
+      </c>
+      <c r="B67" s="13">
         <v>1</v>
       </c>
-      <c r="C67" s="17">
+      <c r="C67" s="13">
         <f>C66/B66</f>
-        <v>3.2422911707573405</v>
-      </c>
-      <c r="D67" s="17">
+        <v>3.1415222935717773</v>
+      </c>
+      <c r="D67" s="13">
         <f>D66/B66</f>
         <v>2.8616251244732323</v>
       </c>
-      <c r="E67" s="17">
+      <c r="E67" s="13">
         <f>E66/B66</f>
         <v>3.8405518217513426</v>
       </c>
-      <c r="F67" s="17">
+      <c r="F67" s="13">
         <f>F66/B66</f>
         <v>0.54703898416107877</v>
       </c>
-      <c r="H67" s="53"/>
-      <c r="I67" s="55"/>
-      <c r="J67" s="55"/>
-      <c r="K67" s="56"/>
-      <c r="L67" s="53"/>
-      <c r="M67" s="53"/>
-    </row>
-    <row r="68" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="H67" s="49"/>
+      <c r="I67" s="51"/>
+      <c r="J67" s="51"/>
+      <c r="K67" s="52"/>
+      <c r="L67" s="49"/>
+      <c r="M67" s="49"/>
+    </row>
+    <row r="68" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A68" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B68" s="17">
+        <v>80</v>
+      </c>
+      <c r="B68" s="13">
         <f>SUM(B31:B62)/SUM(Population!B31:B62)</f>
         <v>27115978.877288565</v>
       </c>
-      <c r="C68" s="17">
+      <c r="C68" s="13">
         <f>SUM(C31:C62)/SUM(Population!C31:C62)</f>
-        <v>64442352.709823705</v>
-      </c>
-      <c r="D68" s="17">
+        <v>62216790.196572669</v>
+      </c>
+      <c r="D68" s="13">
         <f>SUM(D31:D62)/SUM(Population!D31:D62)</f>
         <v>65590894.572723262</v>
       </c>
-      <c r="E68" s="17">
+      <c r="E68" s="13">
         <f>SUM(E31:E62)/SUM(Population!E31:E62)</f>
         <v>84627670.362325758</v>
       </c>
-      <c r="F68" s="17">
+      <c r="F68" s="13">
         <f>SUM(F31:F62)/SUM(Population!F31:F62)</f>
         <v>34222558.94297301</v>
       </c>
-      <c r="H68" s="53"/>
-      <c r="I68" s="55"/>
-      <c r="J68" s="55"/>
-      <c r="K68" s="56"/>
-      <c r="L68" s="53"/>
-      <c r="M68" s="53"/>
-    </row>
-    <row r="69" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="H68" s="49"/>
+      <c r="I68" s="51"/>
+      <c r="J68" s="51"/>
+      <c r="K68" s="52"/>
+      <c r="L68" s="49"/>
+      <c r="M68" s="49"/>
+    </row>
+    <row r="69" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A69" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="17">
+        <v>115</v>
+      </c>
+      <c r="B69" s="13">
         <v>1</v>
       </c>
-      <c r="C69" s="17">
+      <c r="C69" s="13">
         <f t="shared" ref="C69:C71" si="0">C68/B68</f>
-        <v>2.3765453204346039</v>
-      </c>
-      <c r="D69" s="17">
+        <v>2.2944696364505344</v>
+      </c>
+      <c r="D69" s="13">
         <f t="shared" ref="D69:D71" si="1">D68/B68</f>
         <v>2.4189019643934002</v>
       </c>
-      <c r="E69" s="17">
+      <c r="E69" s="13">
         <f t="shared" ref="E69:E71" si="2">E68/B68</f>
         <v>3.1209520683469427</v>
       </c>
-      <c r="F69" s="17">
+      <c r="F69" s="13">
         <f t="shared" ref="F69:F71" si="3">F68/B68</f>
         <v>1.2620808969443724</v>
       </c>
-      <c r="G69" s="53"/>
-      <c r="H69" s="53"/>
-      <c r="I69" s="55"/>
-      <c r="J69" s="55"/>
-      <c r="K69" s="56"/>
-      <c r="L69" s="53"/>
-      <c r="M69" s="53"/>
-    </row>
-    <row r="70" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="51"/>
+      <c r="J69" s="51"/>
+      <c r="K69" s="52"/>
+      <c r="L69" s="49"/>
+      <c r="M69" s="49"/>
+    </row>
+    <row r="70" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A70" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B70" s="17">
+        <v>118</v>
+      </c>
+      <c r="B70" s="13">
         <f>SUM(B2:B62)/SUM(Population!B2:B62)</f>
         <v>22080415.799571779</v>
       </c>
-      <c r="C70" s="17">
+      <c r="C70" s="13">
         <f>SUM(C2:C62)/SUM(Population!C2:C62)</f>
-        <v>56838837.821887895</v>
-      </c>
-      <c r="D70" s="17">
+        <v>54965484.390539549</v>
+      </c>
+      <c r="D70" s="13">
         <f>SUM(D2:D62)/SUM(Population!D2:D62)</f>
         <v>54403839.882208735</v>
       </c>
-      <c r="E70" s="17">
+      <c r="E70" s="13">
         <f>SUM(E2:E62)/SUM(Population!E2:E62)</f>
         <v>72594189.009418637</v>
       </c>
-      <c r="F70" s="17">
+      <c r="F70" s="13">
         <f>SUM(F2:F62)/SUM(Population!F2:F62)</f>
         <v>21933499.42880965</v>
       </c>
-      <c r="H70" s="53"/>
-      <c r="I70" s="55"/>
-      <c r="J70" s="55"/>
-      <c r="K70" s="56"/>
-      <c r="L70" s="53"/>
-      <c r="M70" s="53"/>
-    </row>
-    <row r="71" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="H70" s="49"/>
+      <c r="I70" s="51"/>
+      <c r="J70" s="51"/>
+      <c r="K70" s="52"/>
+      <c r="L70" s="49"/>
+      <c r="M70" s="49"/>
+    </row>
+    <row r="71" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A71" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B71" s="17">
+        <v>119</v>
+      </c>
+      <c r="B71" s="13">
         <v>1</v>
       </c>
-      <c r="C71" s="17">
+      <c r="C71" s="13">
         <f t="shared" si="0"/>
-        <v>2.5741742518721145</v>
-      </c>
-      <c r="D71" s="17">
+        <v>2.4893319441749613</v>
+      </c>
+      <c r="D71" s="13">
         <f t="shared" si="1"/>
         <v>2.4638956247945218</v>
       </c>
-      <c r="E71" s="17">
+      <c r="E71" s="13">
         <f t="shared" si="2"/>
         <v>3.2877183866631037</v>
       </c>
-      <c r="F71" s="17">
+      <c r="F71" s="13">
         <f t="shared" si="3"/>
         <v>0.99334630415949965</v>
       </c>
-      <c r="H71" s="53"/>
-      <c r="I71" s="55"/>
-      <c r="J71" s="55"/>
-      <c r="K71" s="56"/>
-      <c r="L71" s="53"/>
-      <c r="M71" s="53"/>
-    </row>
-    <row r="72" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="H71" s="49"/>
+      <c r="I71" s="51"/>
+      <c r="J71" s="51"/>
+      <c r="K71" s="52"/>
+      <c r="L71" s="49"/>
+      <c r="M71" s="49"/>
+    </row>
+    <row r="72" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3"/>
-      <c r="H72" s="53"/>
-      <c r="I72" s="53"/>
-      <c r="J72" s="53"/>
-      <c r="K72" s="53"/>
-      <c r="L72" s="53"/>
-      <c r="M72" s="53"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="H72" s="49"/>
+      <c r="I72" s="49"/>
+      <c r="J72" s="49"/>
+      <c r="K72" s="49"/>
+      <c r="L72" s="49"/>
+      <c r="M72" s="49"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
-      </c>
-      <c r="H73" s="53"/>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-      <c r="L73" s="53"/>
-      <c r="M73" s="53"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="49"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49"/>
+      <c r="J74" s="49"/>
+      <c r="K74" s="49"/>
+      <c r="L74" s="49"/>
+      <c r="M74" s="49"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H74" s="53"/>
-      <c r="I74" s="53"/>
-      <c r="J74" s="53"/>
-      <c r="K74" s="53"/>
-      <c r="L74" s="53"/>
-      <c r="M74" s="53"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>112</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="H75" s="53"/>
-      <c r="I75" s="53"/>
-      <c r="J75" s="53"/>
-      <c r="K75" s="53"/>
-      <c r="L75" s="53"/>
-      <c r="M75" s="53"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
+      <c r="L75" s="49"/>
+      <c r="M75" s="49"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>150</v>
-      </c>
-      <c r="H76" s="53"/>
-      <c r="I76" s="53"/>
-      <c r="J76" s="53"/>
-      <c r="K76" s="53"/>
-      <c r="L76" s="53"/>
-      <c r="M76" s="53"/>
+        <v>120</v>
+      </c>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
+      <c r="L76" s="49"/>
+      <c r="M76" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6183,642 +6709,266 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0A75E4-DA25-4A08-8974-1A31A91FD529}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A47D5AD-F7DD-4153-9FDF-3A8CE2F55F2C}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" style="17"/>
-    <col min="3" max="4" width="12.3984375" style="17" customWidth="1"/>
-    <col min="5" max="5" width="11.9296875" style="17" customWidth="1"/>
-    <col min="6" max="6" width="11.06640625" style="17"/>
-    <col min="7" max="7" width="14.86328125" style="17" customWidth="1"/>
-    <col min="8" max="16384" width="11.06640625" style="17"/>
+    <col min="1" max="1" width="27.69140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.84375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3828125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="11.921875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="11.07421875" style="13"/>
+    <col min="6" max="6" width="11.84375" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.07421875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="76">
+        <v>4525.4861916551599</v>
+      </c>
+      <c r="D3" s="76">
+        <v>3.94778101992449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="75" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="75">
+        <v>0.3</v>
+      </c>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="75" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" s="75" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="11">
-        <v>2.57</v>
-      </c>
-      <c r="C2" s="11">
-        <v>145.30000000000001</v>
-      </c>
-      <c r="D2" s="11">
-        <f xml:space="preserve"> 4.53*1000</f>
-        <v>4530</v>
-      </c>
-      <c r="E2" s="11">
-        <v>3.95</v>
-      </c>
-      <c r="F2" s="11">
-        <f>F3*(F8/F9)</f>
-        <v>26.509803921568629</v>
-      </c>
-      <c r="G2" s="11">
-        <f>(B2*0.27+D2*0.9)*0.00001</f>
-        <v>4.0776939000000005E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="11">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C3" s="11">
-        <v>140.30000000000001</v>
-      </c>
-      <c r="D3" s="11">
-        <f xml:space="preserve"> 4.21 *1000</f>
-        <v>4210</v>
-      </c>
-      <c r="E3" s="11">
-        <v>3.67</v>
-      </c>
-      <c r="F3" s="11">
-        <f>DLE!U5</f>
-        <v>15.600000000000001</v>
-      </c>
-      <c r="G3" s="11">
-        <f>(B3*0.27+D3*0.7)*0.00001</f>
-        <v>2.9475940000000003E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="11">
-        <f>('DLS v2'!B2+'DLS v2'!B3)/2</f>
-        <v>2.3849999999999998</v>
-      </c>
-      <c r="C4" s="11">
-        <f>('DLS v2'!C2+'DLS v2'!C3)/2</f>
-        <v>142.80000000000001</v>
-      </c>
-      <c r="D4" s="11">
-        <f>('DLS v2'!D2+'DLS v2'!D3)/2</f>
-        <v>4370</v>
-      </c>
-      <c r="E4" s="11">
-        <f>('DLS v2'!E2+'DLS v2'!E3)/2</f>
-        <v>3.81</v>
-      </c>
-      <c r="F4" s="11">
-        <f>('DLS v2'!F2+'DLS v2'!F3)/2</f>
-        <v>21.054901960784314</v>
-      </c>
-      <c r="G4" s="11">
-        <f>('DLS v2'!G2+'DLS v2'!G3)/2</f>
-        <v>3.5126439500000002E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B9" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="17">
-        <v>3.9404604370967649</v>
-      </c>
-      <c r="C8" s="17">
-        <v>205.43626131827909</v>
-      </c>
-      <c r="D8" s="17">
-        <f>3036.5975761951</f>
-        <v>3036.5975761950999</v>
-      </c>
-      <c r="E8" s="17">
-        <v>4.8</v>
-      </c>
-      <c r="F8" s="17">
-        <f>26</f>
-        <v>26</v>
-      </c>
-      <c r="G8" s="17">
-        <f>(B8*0.27+D8*0.9)*0.00001</f>
-        <v>2.7340017428936065E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="17">
-        <v>1.8456474232498501</v>
-      </c>
-      <c r="C9" s="17">
-        <v>198.12008644674611</v>
-      </c>
-      <c r="D9" s="17">
-        <f>2811.06984272459</f>
-        <v>2811.0698427245902</v>
-      </c>
-      <c r="E9" s="17">
-        <v>3.239875298796179</v>
-      </c>
-      <c r="F9" s="17">
-        <f>15.3</f>
-        <v>15.3</v>
-      </c>
-      <c r="G9" s="17">
-        <f>(B9*0.27+D9*0.7)*0.00001</f>
-        <v>1.9682472147114907E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="17">
-        <f>('DLS v2'!B8+'DLS v2'!B9)/2</f>
-        <v>2.8930539301733074</v>
-      </c>
-      <c r="C10" s="17">
-        <f>('DLS v2'!C8+'DLS v2'!C9)/2</f>
-        <v>201.77817388251259</v>
-      </c>
-      <c r="D10" s="17">
-        <f>('DLS v2'!D8+'DLS v2'!D9)/2</f>
-        <v>2923.8337094598451</v>
-      </c>
-      <c r="E10" s="17">
-        <f>('DLS v2'!E8+'DLS v2'!E9)/2</f>
-        <v>4.0199376493980896</v>
-      </c>
-      <c r="F10" s="17">
-        <f>('DLS v2'!F8+'DLS v2'!F9)/2</f>
-        <v>20.65</v>
-      </c>
-      <c r="G10" s="17">
-        <f>('DLS v2'!G8+'DLS v2'!G9)/2</f>
-        <v>2.3511244788025486E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="18" t="e">
-        <f>(B2*Population!#REF!*0.000001)*1000</f>
+      <c r="D9" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="14">
+        <f>(B2*Population!$C$31*0.000001)*1000</f>
+        <v>149.41769260000001</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="14">
+        <f>(B3*Population!$C$31*0.000001)*1000</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="14">
+        <f>(C3*Population!$C$31*0.000000001*1000)</f>
+        <v>307.35804756830697</v>
+      </c>
+      <c r="D12" s="14">
+        <f>(D3*Population!$C$31*0.000001)*1000</f>
+        <v>268.12196858508719</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="14">
+        <f>(B4*Population!$C$31*0.000001)*1000</f>
+        <v>169.79283250000003</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="14">
+        <f>(B6*Population!$C$62*0.000001)*1000</f>
+        <v>21.266045399999999</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="14">
+        <f>(B7*Population!$C$62*0.000001)*1000</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="14">
+        <f>(B8*Population!$C$62*0.000001)*1000</f>
+        <v>35.443408999999996</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F19" s="13">
+        <f>11000000000/(Population!C31*1000)</f>
+        <v>161.96207811068822</v>
+      </c>
+      <c r="G19" s="13" t="e">
+        <f>F19/#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="18" t="e">
-        <f>C2*Population!#REF!*1000*0.000000001</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D13" s="18" t="e">
-        <f>(D2*Population!#REF!*1000*0.000000001)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E13" s="18" t="e">
-        <f>(E2*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F13" s="18" t="e">
-        <f>F2*Population!#REF!*0.000277778</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G13" s="18" t="e">
-        <f>(G2*Population!#REF!*1000)*0.000001</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="18" t="e">
-        <f>(B3*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C14" s="18" t="e">
-        <f>(C3*Population!#REF!*0.000001)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D14" s="18" t="e">
-        <f>(D3*Population!#REF!*0.000000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E14" s="18" t="e">
-        <f>(E3*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F14" s="18" t="e">
-        <f>F3*Population!#REF!*0.000277778</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G14" s="18" t="e">
-        <f>(G3*Population!#REF!*1000)*0.000001</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="18" t="e">
-        <f>(B4*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C15" s="18" t="e">
-        <f>(C4*Population!#REF!*0.000001)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D15" s="18" t="e">
-        <f>(D4*Population!#REF!*0.000000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E15" s="18" t="e">
-        <f>(E4*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F15" s="18" t="e">
-        <f>F4*Population!#REF!*0.000277778</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G15" s="18" t="e">
-        <f>(G4*Population!#REF!*1000)*0.000001</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="68" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="G21" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="G22" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="G23" s="17" t="s">
-        <v>63</v>
-      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" s="61">
+        <f>(B3*Population!$C$31*0.000001)*1000</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="61">
+        <f>(C3*Population!C31*1000*0.000000001)</f>
+        <v>307.35804756830703</v>
+      </c>
+      <c r="D20" s="61">
+        <f>(D3*Population!C31*0.000001)*1000</f>
+        <v>268.12196858508719</v>
+      </c>
+      <c r="F20" s="13">
+        <f>373*1000000000/(Population!C31*1000)</f>
+        <v>5491.9868304806096</v>
+      </c>
+      <c r="G20" s="13">
+        <f>F20/C3</f>
+        <v>1.2135683544030349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B23:D23"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F18" r:id="rId1" xr:uid="{FE1DF694-6272-4B23-A77B-2E2C32319CE3}"/>
-    <hyperlink ref="B18" r:id="rId2" xr:uid="{690E7B6F-16A8-495D-9B9E-E651E414B818}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.9296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="11">
-        <v>2.57</v>
-      </c>
-      <c r="C2" s="11">
-        <v>3.95</v>
-      </c>
-      <c r="D2" s="11">
-        <f>D3*(D8/D9)</f>
-        <v>26.509803921568629</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="11">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C3" s="11">
-        <v>3.67</v>
-      </c>
-      <c r="D3" s="11">
-        <f>DLE!U5</f>
-        <v>15.600000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="11">
-        <f>(DLS!B2+DLS!B3)/2</f>
-        <v>2.3849999999999998</v>
-      </c>
-      <c r="C4" s="11">
-        <f>(DLS!C2+DLS!C3)/2</f>
-        <v>3.81</v>
-      </c>
-      <c r="D4" s="11">
-        <f>(DLS!D2+DLS!D3)/2</f>
-        <v>21.054901960784314</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="15">
-        <v>3.9404604370967649</v>
-      </c>
-      <c r="C8" s="13">
-        <v>4.8</v>
-      </c>
-      <c r="D8">
-        <f>26</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="16">
-        <v>1.8456474232498501</v>
-      </c>
-      <c r="C9" s="14">
-        <v>3.239875298796179</v>
-      </c>
-      <c r="D9">
-        <f>15.3</f>
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10">
-        <f>(DLS!B8+DLS!B9)/2</f>
-        <v>2.8930539301733074</v>
-      </c>
-      <c r="C10" s="17">
-        <f>(DLS!C8+DLS!C9)/2</f>
-        <v>4.0199376493980896</v>
-      </c>
-      <c r="D10" s="17">
-        <f>(DLS!D8+DLS!D9)/2</f>
-        <v>20.65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="18" t="e">
-        <f>(B2*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C13" s="18" t="e">
-        <f>(C2*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D13" s="18" t="e">
-        <f>D2*Population!#REF!*0.000277778</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="18" t="e">
-        <f>(B3*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C14" s="18" t="e">
-        <f>(C3*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D14" s="18" t="e">
-        <f>D3*Population!#REF!*0.000277778</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="18" t="e">
-        <f>(B4*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C15" s="18" t="e">
-        <f>(C4*Population!#REF!*0.000001)*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D15" s="18" t="e">
-        <f>D4*Population!#REF!*0.000277778</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="68" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B18:C18"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="D18" r:id="rId1" xr:uid="{F7B5DC7E-06B3-4D92-84C6-221AF8CD7354}"/>
-    <hyperlink ref="B18" r:id="rId2" xr:uid="{7753ABD6-E8C9-41B2-94EA-8111D4B50F91}"/>
+    <hyperlink ref="B23" r:id="rId1" xr:uid="{D04949F0-64E8-488B-9B04-608012ED57AD}"/>
+    <hyperlink ref="B22" r:id="rId2" location="erladc3ads5" xr:uid="{E6D5DD1C-4947-48F0-8B3C-54EEE46D8BF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId3"/>
@@ -6826,202 +6976,479 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0A75E4-DA25-4A08-8974-1A31A91FD529}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="27.69140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.84375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.3828125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="11.921875" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="11.07421875" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="11">
+        <v>2.5676942899999999</v>
+      </c>
+      <c r="C2" s="11">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="D2" s="11">
+        <f xml:space="preserve"> 4.53*1000</f>
+        <v>4530</v>
+      </c>
+      <c r="E2" s="11">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="11">
+        <v>2.2045302900000001</v>
+      </c>
+      <c r="C3" s="11">
+        <v>140.30000000000001</v>
+      </c>
+      <c r="D3" s="11">
+        <f xml:space="preserve"> 4.21 *1000</f>
+        <v>4210</v>
+      </c>
+      <c r="E3" s="11">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="11">
+        <v>2.47523336291431</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0.50285615693242003</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.32898282460362099</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0.47277171090592901</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="11">
+        <v>1.9231774974899101</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="13">
+        <v>3.9404604370967649</v>
+      </c>
+      <c r="C12" s="13">
+        <v>205.43626131827909</v>
+      </c>
+      <c r="D12" s="13">
+        <f>3036.5975761951</f>
+        <v>3036.5975761950999</v>
+      </c>
+      <c r="E12" s="13">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13">
+        <v>1.8456474232498501</v>
+      </c>
+      <c r="C13" s="13">
+        <v>198.12008644674611</v>
+      </c>
+      <c r="D13" s="13">
+        <f>2811.06984272459</f>
+        <v>2811.0698427245902</v>
+      </c>
+      <c r="E13" s="13">
+        <v>3.239875298796179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="61">
+        <f>(B2*Population!$C$31*0.000001)*1000</f>
+        <v>174.39043459727054</v>
+      </c>
+      <c r="C16" s="61">
+        <f>C2*Population!C31*1000*0.000000001</f>
+        <v>9.8683594249000013</v>
+      </c>
+      <c r="D16" s="61">
+        <f>(D2*Population!C31*1000*0.000000001)</f>
+        <v>307.66461249000002</v>
+      </c>
+      <c r="E16" s="61">
+        <f>(E2*Population!C31*0.000001)*1000</f>
+        <v>268.27267535000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="61">
+        <f>(B3*Population!$C$31*0.000001)*1000</f>
+        <v>149.72537690845857</v>
+      </c>
+      <c r="C17" s="61">
+        <f>(C3*Population!C31*0.000001)</f>
+        <v>9.5287737599000017</v>
+      </c>
+      <c r="D17" s="61">
+        <f>(D3*Population!C31*0.000000001)*1000</f>
+        <v>285.93112993000005</v>
+      </c>
+      <c r="E17" s="61">
+        <f>(E3*Population!C31*0.000001)*1000</f>
+        <v>249.25587810999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="66"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B20:E20"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B20" r:id="rId1" xr:uid="{690E7B6F-16A8-495D-9B9E-E651E414B818}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE59BEB1-58EA-414F-91E0-ADFFF27E94F9}">
   <dimension ref="A2:U6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.06640625" style="17"/>
+    <col min="1" max="1" width="11.07421875" style="13"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="16.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="72" t="s">
+    <row r="2" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="70"/>
+      <c r="M2" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="70"/>
+      <c r="T2" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="U2" s="72" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="B3" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="73" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="73"/>
-      <c r="M2" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="74" t="s">
-        <v>72</v>
-      </c>
-      <c r="O2" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="S2" s="73"/>
-      <c r="T2" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="U2" s="75" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="B3" s="71" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="70" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="70" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="70" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="71" t="s">
-        <v>81</v>
-      </c>
-      <c r="I3" s="71" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="71" t="s">
-        <v>83</v>
-      </c>
-      <c r="K3" s="70" t="s">
-        <v>84</v>
-      </c>
-      <c r="L3" s="70" t="s">
-        <v>85</v>
-      </c>
-      <c r="M3" s="76"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="71" t="s">
-        <v>86</v>
-      </c>
-      <c r="P3" s="71" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q3" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="R3" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="S3" s="70" t="s">
-        <v>91</v>
-      </c>
-      <c r="T3" s="77"/>
-      <c r="U3" s="75"/>
-    </row>
-    <row r="4" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="R4" s="70"/>
-      <c r="S4" s="70"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="75"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A5" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="25">
+      <c r="F3" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" s="73"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="68" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="S3" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" s="74"/>
+      <c r="U3" s="72"/>
+    </row>
+    <row r="4" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="74"/>
+      <c r="U4" s="72"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="21">
         <v>2.7</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="22">
         <v>0.3</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="22">
         <v>0.2</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="23">
         <v>0.8</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="23">
         <v>0.7</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="23">
         <v>0</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="22">
         <v>0.2</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="22">
         <v>1.3</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="22">
         <v>0.2</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="23">
         <v>0.3</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="23">
         <v>0.3</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="22">
         <v>1.4</v>
       </c>
-      <c r="N5" s="27">
+      <c r="N5" s="23">
         <v>0.4</v>
       </c>
-      <c r="O5" s="26">
+      <c r="O5" s="22">
         <v>0</v>
       </c>
-      <c r="P5" s="26">
+      <c r="P5" s="22">
         <v>0.1</v>
       </c>
-      <c r="Q5" s="26">
+      <c r="Q5" s="22">
         <v>0.4</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="23">
         <v>2.2999999999999998</v>
       </c>
-      <c r="S5" s="27">
+      <c r="S5" s="23">
         <v>0.7</v>
       </c>
-      <c r="T5" s="26">
+      <c r="T5" s="22">
         <v>3.3</v>
       </c>
-      <c r="U5" s="28">
+      <c r="U5" s="24">
         <f>SUM(B5:T5)</f>
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A6" s="17" t="s">
-        <v>10</v>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A6" s="13" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7055,217 +7482,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC11EFA9-274E-476D-8BFE-D8769B6BF052}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" t="e">
-        <f>(Population!#REF!*DLS!B2)/(Population!#REF!*DLS!B8)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C2" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D2" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E2" s="17" t="e">
-        <f>(Population!#REF!*DLS!C2)/(Population!#REF!*DLS!C8)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F2" s="17" t="e">
-        <f>(Population!#REF!*DLS!D2)/(Population!#REF!*DLS!D8)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G2" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="17" t="e">
-        <f>(Population!#REF!*DLS!B3)/(Population!#REF!*DLS!B9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C3" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D3" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="17" t="e">
-        <f>(Population!#REF!*DLS!C3)/(Population!#REF!*DLS!C9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F3" s="17" t="e">
-        <f>(Population!#REF!*DLS!D3)/(Population!#REF!*DLS!D9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G3" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" t="e">
-        <f>(Population!#REF!*DLS!B4)/(Population!#REF!*DLS!B10)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C5" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D5" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E5" s="17" t="e">
-        <f>(Population!#REF!*DLS!C4)/(Population!#REF!*DLS!C10)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F5" s="17" t="e">
-        <f>(Population!#REF!*DLS!D4)/(Population!#REF!*DLS!D10)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G5" s="17" t="e">
-        <f>(Population!#REF!*DLS!#REF!)/(Population!#REF!*DLS!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="17">
-        <v>3494.0786014333898</v>
-      </c>
-      <c r="E8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8">
-        <f>1-F9</f>
-        <v>0.82218380833807991</v>
-      </c>
-      <c r="G8">
-        <v>0.7</v>
-      </c>
-      <c r="H8">
-        <f>F8*G8+F9*G9</f>
-        <v>0.74445404791547987</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="17">
-        <v>201.308612543306</v>
-      </c>
-      <c r="E9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9">
-        <f>SUM(D9:D12)/SUM(D8:D13)</f>
-        <v>0.17781619166192006</v>
-      </c>
-      <c r="G9">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10">
-        <v>520</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11">
-        <v>40</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12">
-        <v>40</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13">
-        <v>211</v>
-      </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8180FC1D-0F23-420D-BB82-17E2625E23C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08EB7DC-2D65-4867-AC72-14A14670277B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
@@ -896,7 +896,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1017,6 +1017,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1032,11 +1034,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1044,20 +1052,13 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Lien hypertexte" xfId="3" builtinId="8"/>
@@ -1469,7 +1470,10 @@
       <c r="H4" s="41">
         <v>50</v>
       </c>
-      <c r="I4" s="41"/>
+      <c r="I4" s="41">
+        <f>I3*7</f>
+        <v>45.5</v>
+      </c>
       <c r="J4" s="41">
         <f>J3*2</f>
         <v>11.18</v>
@@ -1665,9 +1669,9 @@
         <f>((Population!C119/100)*H4)/H7</f>
         <v>366.78032073601571</v>
       </c>
-      <c r="I10" s="27">
-        <f>(Population!C119/100)*I4</f>
-        <v>0</v>
+      <c r="I10" s="77">
+        <f>(Population!C119/100)*I4/I7</f>
+        <v>333.77009186977438</v>
       </c>
       <c r="J10" s="27">
         <f>(Population!C119/100)*J4/J7</f>
@@ -1941,8 +1945,8 @@
         <v>5.1945832038822681</v>
       </c>
       <c r="I19" s="11">
-        <f>I4*1000000/(Population!B118*1000)</f>
-        <v>0</v>
+        <f>I4*1000000000000/(Population!B118*1000)</f>
+        <v>4727.0707155328637</v>
       </c>
       <c r="J19" s="11">
         <f>J4*1000000000/(Population!C118*1000)</f>
@@ -6445,9 +6449,9 @@
         <v>0.95614641891771557</v>
       </c>
       <c r="H65" s="49"/>
-      <c r="I65" s="62"/>
-      <c r="J65" s="63"/>
-      <c r="K65" s="64"/>
+      <c r="I65" s="64"/>
+      <c r="J65" s="65"/>
+      <c r="K65" s="66"/>
       <c r="L65" s="49"/>
       <c r="M65" s="49"/>
     </row>
@@ -6752,10 +6756,10 @@
         <v>144</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="76">
+      <c r="C3" s="63">
         <v>4525.4861916551599</v>
       </c>
-      <c r="D3" s="76">
+      <c r="D3" s="63">
         <v>3.94778101992449</v>
       </c>
     </row>
@@ -6776,32 +6780,32 @@
       <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="75">
+      <c r="B6" s="62">
         <v>0.3</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="75">
+      <c r="B8" s="62">
         <v>0.5</v>
       </c>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="11" t="s">
@@ -6956,11 +6960,11 @@
       <c r="A23" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="65" t="s">
+      <c r="B23" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7233,12 +7237,12 @@
       <c r="A20" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7261,41 +7265,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="70" t="s">
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="69" t="s">
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="70" t="s">
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="70"/>
-      <c r="M2" s="73" t="s">
+      <c r="L2" s="74"/>
+      <c r="M2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="71" t="s">
+      <c r="N2" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="69" t="s">
+      <c r="O2" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="70" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="S2" s="70"/>
-      <c r="T2" s="74" t="s">
+      <c r="S2" s="74"/>
+      <c r="T2" s="76" t="s">
         <v>66</v>
       </c>
       <c r="U2" s="72" t="s">
@@ -7303,81 +7307,81 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="17.149999999999999" x14ac:dyDescent="0.4">
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="68" t="s">
+      <c r="I3" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="68" t="s">
+      <c r="J3" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="67" t="s">
+      <c r="K3" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="67" t="s">
+      <c r="L3" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="M3" s="73"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="68" t="s">
+      <c r="M3" s="75"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="68" t="s">
+      <c r="P3" s="70" t="s">
         <v>60</v>
       </c>
       <c r="Q3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="R3" s="67" t="s">
+      <c r="R3" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="S3" s="67" t="s">
+      <c r="S3" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="T3" s="74"/>
+      <c r="T3" s="76"/>
       <c r="U3" s="72"/>
     </row>
     <row r="4" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="70"/>
       <c r="Q4" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="74"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="76"/>
       <c r="U4" s="72"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.4">
@@ -7453,6 +7457,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -7467,17 +7482,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08EB7DC-2D65-4867-AC72-14A14670277B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF19EA1-8D8E-471B-BE37-FB6CD2DAEEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
@@ -1019,6 +1019,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1034,17 +1035,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1052,13 +1047,18 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Lien hypertexte" xfId="3" builtinId="8"/>
@@ -1344,21 +1344,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C32444-97C3-4A7C-A91C-82059EB528AD}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27" style="13" customWidth="1"/>
-    <col min="2" max="2" width="14.15234375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="11.69140625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="14.07421875" style="13" customWidth="1"/>
-    <col min="5" max="6" width="9.23046875" style="13"/>
-    <col min="7" max="7" width="11.3828125" style="13" customWidth="1"/>
-    <col min="8" max="8" width="11.921875" style="13" customWidth="1"/>
-    <col min="9" max="9" width="13.921875" style="13" customWidth="1"/>
-    <col min="10" max="10" width="16.07421875" style="13" customWidth="1"/>
-    <col min="11" max="16384" width="9.23046875" style="13"/>
+    <col min="2" max="2" width="14.1328125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="14.06640625" style="13" customWidth="1"/>
+    <col min="5" max="6" width="9.19921875" style="13"/>
+    <col min="7" max="7" width="11.3984375" style="13" customWidth="1"/>
+    <col min="8" max="8" width="11.9296875" style="13" customWidth="1"/>
+    <col min="9" max="9" width="13.9296875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="16.06640625" style="13" customWidth="1"/>
+    <col min="11" max="16384" width="9.19921875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="45" t="s">
         <v>91</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="38" t="s">
         <v>85</v>
       </c>
@@ -1411,7 +1411,7 @@
       <c r="I2" s="39"/>
       <c r="J2" s="39"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="40" t="s">
         <v>87</v>
       </c>
@@ -1441,10 +1441,10 @@
         <v>6.5</v>
       </c>
       <c r="J3" s="42">
-        <v>5.59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="40" t="s">
         <v>86</v>
       </c>
@@ -1476,10 +1476,10 @@
       </c>
       <c r="J4" s="41">
         <f>J3*2</f>
-        <v>11.18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="43" t="s">
         <v>93</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1523,7 +1523,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="29" t="s">
         <v>99</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="18" t="s">
         <v>88</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
         <v>90</v>
       </c>
@@ -1634,10 +1634,10 @@
       </c>
       <c r="J9" s="27">
         <f>(Population!C119/100)*J3/J7</f>
-        <v>41.006039858286563</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+        <v>40.345835280961737</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="18" t="s">
         <v>89</v>
       </c>
@@ -1669,16 +1669,16 @@
         <f>((Population!C119/100)*H4)/H7</f>
         <v>366.78032073601571</v>
       </c>
-      <c r="I10" s="77">
+      <c r="I10" s="64">
         <f>(Population!C119/100)*I4/I7</f>
         <v>333.77009186977438</v>
       </c>
       <c r="J10" s="27">
         <f>(Population!C119/100)*J4/J7</f>
-        <v>82.012079716573126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+        <v>80.691670561923473</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="18" t="s">
         <v>92</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="29" t="s">
         <v>100</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="37" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" s="37" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="35"/>
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
@@ -1754,7 +1754,7 @@
       <c r="I13" s="36"/>
       <c r="J13" s="36"/>
     </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="33" t="s">
         <v>98</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1798,7 +1798,7 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="29" t="s">
         <v>101</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="15" t="s">
         <v>94</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="15" t="s">
         <v>95</v>
       </c>
@@ -1909,10 +1909,10 @@
       </c>
       <c r="J18" s="28">
         <f>J3/(Population!C118*1000)*1000000000</f>
-        <v>79.16924237219726</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+        <v>77.894603407349734</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="15" t="s">
         <v>96</v>
       </c>
@@ -1950,10 +1950,10 @@
       </c>
       <c r="J19" s="11">
         <f>J4*1000000000/(Population!C118*1000)</f>
-        <v>158.33848474439455</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>155.78920681469947</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="16" t="s">
         <v>97</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="29" t="s">
         <v>102</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -2029,10 +2029,10 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="8"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="8"/>
     </row>
   </sheetData>
@@ -2044,18 +2044,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763A0529-0113-40C2-8132-A760C1078623}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27" style="13" customWidth="1"/>
-    <col min="2" max="2" width="14.15234375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="11.69140625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="14.07421875" style="13" customWidth="1"/>
-    <col min="5" max="6" width="9.23046875" style="13"/>
-    <col min="7" max="7" width="16.07421875" style="13" customWidth="1"/>
-    <col min="8" max="16384" width="9.23046875" style="13"/>
+    <col min="2" max="2" width="14.1328125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="14.06640625" style="13" customWidth="1"/>
+    <col min="5" max="6" width="9.19921875" style="13"/>
+    <col min="7" max="7" width="16.06640625" style="13" customWidth="1"/>
+    <col min="8" max="16384" width="9.19921875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="45" t="s">
         <v>91</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="38" t="s">
         <v>85</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="F2" s="39"/>
       <c r="G2" s="39"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="40" t="s">
         <v>87</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="40" t="s">
         <v>86</v>
       </c>
@@ -2123,7 +2123,7 @@
       <c r="F4" s="41"/>
       <c r="G4" s="41"/>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="43" t="s">
         <v>93</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2155,7 +2155,7 @@
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="29" t="s">
         <v>99</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="18" t="s">
         <v>88</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
         <v>90</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>40.345835280961737</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="18" t="s">
         <v>89</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="18" t="s">
         <v>92</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="29" t="s">
         <v>100</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="37" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" s="37" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="35"/>
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
@@ -2320,7 +2320,7 @@
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="33" t="s">
         <v>98</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -2352,7 +2352,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="29" t="s">
         <v>101</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="15" t="s">
         <v>94</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="15" t="s">
         <v>95</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>77.894603407349734</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="15" t="s">
         <v>96</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="16" t="s">
         <v>97</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="29" t="s">
         <v>102</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -2517,10 +2517,10 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="8"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="8"/>
     </row>
   </sheetData>
@@ -2532,13 +2532,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
   <dimension ref="A1:F123"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.3828125" customWidth="1"/>
-    <col min="2" max="2" width="12.84375" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="25" t="s">
         <v>5</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>1153582.7239999999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>1170788.5279999999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>1184574.237</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>1197308.575</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>1209003.0959999999</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>1220133.9269999999</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>1230944.8119999999</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>1241139.622</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>1250847.1270000001</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>1260176.655</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>1269581.175</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>1278725.0630000001</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>1286866.8389999999</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>1294517.3259999999</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>1302100.3160000001</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>1310027.1359999999</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>1318054.0360000001</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>1325813.5819999999</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>1333821.0160000001</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>1342522.716</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>1351561.514</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>1360250.6640000001</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>1369520.8640000001</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>1379008.04</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>1387951.9720000001</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>1396134.1740000001</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>1404052.632</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>1412354.727</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>1419008.956</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>1423520.3570000001</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>1426106.0930000001</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>1426437.267</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>1425179.5689999999</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>1422584.933</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>1419321.2779999999</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>1416096.094</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" s="59">
         <v>2026</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>1412914.0889999999</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="59">
         <v>2027</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>1409679.406</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" s="59">
         <v>2028</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>1406136.7439999999</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="59">
         <v>2029</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>1402282.7520000001</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="59">
         <v>2030</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>1398153.8319999999</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="59">
         <v>2031</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>1393748.67</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" s="59">
         <v>2032</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>1389060.0319999999</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" s="59">
         <v>2033</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>1384096.5209999999</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" s="59">
         <v>2034</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>1378876.9339999999</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" s="59">
         <v>2035</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>1373427.531</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="59">
         <v>2036</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>1367742.7849999999</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="59">
         <v>2037</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>1361830.0630000001</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="59">
         <v>2038</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>1355722.7069999999</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="59">
         <v>2039</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>1349394.7180000001</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="59">
         <v>2040</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>1342816.6569999999</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="59">
         <v>2041</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>1335990.2309999999</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="59">
         <v>2042</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>1328909.2379999999</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="59">
         <v>2043</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>1321590.798</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="59">
         <v>2044</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>1314015.987</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" s="59">
         <v>2045</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>1306113.7879999999</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" s="59">
         <v>2046</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>1297817.5819999999</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" s="59">
         <v>2047</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>1289120.4269999999</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" s="59">
         <v>2048</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>1279992.585</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="59">
         <v>2049</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>1270381.145</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" s="59">
         <v>2050</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>1260289.0930000001</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="59">
         <v>2051</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>1249692.5379999999</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="59">
         <v>2052</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>1238557.132</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="59">
         <v>2053</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>1226929.8540000001</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="59">
         <v>2054</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>1214853.3459999999</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="59">
         <v>2055</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>1202342.4709999999</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="59">
         <v>2056</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>1189440.669</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="59">
         <v>2057</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>1176217.9450000001</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="59">
         <v>2058</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>1162722.7080000001</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="59">
         <v>2059</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>1149002.1669999999</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="59">
         <v>2060</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>1135127.1910000001</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="59">
         <v>2061</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>1121174.7169999999</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" s="59">
         <v>2062</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>1107207.1329999999</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" s="59">
         <v>2063</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>1093276.7039999999</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="59">
         <v>2064</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>1079407.882</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="59">
         <v>2065</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>1065632.5290000001</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="59">
         <v>2066</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>1051989.135</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="59">
         <v>2067</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>1038472.818</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="59">
         <v>2068</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>1025103.452</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" s="59">
         <v>2069</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>1011878.19</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" s="59">
         <v>2070</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>998784.31900000002</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" s="59">
         <v>2071</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>985806.56</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" s="59">
         <v>2072</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>972905.67099999997</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" s="59">
         <v>2073</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>960055.38300000003</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" s="59">
         <v>2074</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>947249.41700000002</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" s="59">
         <v>2075</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>934466.66</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" s="59">
         <v>2076</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>921677.63</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" s="59">
         <v>2077</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>908874.53200000001</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90" s="59">
         <v>2078</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>896043.78899999999</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" s="59">
         <v>2079</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>883166.97499999998</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" s="59">
         <v>2080</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>870252.34400000004</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" s="59">
         <v>2081</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>857328.71499999997</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" s="59">
         <v>2082</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>844439.196</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" s="59">
         <v>2083</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>831604.66700000002</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" s="59">
         <v>2084</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>818815.35600000003</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" s="59">
         <v>2085</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>806115.054</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98" s="59">
         <v>2086</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>793559.25399999996</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" s="59">
         <v>2087</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>781153.71799999999</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" s="59">
         <v>2088</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>768899.13199999998</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" s="59">
         <v>2089</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>756809.11</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" s="59">
         <v>2090</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>744902.83600000001</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" s="59">
         <v>2091</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>733179.45600000001</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" s="59">
         <v>2092</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>721612.75</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" s="59">
         <v>2093</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>710185.96799999999</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" s="59">
         <v>2094</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>698893.77</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" s="59">
         <v>2095</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>687724.08499999996</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" s="59">
         <v>2096</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>676660.87699999998</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109" s="59">
         <v>2097</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>665695.50300000003</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110" s="59">
         <v>2098</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>654825.38899999997</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" s="59">
         <v>2099</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>644049.4</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" s="59">
         <v>2100</v>
       </c>
@@ -4778,13 +4778,13 @@
         <v>633368.11300000001</v>
       </c>
     </row>
-    <row r="113" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>13</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>18.223874457114288</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A115" s="3" t="s">
         <v>80</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>1365292.1845625006</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A116" s="3" t="s">
         <v>108</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>15.491065655429644</v>
       </c>
     </row>
-    <row r="117" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A117" s="3" t="s">
         <v>125</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>13.040560048995525</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A118" s="3" t="s">
         <v>14</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>1101676.6355609756</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A119" s="3" t="s">
         <v>109</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>11.445501894389142</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
         <v>73</v>
       </c>
@@ -4958,19 +4958,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
   <dimension ref="A1:AI76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.23046875" customWidth="1"/>
-    <col min="3" max="3" width="16.4609375" customWidth="1"/>
-    <col min="4" max="4" width="22.07421875" customWidth="1"/>
-    <col min="5" max="5" width="20.69140625" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.19921875" customWidth="1"/>
+    <col min="3" max="3" width="16.46484375" customWidth="1"/>
+    <col min="4" max="4" width="22.06640625" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="10.69140625" style="13"/>
-    <col min="9" max="10" width="10.69140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="13"/>
+    <col min="9" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5018,7 +5018,7 @@
       <c r="AH1" s="7"/>
       <c r="AI1" s="7"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A2" s="53">
         <v>1990</v>
       </c>
@@ -5066,7 +5066,7 @@
       <c r="AH2" s="7"/>
       <c r="AI2" s="7"/>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" s="53">
         <v>1991</v>
       </c>
@@ -5114,7 +5114,7 @@
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" s="53">
         <v>1992</v>
       </c>
@@ -5162,7 +5162,7 @@
       <c r="AH4" s="7"/>
       <c r="AI4" s="7"/>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" s="53">
         <v>1993</v>
       </c>
@@ -5209,7 +5209,7 @@
       <c r="AH5" s="7"/>
       <c r="AI5" s="7"/>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A6" s="53">
         <v>1994</v>
       </c>
@@ -5229,7 +5229,7 @@
         <v>3047411115925</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A7" s="53">
         <v>1995</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>3383096056447</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" s="53">
         <v>1996</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>3720501963123</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A9" s="53">
         <v>1997</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>4066419152961</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A10" s="53">
         <v>1998</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>4388623718711</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A11" s="53">
         <v>1999</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>4728357537870</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A12" s="53">
         <v>2000</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>5133746736757</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A13" s="53">
         <v>2001</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>5561082225597</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A14" s="53">
         <v>2002</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>6074706488414</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A15" s="53">
         <v>2003</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>6689090876282</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A16" s="53">
         <v>2004</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>7367393399861</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="53">
         <v>2005</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>8211218760901</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="53">
         <v>2006</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>9252014077441</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="53">
         <v>2007</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>10561245407110</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="53">
         <v>2008</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>11582388576956</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="53">
         <v>2009</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>12671839645498</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="53">
         <v>2010</v>
       </c>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="53">
         <v>2011</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>15340013860010</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="53">
         <v>2012</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>16545404559826</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="53">
         <v>2013</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>17832377196873</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="53">
         <v>2014</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>19162852171599</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="53">
         <v>2015</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>20500730181113</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="53">
         <v>2016</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>21889385822096</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="53">
         <v>2017</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>23397835751145</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="53">
         <v>2018</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>24979016132707</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="53">
         <v>2019</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>26494587477980</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="53">
         <v>2020</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>27114429372607</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" s="53">
         <v>2021</v>
       </c>
@@ -5770,7 +5770,7 @@
         <v>29438240129870</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" s="53">
         <v>2022</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>30360791708735</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" s="53">
         <v>2023</v>
       </c>
@@ -5810,7 +5810,7 @@
         <v>32005133203227</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" s="53">
         <v>2024</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>33592044935159</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A37" s="53">
         <v>2025</v>
       </c>
@@ -5856,7 +5856,7 @@
       <c r="L37" s="49"/>
       <c r="M37" s="49"/>
     </row>
-    <row r="38" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A38" s="57">
         <v>2026</v>
       </c>
@@ -5882,7 +5882,7 @@
       <c r="L38" s="49"/>
       <c r="M38" s="49"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39" s="57">
         <v>2027</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>37948223078959</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A40" s="57">
         <v>2028</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>39369249953641</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A41" s="57">
         <v>2029</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>40843489263971</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A42" s="57">
         <v>2030</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>42372933627653</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A43" s="57">
         <v>2031</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>43593096339827</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A44" s="57">
         <v>2032</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>44848394618899</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A45" s="57">
         <v>2033</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>46139840221786</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46" s="57">
         <v>2034</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>47468474039756</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47" s="57">
         <v>2035</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>48835366937379</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48" s="57">
         <v>2036</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>49829940141406</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A49" s="57">
         <v>2037</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>50844768662843</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A50" s="57">
         <v>2038</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>51880265018217</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A51" s="57">
         <v>2039</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>52936850125299</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A52" s="57">
         <v>2040</v>
       </c>
@@ -6168,7 +6168,7 @@
       <c r="L52" s="49"/>
       <c r="M52" s="49"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A53" s="57">
         <v>2041</v>
       </c>
@@ -6194,7 +6194,7 @@
       <c r="L53" s="49"/>
       <c r="M53" s="49"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="57">
         <v>2042</v>
       </c>
@@ -6220,7 +6220,7 @@
       <c r="L54" s="49"/>
       <c r="M54" s="49"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A55" s="57">
         <v>2043</v>
       </c>
@@ -6246,7 +6246,7 @@
       <c r="L55" s="49"/>
       <c r="M55" s="49"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A56" s="57">
         <v>2044</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>57946661477194</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A57" s="57">
         <v>2045</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>58973516252283</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A58" s="57">
         <v>2046</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>59871715719212</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A59" s="57">
         <v>2047</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>60783595263805</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A60" s="57">
         <v>2048</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>61709363241255</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A61" s="57">
         <v>2049</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>62649231180123</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A62" s="57">
         <v>2050</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>63603413830667</v>
       </c>
     </row>
-    <row r="63" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A63" s="55"/>
       <c r="B63" s="56"/>
       <c r="C63" s="56"/>
@@ -6394,7 +6394,7 @@
       <c r="E63" s="56"/>
       <c r="F63" s="56"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A64" s="48">
         <v>2019</v>
       </c>
@@ -6425,7 +6425,7 @@
       <c r="L64" s="49"/>
       <c r="M64" s="49"/>
     </row>
-    <row r="65" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A65" s="13" t="s">
         <v>110</v>
       </c>
@@ -6449,13 +6449,13 @@
         <v>0.95614641891771557</v>
       </c>
       <c r="H65" s="49"/>
-      <c r="I65" s="64"/>
-      <c r="J65" s="65"/>
-      <c r="K65" s="66"/>
+      <c r="I65" s="65"/>
+      <c r="J65" s="66"/>
+      <c r="K65" s="67"/>
       <c r="L65" s="49"/>
       <c r="M65" s="49"/>
     </row>
-    <row r="66" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A66" s="3" t="s">
         <v>114</v>
       </c>
@@ -6486,7 +6486,7 @@
       <c r="L66" s="49"/>
       <c r="M66" s="49"/>
     </row>
-    <row r="67" spans="1:13" s="13" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13" s="13" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67" s="3" t="s">
         <v>116</v>
       </c>
@@ -6516,7 +6516,7 @@
       <c r="L67" s="49"/>
       <c r="M67" s="49"/>
     </row>
-    <row r="68" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A68" s="3" t="s">
         <v>80</v>
       </c>
@@ -6547,7 +6547,7 @@
       <c r="L68" s="49"/>
       <c r="M68" s="49"/>
     </row>
-    <row r="69" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A69" s="3" t="s">
         <v>115</v>
       </c>
@@ -6578,7 +6578,7 @@
       <c r="L69" s="49"/>
       <c r="M69" s="49"/>
     </row>
-    <row r="70" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A70" s="3" t="s">
         <v>118</v>
       </c>
@@ -6609,7 +6609,7 @@
       <c r="L70" s="49"/>
       <c r="M70" s="49"/>
     </row>
-    <row r="71" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A71" s="3" t="s">
         <v>119</v>
       </c>
@@ -6639,7 +6639,7 @@
       <c r="L71" s="49"/>
       <c r="M71" s="49"/>
     </row>
-    <row r="72" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A72" s="3"/>
       <c r="H72" s="49"/>
       <c r="I72" s="49"/>
@@ -6648,7 +6648,7 @@
       <c r="L72" s="49"/>
       <c r="M72" s="49"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>10</v>
       </c>
@@ -6662,7 +6662,7 @@
       <c r="L73" s="49"/>
       <c r="M73" s="49"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -6676,7 +6676,7 @@
       <c r="L74" s="49"/>
       <c r="M74" s="49"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -6690,7 +6690,7 @@
       <c r="L75" s="49"/>
       <c r="M75" s="49"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -6716,18 +6716,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A47D5AD-F7DD-4153-9FDF-3A8CE2F55F2C}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="11.84375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3828125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="11.921875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="11.07421875" style="13"/>
-    <col min="6" max="6" width="11.84375" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.07421875" style="13"/>
+    <col min="1" max="1" width="27.6640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="11.9296875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="11.06640625" style="13"/>
+    <col min="6" max="6" width="11.86328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.06640625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>15</v>
       </c>
@@ -6741,7 +6741,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
         <v>143</v>
       </c>
@@ -6751,7 +6751,7 @@
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
         <v>144</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>3.94778101992449</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
         <v>145</v>
       </c>
@@ -6773,13 +6773,13 @@
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="62" t="s">
         <v>146</v>
       </c>
@@ -6789,7 +6789,7 @@
       <c r="C6" s="62"/>
       <c r="D6" s="62"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="62" t="s">
         <v>147</v>
       </c>
@@ -6797,7 +6797,7 @@
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="62" t="s">
         <v>148</v>
       </c>
@@ -6807,7 +6807,7 @@
       <c r="C8" s="62"/>
       <c r="D8" s="62"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
         <v>0</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
         <v>140</v>
       </c>
@@ -6832,7 +6832,7 @@
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="14" t="s">
         <v>139</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>268.12196858508719</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="14" t="s">
         <v>141</v>
       </c>
@@ -6860,13 +6860,13 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="14"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="14" t="s">
         <v>137</v>
       </c>
@@ -6877,7 +6877,7 @@
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="14" t="s">
         <v>136</v>
       </c>
@@ -6888,7 +6888,7 @@
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="14" t="s">
         <v>138</v>
       </c>
@@ -6899,7 +6899,7 @@
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="14" t="s">
         <v>0</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F19" s="13">
         <f>11000000000/(Population!C31*1000)</f>
         <v>161.96207811068822</v>
@@ -6923,7 +6923,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="14" t="s">
         <v>142</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>1.2135683544030349</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="49" t="s">
         <v>134</v>
       </c>
@@ -6956,15 +6956,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6982,16 +6982,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0A75E4-DA25-4A08-8974-1A31A91FD529}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="11.84375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.3828125" style="13" customWidth="1"/>
-    <col min="5" max="5" width="11.921875" style="13" customWidth="1"/>
-    <col min="6" max="16384" width="11.07421875" style="13"/>
+    <col min="1" max="1" width="27.6640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.3984375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="11.9296875" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="11.06640625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>15</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
         <v>39</v>
       </c>
@@ -7026,7 +7026,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
         <v>40</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
         <v>131</v>
       </c>
@@ -7055,7 +7055,7 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
         <v>127</v>
       </c>
@@ -7066,7 +7066,7 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
         <v>129</v>
       </c>
@@ -7077,7 +7077,7 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
         <v>130</v>
       </c>
@@ -7088,7 +7088,7 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
         <v>128</v>
       </c>
@@ -7099,7 +7099,7 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
         <v>0</v>
       </c>
@@ -7116,12 +7116,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
         <v>34</v>
       </c>
@@ -7139,7 +7139,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>3.239875298796179</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
         <v>0</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="14" t="s">
         <v>29</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>268.27267535000004</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="14" t="s">
         <v>30</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>249.25587810999997</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="14" t="s">
         <v>0</v>
       </c>
@@ -7233,16 +7233,16 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="68"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7259,132 +7259,132 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE59BEB1-58EA-414F-91E0-ADFFF27E94F9}">
   <dimension ref="A2:U6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.07421875" style="13"/>
+    <col min="1" max="1" width="11.06640625" style="13"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="73" t="s">
+    <row r="2" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="74" t="s">
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="73" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="74" t="s">
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="74"/>
-      <c r="M2" s="75" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="69" t="s">
+      <c r="N2" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="73" t="s">
+      <c r="O2" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="74" t="s">
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="S2" s="74"/>
-      <c r="T2" s="76" t="s">
+      <c r="S2" s="73"/>
+      <c r="T2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="75" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="17.149999999999999" x14ac:dyDescent="0.4">
-      <c r="B3" s="70" t="s">
+    <row r="3" spans="1:21" ht="17.649999999999999" x14ac:dyDescent="0.45">
+      <c r="B3" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="70" t="s">
+      <c r="H3" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="70" t="s">
+      <c r="J3" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="71" t="s">
+      <c r="K3" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="71" t="s">
+      <c r="L3" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="M3" s="75"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="70" t="s">
+      <c r="M3" s="76"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="70" t="s">
+      <c r="P3" s="71" t="s">
         <v>60</v>
       </c>
       <c r="Q3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="R3" s="71" t="s">
+      <c r="R3" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="S3" s="71" t="s">
+      <c r="S3" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="T3" s="76"/>
-      <c r="U3" s="72"/>
-    </row>
-    <row r="4" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="70"/>
-      <c r="P4" s="70"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="75"/>
+    </row>
+    <row r="4" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
       <c r="Q4" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="72"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="R4" s="70"/>
+      <c r="S4" s="70"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="75"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="13" t="s">
         <v>65</v>
       </c>
@@ -7450,24 +7450,13 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -7482,6 +7471,17 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
